--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 30 Jun 2026 19:14</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 01 Jul 2026 19:16</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 13 Jul 2026 18:54</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 14 Jul 2026 18:35</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 20 Jul 2026 19:11</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 21 Jul 2026 18:47</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 28 Jul 2026 18:52</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 29 Jul 2026 18:30</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 30 Jul 2026 18:53</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 31 Jul 2026 18:50</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>14.02</v>
+        <v>13.99</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>12.79</v>
+        <v>12.63</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.84</v>
@@ -857,7 +857,7 @@
         <v>-22.15</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>8.77</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="14">
@@ -2081,22 +2081,22 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>76.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>26.52</v>
+        <v>27.33</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>16.58</v>
+        <v>17.03</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>-28.94</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>26.6</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="74">
@@ -2109,22 +2109,22 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>75.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.02</v>
+        <v>43.58</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>22.15</v>
+        <v>22.92</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>-57.16</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>50.36</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="75">
@@ -2137,22 +2137,22 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>21.31</v>
+        <v>21.22</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>14.61</v>
+        <v>14.46</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>-19.86</v>
       </c>
       <c r="H75" s="11" t="n">
-        <v>21.54</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="76">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>22.41</v>
+        <v>22.55</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>17.78</v>
+        <v>17.82</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>1.41</v>
@@ -2180,7 +2180,7 @@
         <v>-34.67</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>23.4</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="78">
@@ -2788,22 +2788,22 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>77.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>29.9</v>
+        <v>31.96</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>25.77</v>
+        <v>26.96</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>-27.24</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>34.83</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="108">
@@ -2816,22 +2816,22 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>23.6</v>
+        <v>24.49</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>13.18</v>
+        <v>13.62</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="G108" s="13" t="n">
         <v>-45.32</v>
       </c>
       <c r="H108" s="11" t="n">
-        <v>26.15</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="109">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="C109" s="12" t="n">
-        <v>63.1</v>
+        <v>62.9</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>9.82</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>0.51</v>
@@ -2859,7 +2859,7 @@
         <v>-30.75</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="110">
@@ -2872,22 +2872,22 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>61.6</v>
+        <v>61.9</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>11.48</v>
+        <v>11.67</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G110" s="10" t="n">
         <v>-29.85</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>5.64</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="111">
@@ -7299,67 +7299,67 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>76.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>29.37</v>
+        <v>30.84</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>26.52</v>
+        <v>27.33</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>16.58</v>
+        <v>17.03</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>7.97</v>
+        <v>8.18</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>28.29</v>
+        <v>29.61</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>26.91</v>
+        <v>27.73</v>
       </c>
       <c r="J4" s="21" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="K4" s="21" t="n">
-        <v>26.45</v>
+        <v>26.46</v>
       </c>
       <c r="L4" s="22" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M4" s="22" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="N4" s="22" t="n">
-        <v>18.85</v>
+        <v>18.87</v>
       </c>
       <c r="O4" s="23" t="n">
         <v>-28.94</v>
       </c>
       <c r="P4" s="22" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q4" s="22" t="n">
         <v>-1.85</v>
       </c>
       <c r="R4" s="24" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
       <c r="S4" s="24" t="n">
         <v>31.2</v>
       </c>
       <c r="T4" s="21" t="n">
-        <v>26.6</v>
+        <v>27.35</v>
       </c>
       <c r="U4" s="25" t="n">
-        <v>0.296</v>
+        <v>0.297</v>
       </c>
       <c r="V4" s="25" t="n">
         <v>0.043</v>
       </c>
       <c r="W4" s="21" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="X4" s="24" t="n">
         <v>87.59999999999999</v>
@@ -7368,7 +7368,7 @@
         <v>4.7</v>
       </c>
       <c r="Z4" s="19" t="n">
-        <v>21.552</v>
+        <v>21.9644</v>
       </c>
     </row>
     <row r="5">
@@ -7381,67 +7381,67 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>75.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>58.51</v>
+        <v>63.83</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>42.02</v>
+        <v>43.58</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>22.15</v>
+        <v>22.92</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>12.02</v>
+        <v>12.39</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>50.55</v>
+        <v>53.08</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>36.07</v>
+        <v>38.07</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>18.01</v>
+        <v>18.02</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>10.63</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>34.45</v>
+        <v>34.48</v>
       </c>
       <c r="O5" s="13" t="n">
         <v>-57.16</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>-3.38</v>
+        <v>-3.37</v>
       </c>
       <c r="R5" s="17" t="n">
-        <v>56.2</v>
+        <v>58.1</v>
       </c>
       <c r="S5" s="17" t="n">
         <v>27.6</v>
       </c>
       <c r="T5" s="11" t="n">
-        <v>50.36</v>
+        <v>52.02</v>
       </c>
       <c r="U5" s="18" t="n">
-        <v>0.527</v>
+        <v>0.528</v>
       </c>
       <c r="V5" s="18" t="n">
         <v>0.039</v>
       </c>
       <c r="W5" s="11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X5" s="17" t="n">
         <v>55.5</v>
@@ -7450,7 +7450,7 @@
         <v>13.6</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>52.5314</v>
+        <v>54.2816</v>
       </c>
     </row>
     <row r="6">
@@ -7463,25 +7463,25 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>21.7</v>
+        <v>21.16</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>21.31</v>
+        <v>21.22</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>14.61</v>
+        <v>14.46</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>9.890000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>22.89</v>
+        <v>22.69</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>19.86</v>
+        <v>19.97</v>
       </c>
       <c r="J6" s="21" t="n">
         <v>16.27</v>
@@ -7490,13 +7490,13 @@
         <v>15.88</v>
       </c>
       <c r="L6" s="22" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>15.35</v>
+        <v>15.34</v>
       </c>
       <c r="O6" s="22" t="n">
         <v>-19.86</v>
@@ -7505,16 +7505,16 @@
         <v>1.07</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>-1.45</v>
+        <v>-1.44</v>
       </c>
       <c r="R6" s="24" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="S6" s="24" t="n">
         <v>52.1</v>
       </c>
       <c r="T6" s="21" t="n">
-        <v>21.54</v>
+        <v>21.36</v>
       </c>
       <c r="U6" s="25" t="n">
         <v>0.403</v>
@@ -7523,7 +7523,7 @@
         <v>0.122</v>
       </c>
       <c r="W6" s="21" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X6" s="24" t="n">
         <v>83.7</v>
@@ -7532,7 +7532,7 @@
         <v>5.8</v>
       </c>
       <c r="Z6" s="19" t="n">
-        <v>25.6949</v>
+        <v>25.6362</v>
       </c>
     </row>
     <row r="7">
@@ -7545,25 +7545,25 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>24.29</v>
+        <v>26.06</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>22.41</v>
+        <v>22.55</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>17.78</v>
+        <v>17.82</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>14.93</v>
+        <v>14.97</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>25.91</v>
+        <v>26.1</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>22.78</v>
+        <v>23.11</v>
       </c>
       <c r="J7" s="11" t="n">
         <v>12.92</v>
@@ -7575,10 +7575,10 @@
         <v>1.41</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>14.75</v>
+        <v>14.74</v>
       </c>
       <c r="O7" s="13" t="n">
         <v>-34.67</v>
@@ -7590,19 +7590,19 @@
         <v>-1.3</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="S7" s="17" t="n">
         <v>52</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>23.4</v>
+        <v>23.45</v>
       </c>
       <c r="U7" s="18" t="n">
         <v>0.448</v>
       </c>
       <c r="V7" s="18" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="W7" s="11" t="n">
         <v>1.13</v>
@@ -7614,7 +7614,7 @@
         <v>12.2</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>42.7993</v>
+        <v>42.9379</v>
       </c>
     </row>
     <row r="8">
@@ -7710,28 +7710,28 @@
         <v>69.8</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>21.61</v>
+        <v>22.04</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>21.63</v>
+        <v>21.69</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12.4</v>
+        <v>12.31</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>22.86</v>
+        <v>22.93</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>19.49</v>
+        <v>19.82</v>
       </c>
       <c r="J9" s="11" t="n">
         <v>15.02</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>1</v>
@@ -7740,7 +7740,7 @@
         <v>1.31</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>19.16</v>
+        <v>19.14</v>
       </c>
       <c r="O9" s="13" t="n">
         <v>-30.84</v>
@@ -7758,7 +7758,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="T9" s="11" t="n">
-        <v>22.12</v>
+        <v>22.1</v>
       </c>
       <c r="U9" s="18" t="n">
         <v>0.477</v>
@@ -7776,7 +7776,7 @@
         <v>5.2</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>18.91</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="10">
@@ -7789,25 +7789,25 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>14.19</v>
+        <v>15.24</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>16.95</v>
+        <v>17.23</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>11.14</v>
+        <v>11.41</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>15.89</v>
+        <v>15.97</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>16.18</v>
+        <v>16.63</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>15.78</v>
+        <v>16.23</v>
       </c>
       <c r="J10" s="21" t="n">
         <v>16.65</v>
@@ -7816,37 +7816,37 @@
         <v>16.1</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>15.92</v>
+        <v>15.91</v>
       </c>
       <c r="O10" s="23" t="n">
         <v>-30.78</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q10" s="22" t="n">
         <v>-1.52</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="S10" s="24" t="n">
         <v>15</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>18.68</v>
+        <v>18.93</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="V10" s="25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="W10" s="21" t="n">
         <v>0.53</v>
@@ -7858,7 +7858,7 @@
         <v>11</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>45.6025</v>
+        <v>45.9231</v>
       </c>
     </row>
     <row r="11">
@@ -7867,80 +7867,80 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>HSBC Global Emerging Market Fund - Growth Direct</t>
+          <t>DSP World Mining Overseas Equity Omni FoF - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>67.8</v>
+        <v>68.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>44.82</v>
+        <v>70.56</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>22.74</v>
+        <v>23.06</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11.11</v>
+        <v>15.82</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>11.97</v>
+        <v>16.89</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>31.77</v>
+        <v>36.52</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>21.17</v>
+        <v>24.96</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>10.29</v>
+        <v>13.5</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>7.28</v>
+        <v>10.24</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1.12</v>
+        <v>0.86</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>19.61</v>
+        <v>27.01</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>-34.59</v>
+        <v>-62.21</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>-1.77</v>
+        <v>-2.64</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>71.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>73.5</v>
+        <v>67.5</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>22.89</v>
+        <v>23.66</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>0.681</v>
+        <v>0.59</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.218</v>
+        <v>0.079</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>1.04</v>
+        <v>0.68</v>
       </c>
       <c r="X11" s="17" t="n">
-        <v>67.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Y11" s="17" t="n">
         <v>13.6</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>35.2742</v>
+        <v>33.2789</v>
       </c>
     </row>
     <row r="12">
@@ -7949,80 +7949,80 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>DSP World Mining Overseas Equity Omni FoF - Direct Plan - Growth</t>
+          <t>HSBC Global Emerging Market Fund - Growth Direct</t>
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>66.38</v>
+        <v>45</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>21.88</v>
+        <v>22.9</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>15.18</v>
+        <v>10.77</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>16.55</v>
+        <v>12.01</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>34.42</v>
+        <v>32</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>23.43</v>
+        <v>21.7</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>13.49</v>
+        <v>10.29</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>10.24</v>
+        <v>7.28</v>
       </c>
       <c r="L12" s="22" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>26.98</v>
+        <v>19.6</v>
       </c>
       <c r="O12" s="23" t="n">
-        <v>-62.21</v>
+        <v>-34.59</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>-2.64</v>
+        <v>-1.77</v>
       </c>
       <c r="R12" s="24" t="n">
-        <v>62.6</v>
+        <v>71.5</v>
       </c>
       <c r="S12" s="24" t="n">
-        <v>67.5</v>
+        <v>73.5</v>
       </c>
       <c r="T12" s="21" t="n">
-        <v>22.48</v>
+        <v>22.94</v>
       </c>
       <c r="U12" s="25" t="n">
-        <v>0.589</v>
+        <v>0.681</v>
       </c>
       <c r="V12" s="25" t="n">
-        <v>0.079</v>
+        <v>0.218</v>
       </c>
       <c r="W12" s="21" t="n">
-        <v>0.64</v>
+        <v>1.04</v>
       </c>
       <c r="X12" s="24" t="n">
-        <v>68.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="Y12" s="24" t="n">
         <v>13.6</v>
       </c>
       <c r="Z12" s="19" t="n">
-        <v>32.3287</v>
+        <v>35.4116</v>
       </c>
     </row>
     <row r="13">
@@ -8031,80 +8031,80 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Principal Global Opportunities Fund-Direct Plan - Growth Option</t>
+          <t>Aditya Birla Sun Life International Equity Fund - Growth - Direct Plan</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>66</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>26.44</v>
+        <v>22.58</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>25.03</v>
+        <v>17.94</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>16.84</v>
+        <v>11.85</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>8.35</v>
+        <v>13.51</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>25.77</v>
+        <v>22.99</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>18.22</v>
+        <v>17.94</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>11.54</v>
+        <v>11.62</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>8.210000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>19.98</v>
+        <v>12.74</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>-37.39</v>
+        <v>-27.46</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-1.64</v>
+        <v>-1.19</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>12.9</v>
+        <v>18.1</v>
       </c>
       <c r="S13" s="17" t="n">
-        <v>27</v>
+        <v>20.1</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>22.45</v>
+        <v>17.75</v>
       </c>
       <c r="U13" s="18" t="n">
-        <v>0.233</v>
+        <v>0.172</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>0.063</v>
+        <v>0.032</v>
       </c>
       <c r="W13" s="11" t="n">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="X13" s="17" t="n">
-        <v>68.2</v>
+        <v>84.5</v>
       </c>
       <c r="Y13" s="17" t="n">
-        <v>9</v>
+        <v>13.6</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>49.2461</v>
+        <v>56.2156</v>
       </c>
     </row>
     <row r="14">
@@ -8113,80 +8113,80 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life International Equity Fund - Growth - Direct Plan</t>
+          <t>Principal Global Opportunities Fund-Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>65.5</v>
+        <v>66</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>21.42</v>
+        <v>26.44</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>17.15</v>
+        <v>25.03</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>11.36</v>
+        <v>16.84</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>13.29</v>
+        <v>8.35</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>21.61</v>
+        <v>25.77</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>16.91</v>
+        <v>18.22</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>11.61</v>
+        <v>11.54</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>9.75</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>12.7</v>
+        <v>19.98</v>
       </c>
       <c r="O14" s="23" t="n">
-        <v>-27.46</v>
+        <v>-37.39</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="R14" s="24" t="n">
-        <v>17.5</v>
+        <v>12.9</v>
       </c>
       <c r="S14" s="24" t="n">
-        <v>20.1</v>
+        <v>27</v>
       </c>
       <c r="T14" s="21" t="n">
-        <v>16.98</v>
+        <v>22.45</v>
       </c>
       <c r="U14" s="25" t="n">
-        <v>0.171</v>
+        <v>0.233</v>
       </c>
       <c r="V14" s="25" t="n">
-        <v>0.032</v>
+        <v>0.063</v>
       </c>
       <c r="W14" s="21" t="n">
-        <v>0.51</v>
+        <v>0.09</v>
       </c>
       <c r="X14" s="24" t="n">
-        <v>84.5</v>
+        <v>68.2</v>
       </c>
       <c r="Y14" s="24" t="n">
-        <v>13.6</v>
+        <v>9</v>
       </c>
       <c r="Z14" s="19" t="n">
-        <v>55.0964</v>
+        <v>49.2461</v>
       </c>
     </row>
     <row r="15">
@@ -8199,25 +8199,25 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>39.23</v>
+        <v>39.63</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>21.01</v>
+        <v>21.12</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10.65</v>
+        <v>10.71</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>11.11</v>
+        <v>11.14</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>27.65</v>
+        <v>27.8</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>19.46</v>
+        <v>19.9</v>
       </c>
       <c r="J15" s="11" t="n">
         <v>9.98</v>
@@ -8229,10 +8229,10 @@
         <v>1.02</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>17.71</v>
+        <v>17.7</v>
       </c>
       <c r="O15" s="13" t="n">
         <v>-31.96</v>
@@ -8244,13 +8244,13 @@
         <v>-1.72</v>
       </c>
       <c r="R15" s="17" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="S15" s="17" t="n">
         <v>69.7</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>18.74</v>
+        <v>18.77</v>
       </c>
       <c r="U15" s="18" t="n">
         <v>0.584</v>
@@ -8268,7 +8268,7 @@
         <v>13.6</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>39.672</v>
+        <v>39.784</v>
       </c>
     </row>
     <row r="16">
@@ -8605,80 +8605,80 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>ICICI Prudential Global Stable Equity Fund (FOF) - Direct - Growth</t>
+          <t>PGIM India Global Equity Opportunities Fund of Fund- Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C20" s="20" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>23.51</v>
+        <v>10.1</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>13.91</v>
+        <v>15.28</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>10.9</v>
+        <v>6.3</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>10.39</v>
+        <v>14.73</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>17.72</v>
+        <v>12.74</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>14.51</v>
+        <v>13.56</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>10.43</v>
+        <v>17.81</v>
       </c>
       <c r="K20" s="21" t="n">
-        <v>9.67</v>
+        <v>16.51</v>
       </c>
       <c r="L20" s="22" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>1.17</v>
+        <v>0.85</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>11.75</v>
+        <v>21.04</v>
       </c>
       <c r="O20" s="23" t="n">
-        <v>-26.16</v>
+        <v>-43.42</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>-1.08</v>
+        <v>-2.09</v>
       </c>
       <c r="R20" s="24" t="n">
-        <v>20.6</v>
+        <v>26.7</v>
       </c>
       <c r="S20" s="24" t="n">
-        <v>30.7</v>
+        <v>38.6</v>
       </c>
       <c r="T20" s="21" t="n">
-        <v>14.2</v>
+        <v>17.16</v>
       </c>
       <c r="U20" s="25" t="n">
-        <v>0.251</v>
+        <v>0.248</v>
       </c>
       <c r="V20" s="25" t="n">
-        <v>0.077</v>
+        <v>0.025</v>
       </c>
       <c r="W20" s="21" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="X20" s="24" t="n">
-        <v>95.5</v>
+        <v>84.3</v>
       </c>
       <c r="Y20" s="24" t="n">
-        <v>12.9</v>
+        <v>10.4</v>
       </c>
       <c r="Z20" s="19" t="n">
-        <v>37.04</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="21">
@@ -8687,80 +8687,80 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Kotak US Equity Fund - Direct Plan - Growth option</t>
+          <t>ICICI Prudential Global Stable Equity Fund (FOF) - Direct - Growth</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>60.5</v>
+        <v>61.2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>17.12</v>
+        <v>21.44</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>13.33</v>
+        <v>13.45</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>11.68</v>
+        <v>10.63</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>6.17</v>
+        <v>10.26</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>15.3</v>
+        <v>16.85</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>13.95</v>
+        <v>14.15</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>11.32</v>
+        <v>10.43</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>12.25</v>
+        <v>9.67</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>-22.42</v>
+        <v>11.77</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>-26.16</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>-1.34</v>
+        <v>-1.12</v>
       </c>
       <c r="R21" s="17" t="n">
-        <v>7.2</v>
+        <v>20.2</v>
       </c>
       <c r="S21" s="17" t="n">
-        <v>-8.199999999999999</v>
+        <v>30.7</v>
       </c>
       <c r="T21" s="11" t="n">
-        <v>15.51</v>
+        <v>13.64</v>
       </c>
       <c r="U21" s="18" t="n">
-        <v>0.011</v>
+        <v>0.25</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="W21" s="11" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="X21" s="17" t="n">
-        <v>92.5</v>
+        <v>95.5</v>
       </c>
       <c r="Y21" s="17" t="n">
-        <v>5.1</v>
+        <v>12.9</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>20.129</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="22">
@@ -8769,80 +8769,80 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life International Equity Fund - Plan B - Growth - Direct Plan</t>
+          <t>Kotak US Equity Fund - Direct Plan - Growth option</t>
         </is>
       </c>
       <c r="C22" s="20" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>14.21</v>
+        <v>17.12</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>19.43</v>
+        <v>13.33</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>9.470000000000001</v>
+        <v>11.68</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>12.05</v>
+        <v>6.17</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>12.23</v>
+        <v>15.3</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>12.76</v>
+        <v>13.95</v>
       </c>
       <c r="J22" s="21" t="n">
-        <v>12.54</v>
+        <v>11.32</v>
       </c>
       <c r="K22" s="21" t="n">
-        <v>10.7</v>
+        <v>12.25</v>
       </c>
       <c r="L22" s="22" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>1.45</v>
+        <v>0.88</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="O22" s="23" t="n">
-        <v>-36.39</v>
+        <v>13.03</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>-22.42</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>-1.42</v>
+        <v>-1.34</v>
       </c>
       <c r="R22" s="24" t="n">
-        <v>63.7</v>
+        <v>7.2</v>
       </c>
       <c r="S22" s="24" t="n">
-        <v>90</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="T22" s="21" t="n">
-        <v>2.91</v>
+        <v>15.51</v>
       </c>
       <c r="U22" s="25" t="n">
-        <v>0.784</v>
+        <v>0.011</v>
       </c>
       <c r="V22" s="25" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="W22" s="23" t="n">
-        <v>-0.22</v>
+        <v>0</v>
+      </c>
+      <c r="W22" s="21" t="n">
+        <v>0.17</v>
       </c>
       <c r="X22" s="24" t="n">
-        <v>73.7</v>
+        <v>92.5</v>
       </c>
       <c r="Y22" s="24" t="n">
-        <v>10.6</v>
+        <v>5.1</v>
       </c>
       <c r="Z22" s="19" t="n">
-        <v>30.2806</v>
+        <v>20.129</v>
       </c>
     </row>
     <row r="23">
@@ -8851,80 +8851,80 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>PGIM India Global Equity Opportunities Fund of Fund- Direct Plan - Growth</t>
+          <t>Aditya Birla Sun Life International Equity Fund - Plan B - Growth - Direct Plan</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>59.7</v>
+        <v>60.4</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>6.03</v>
+        <v>14.21</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13.66</v>
+        <v>19.43</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5.41</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>14.24</v>
+        <v>12.05</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>9.92</v>
+        <v>12.23</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>11.63</v>
+        <v>12.76</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>17.8</v>
+        <v>12.54</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>16.51</v>
+        <v>10.7</v>
       </c>
       <c r="L23" s="10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>-36.39</v>
+      </c>
+      <c r="P23" s="10" t="n">
         <v>0.53</v>
       </c>
-      <c r="M23" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="N23" s="10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O23" s="13" t="n">
-        <v>-43.42</v>
-      </c>
-      <c r="P23" s="10" t="n">
-        <v>0.31</v>
-      </c>
       <c r="Q23" s="10" t="n">
-        <v>-2.09</v>
+        <v>-1.42</v>
       </c>
       <c r="R23" s="17" t="n">
-        <v>25.1</v>
+        <v>63.7</v>
       </c>
       <c r="S23" s="17" t="n">
-        <v>38.6</v>
+        <v>90</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>15.4</v>
+        <v>2.91</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>0.246</v>
+        <v>0.784</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="W23" s="11" t="n">
-        <v>0.37</v>
+        <v>0.777</v>
+      </c>
+      <c r="W23" s="13" t="n">
+        <v>-0.22</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="Y23" s="17" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>53.48</v>
+        <v>30.2806</v>
       </c>
     </row>
     <row r="24">
@@ -9179,78 +9179,80 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>PGIM India Global Select Real Estate Securities Fund of Fund - Direct Plan - Growth Option</t>
+          <t>DSP Global Clean Energy Overseas Equity Omni FoF Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
-        <v>56</v>
+        <v>56.8</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>27.39</v>
+        <v>40.29</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>16.08</v>
+        <v>15.63</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6.61</v>
+        <v>12.35</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>3.25</v>
+        <v>9.58</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>20.08</v>
+        <v>26.7</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>15.15</v>
+        <v>18.95</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="K27" s="13" t="n"/>
+        <v>7.81</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>4.48</v>
+      </c>
       <c r="L27" s="10" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>1.27</v>
+        <v>0.95</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>14.18</v>
+        <v>20.4</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>-27.4</v>
+        <v>-49.73</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>-1.41</v>
+        <v>-2</v>
       </c>
       <c r="R27" s="17" t="n">
-        <v>13.5</v>
+        <v>48.1</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>8.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="T27" s="11" t="n">
-        <v>17.7</v>
+        <v>15.34</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>0.135</v>
+        <v>0.427</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>0.016</v>
+        <v>0.073</v>
       </c>
       <c r="W27" s="11" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="X27" s="17" t="n">
-        <v>80.5</v>
+        <v>58.4</v>
       </c>
       <c r="Y27" s="17" t="n">
-        <v>4.6</v>
+        <v>13.6</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>14.42</v>
+        <v>29.9851</v>
       </c>
     </row>
     <row r="28">
@@ -9259,80 +9261,78 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>DSP Global Clean Energy Overseas Equity Omni FoF Direct Plan - Growth</t>
+          <t>PGIM India Global Select Real Estate Securities Fund of Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C28" s="20" t="n">
-        <v>55.4</v>
+        <v>55.7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>36.81</v>
+        <v>27.71</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>14.71</v>
+        <v>15.97</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>12.01</v>
+        <v>6.55</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>9.32</v>
+        <v>3.22</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>25.03</v>
+        <v>19.85</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>17.76</v>
+        <v>15.01</v>
       </c>
       <c r="J28" s="21" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="K28" s="21" t="n">
-        <v>4.48</v>
-      </c>
+        <v>9.25</v>
+      </c>
+      <c r="K28" s="23" t="n"/>
       <c r="L28" s="22" t="n">
-        <v>0.59</v>
+        <v>0.87</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>0.87</v>
+        <v>1.25</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>20.36</v>
+        <v>14.17</v>
       </c>
       <c r="O28" s="23" t="n">
-        <v>-49.73</v>
+        <v>-27.4</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>-2</v>
+        <v>-1.41</v>
       </c>
       <c r="R28" s="24" t="n">
-        <v>46.9</v>
+        <v>13.4</v>
       </c>
       <c r="S28" s="24" t="n">
-        <v>65.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="T28" s="21" t="n">
-        <v>14.42</v>
+        <v>17.54</v>
       </c>
       <c r="U28" s="25" t="n">
-        <v>0.426</v>
+        <v>0.135</v>
       </c>
       <c r="V28" s="25" t="n">
-        <v>0.073</v>
+        <v>0.016</v>
       </c>
       <c r="W28" s="21" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="X28" s="24" t="n">
-        <v>58.4</v>
+        <v>80.5</v>
       </c>
       <c r="Y28" s="24" t="n">
-        <v>13.6</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" s="19" t="n">
-        <v>29.2763</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="29">
@@ -9341,85 +9341,83 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Invesco India - Invesco Global Consumer Trends Fund of Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Global Electric &amp; Autonomous Vehicles Equity Passive FOF - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
-        <v>55.1</v>
+        <v>54.2</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>6.34</v>
+        <v>48.93</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>16.9</v>
+        <v>11.58</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2.84</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>1.96</v>
+        <v>4.63</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>18.24</v>
+        <v>25.65</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>14.17</v>
+        <v>21.15</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="K29" s="11" t="n">
-        <v>8.550000000000001</v>
-      </c>
+        <v>18.45</v>
+      </c>
+      <c r="K29" s="13" t="n"/>
       <c r="L29" s="10" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>29.81</v>
+        <v>28.11</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>-51.22</v>
+        <v>-30.41</v>
       </c>
       <c r="P29" s="10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>-3.28</v>
+        <v>-2.38</v>
       </c>
       <c r="R29" s="17" t="n">
-        <v>82.8</v>
+        <v>27.7</v>
       </c>
       <c r="S29" s="17" t="n">
-        <v>82</v>
+        <v>45.3</v>
       </c>
       <c r="T29" s="11" t="n">
-        <v>18.93</v>
+        <v>14.32</v>
       </c>
       <c r="U29" s="18" t="n">
-        <v>0.714</v>
+        <v>0.215</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>0.098</v>
+        <v>0.01</v>
       </c>
       <c r="W29" s="11" t="n">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="X29" s="17" t="n">
-        <v>67.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="Y29" s="17" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>12.1571</v>
+        <v>15.877</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
@@ -9503,78 +9501,80 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Global Electric &amp; Autonomous Vehicles Equity Passive FOF - Direct Plan - Growth</t>
+          <t>Invesco India - Invesco Global Consumer Trends Fund of Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>43.9</v>
+        <v>3.2</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>10.52</v>
+        <v>15.39</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>8.84</v>
+        <v>2.28</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>4.33</v>
+        <v>1.57</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>23.66</v>
+        <v>15.53</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>19.63</v>
+        <v>12.96</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>18.42</v>
-      </c>
-      <c r="K31" s="13" t="n"/>
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>8.539999999999999</v>
+      </c>
       <c r="L31" s="10" t="n">
-        <v>0.32</v>
+        <v>0.55</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>28.08</v>
+        <v>29.89</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>-30.41</v>
+        <v>-51.22</v>
       </c>
       <c r="P31" s="10" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="Q31" s="10" t="n">
-        <v>-2.38</v>
+        <v>-3.32</v>
       </c>
       <c r="R31" s="17" t="n">
-        <v>26.6</v>
+        <v>79.5</v>
       </c>
       <c r="S31" s="17" t="n">
-        <v>45.3</v>
+        <v>82</v>
       </c>
       <c r="T31" s="11" t="n">
-        <v>13.24</v>
+        <v>17.13</v>
       </c>
       <c r="U31" s="18" t="n">
-        <v>0.213</v>
+        <v>0.712</v>
       </c>
       <c r="V31" s="18" t="n">
-        <v>0.01</v>
+        <v>0.096</v>
       </c>
       <c r="W31" s="11" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="X31" s="17" t="n">
-        <v>64.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Y31" s="17" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>15.43</v>
+        <v>11.6926</v>
       </c>
     </row>
     <row r="32">
@@ -9587,66 +9587,66 @@
         </is>
       </c>
       <c r="C32" s="27" t="n">
-        <v>46</v>
+        <v>46.6</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>10.22</v>
+        <v>11.01</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H32" s="23" t="n"/>
       <c r="I32" s="23" t="n"/>
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="22" t="n">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>3.59</v>
+        <v>3.89</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>11.49</v>
+        <v>11.46</v>
       </c>
       <c r="O32" s="22" t="n">
         <v>-3.86</v>
       </c>
       <c r="P32" s="22" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>-1.11</v>
+        <v>-1.08</v>
       </c>
       <c r="R32" s="24" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="S32" s="24" t="n">
         <v>-27</v>
       </c>
       <c r="T32" s="21" t="n">
-        <v>37.36</v>
+        <v>39.91</v>
       </c>
       <c r="U32" s="25" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="V32" s="25" t="n">
         <v>0.001</v>
       </c>
       <c r="W32" s="21" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="X32" s="24" t="n"/>
       <c r="Y32" s="24" t="n">
         <v>0.3</v>
       </c>
       <c r="Z32" s="19" t="n">
-        <v>11.036</v>
+        <v>11.115</v>
       </c>
     </row>
     <row r="33">
@@ -9741,67 +9741,67 @@
         </is>
       </c>
       <c r="C34" s="27" t="n">
-        <v>45.1</v>
+        <v>43.5</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>14.56</v>
+        <v>10.05</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>10.09</v>
+        <v>9.18</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>4.22</v>
+        <v>3.72</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>13.65</v>
+        <v>11.95</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>8.9</v>
+        <v>8.06</v>
       </c>
       <c r="J34" s="21" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="K34" s="21" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="22" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>17.15</v>
+        <v>17.21</v>
       </c>
       <c r="O34" s="23" t="n">
         <v>-25.54</v>
       </c>
       <c r="P34" s="22" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>-1.63</v>
+        <v>-1.66</v>
       </c>
       <c r="R34" s="24" t="n">
-        <v>30.3</v>
+        <v>29.3</v>
       </c>
       <c r="S34" s="24" t="n">
         <v>52.5</v>
       </c>
       <c r="T34" s="21" t="n">
-        <v>10.59</v>
+        <v>9.49</v>
       </c>
       <c r="U34" s="25" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="V34" s="25" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="W34" s="21" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="X34" s="24" t="n">
         <v>63.4</v>
@@ -9810,7 +9810,7 @@
         <v>5.6</v>
       </c>
       <c r="Z34" s="19" t="n">
-        <v>12.6635</v>
+        <v>12.3528</v>
       </c>
     </row>
     <row r="35">
@@ -13178,25 +13178,25 @@
         </is>
       </c>
       <c r="C34" s="20" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>10.91</v>
+        <v>10.96</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>9.869999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>11.13</v>
+        <v>11.15</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>6.7</v>
+        <v>6.78</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="J34" s="21" t="n">
         <v>14.75</v>
@@ -13208,10 +13208,10 @@
         <v>0.45</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>12.74</v>
+        <v>12.73</v>
       </c>
       <c r="O34" s="23" t="n">
         <v>-36.25</v>
@@ -13220,16 +13220,16 @@
         <v>0.3</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>-1.3</v>
+        <v>-1.29</v>
       </c>
       <c r="R34" s="24" t="n">
-        <v>90.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="S34" s="24" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="T34" s="21" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="U34" s="25" t="n">
         <v>0.927</v>
@@ -13238,7 +13238,7 @@
         <v>0.927</v>
       </c>
       <c r="W34" s="21" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="X34" s="24" t="n">
         <v>81.7</v>
@@ -13247,7 +13247,7 @@
         <v>13.6</v>
       </c>
       <c r="Z34" s="19" t="n">
-        <v>1139.1655</v>
+        <v>1140.7752</v>
       </c>
     </row>
     <row r="35">
@@ -18482,22 +18482,22 @@
         <v>73.09999999999999</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>7.08</v>
+        <v>6.91</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>16.12</v>
+        <v>16.23</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>13.71</v>
+        <v>13.4</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>14.34</v>
+        <v>14.37</v>
       </c>
       <c r="H46" s="21" t="n">
-        <v>11.42</v>
+        <v>11.59</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>14.2</v>
+        <v>14.33</v>
       </c>
       <c r="J46" s="21" t="n">
         <v>21.62</v>
@@ -18506,13 +18506,13 @@
         <v>21.47</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>13.34</v>
+        <v>13.33</v>
       </c>
       <c r="O46" s="23" t="n">
         <v>-31.87</v>
@@ -18524,13 +18524,13 @@
         <v>-1.32</v>
       </c>
       <c r="R46" s="24" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S46" s="24" t="n">
         <v>91.2</v>
       </c>
       <c r="T46" s="21" t="n">
-        <v>9</v>
+        <v>9.01</v>
       </c>
       <c r="U46" s="25" t="n">
         <v>0.886</v>
@@ -18548,7 +18548,7 @@
         <v>7.8</v>
       </c>
       <c r="Z46" s="19" t="n">
-        <v>38.27</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="47">
@@ -19295,25 +19295,25 @@
         </is>
       </c>
       <c r="C56" s="29" t="n">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>6.22</v>
+        <v>6.01</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>14.53</v>
+        <v>14.52</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>15.04</v>
+        <v>14.8</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>15.23</v>
+        <v>15.22</v>
       </c>
       <c r="H56" s="21" t="n">
-        <v>10.97</v>
+        <v>10.92</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>14.31</v>
+        <v>14.25</v>
       </c>
       <c r="J56" s="21" t="n">
         <v>19.5</v>
@@ -19328,7 +19328,7 @@
         <v>0.89</v>
       </c>
       <c r="N56" s="22" t="n">
-        <v>12.87</v>
+        <v>12.86</v>
       </c>
       <c r="O56" s="23" t="n">
         <v>-36.43</v>
@@ -19337,16 +19337,16 @@
         <v>0.4</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>-1.34</v>
+        <v>-1.33</v>
       </c>
       <c r="R56" s="24" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="S56" s="24" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="T56" s="21" t="n">
-        <v>7.31</v>
+        <v>7.2</v>
       </c>
       <c r="U56" s="25" t="n">
         <v>0.895</v>
@@ -19355,7 +19355,7 @@
         <v>0.837</v>
       </c>
       <c r="W56" s="21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X56" s="24" t="n">
         <v>89.5</v>
@@ -19364,12 +19364,12 @@
         <v>13.6</v>
       </c>
       <c r="Z56" s="19" t="n">
-        <v>717.9623</v>
+        <v>717.6357</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
@@ -34392,65 +34392,65 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>77.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>37.21</v>
+        <v>43.35</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>29.9</v>
+        <v>31.96</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>25.77</v>
+        <v>26.96</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>12.15</v>
+        <v>12.68</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>34.07</v>
+        <v>37.55</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>34.95</v>
+        <v>37.61</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>37.88</v>
+        <v>37.93</v>
       </c>
       <c r="K3" s="13" t="n"/>
       <c r="L3" s="10" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="N3" s="10" t="n">
-        <v>25.57</v>
+        <v>25.71</v>
       </c>
       <c r="O3" s="13" t="n">
         <v>-27.24</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>-2.53</v>
       </c>
       <c r="R3" s="17" t="n">
-        <v>29.2</v>
+        <v>31.1</v>
       </c>
       <c r="S3" s="17" t="n">
         <v>15.5</v>
       </c>
       <c r="T3" s="11" t="n">
-        <v>34.83</v>
+        <v>37.07</v>
       </c>
       <c r="U3" s="18" t="n">
-        <v>0.182</v>
+        <v>0.184</v>
       </c>
       <c r="V3" s="18" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="W3" s="11" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="X3" s="17" t="n">
         <v>99.3</v>
@@ -34459,7 +34459,7 @@
         <v>3.9</v>
       </c>
       <c r="Z3" s="8" t="n">
-        <v>31.475</v>
+        <v>33.002</v>
       </c>
     </row>
     <row r="4">
@@ -34472,67 +34472,67 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>16.32</v>
+        <v>19.01</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>23.6</v>
+        <v>24.49</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>13.18</v>
+        <v>13.62</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>14.77</v>
+        <v>15.02</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>23.56</v>
+        <v>25.05</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>22.69</v>
+        <v>23.94</v>
       </c>
       <c r="J4" s="21" t="n">
-        <v>22.88</v>
+        <v>22.89</v>
       </c>
       <c r="K4" s="21" t="n">
-        <v>18.4</v>
+        <v>18.41</v>
       </c>
       <c r="L4" s="22" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="M4" s="22" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N4" s="22" t="n">
-        <v>27.86</v>
+        <v>27.87</v>
       </c>
       <c r="O4" s="23" t="n">
         <v>-45.32</v>
       </c>
       <c r="P4" s="22" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="Q4" s="22" t="n">
         <v>-2.89</v>
       </c>
       <c r="R4" s="24" t="n">
-        <v>81.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="S4" s="24" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="T4" s="21" t="n">
-        <v>26.15</v>
+        <v>27.02</v>
       </c>
       <c r="U4" s="25" t="n">
-        <v>0.572</v>
+        <v>0.573</v>
       </c>
       <c r="V4" s="25" t="n">
         <v>0.076</v>
       </c>
       <c r="W4" s="21" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="X4" s="24" t="n">
         <v>75.40000000000001</v>
@@ -34541,7 +34541,7 @@
         <v>6.4</v>
       </c>
       <c r="Z4" s="19" t="n">
-        <v>36.7405</v>
+        <v>37.5389</v>
       </c>
     </row>
     <row r="5">
@@ -34554,25 +34554,25 @@
         </is>
       </c>
       <c r="C5" s="26" t="n">
-        <v>63.1</v>
+        <v>62.9</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>-4.98</v>
+        <v>-5.1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>9.82</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>16.19</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>9.67</v>
+        <v>9.65</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>19.24</v>
@@ -34584,10 +34584,10 @@
         <v>0.51</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
       <c r="O5" s="13" t="n">
         <v>-30.75</v>
@@ -34599,13 +34599,13 @@
         <v>-1.49</v>
       </c>
       <c r="R5" s="17" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S5" s="17" t="n">
         <v>89.8</v>
       </c>
       <c r="T5" s="11" t="n">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
       <c r="U5" s="18" t="n">
         <v>0.759</v>
@@ -34614,7 +34614,7 @@
         <v>0.447</v>
       </c>
       <c r="W5" s="11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="X5" s="17" t="n">
         <v>76.7</v>
@@ -34623,7 +34623,7 @@
         <v>13.6</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>534.0788</v>
+        <v>533.9653</v>
       </c>
     </row>
     <row r="6">
@@ -34636,25 +34636,25 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>61.6</v>
+        <v>61.9</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>-3.56</v>
+        <v>-3.26</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>11.48</v>
+        <v>11.67</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>16.64</v>
+        <v>16.7</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>4.81</v>
+        <v>5.12</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>8.43</v>
+        <v>8.59</v>
       </c>
       <c r="J6" s="21" t="n">
         <v>20.6</v>
@@ -34663,40 +34663,40 @@
         <v>18.51</v>
       </c>
       <c r="L6" s="22" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>15.28</v>
+        <v>15.27</v>
       </c>
       <c r="O6" s="23" t="n">
         <v>-29.85</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="Q6" s="22" t="n">
         <v>-1.5</v>
       </c>
       <c r="R6" s="24" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="S6" s="24" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="T6" s="21" t="n">
-        <v>5.64</v>
+        <v>5.74</v>
       </c>
       <c r="U6" s="25" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="V6" s="25" t="n">
         <v>0.467</v>
       </c>
       <c r="W6" s="21" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="X6" s="24" t="n">
         <v>78.2</v>
@@ -34705,7 +34705,7 @@
         <v>13.5</v>
       </c>
       <c r="Z6" s="19" t="n">
-        <v>233.1691</v>
+        <v>234.3394</v>
       </c>
     </row>
     <row r="7">
@@ -34800,25 +34800,25 @@
         </is>
       </c>
       <c r="C8" s="20" t="n">
-        <v>57.1</v>
+        <v>56.7</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>-5.64</v>
+        <v>-6.07</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>9.380000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>6.57</v>
+        <v>6.33</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>17.39</v>
+        <v>17.36</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>5.42</v>
+        <v>5.28</v>
       </c>
       <c r="J8" s="21" t="n">
         <v>22.85</v>
@@ -34830,37 +34830,37 @@
         <v>0.28</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="N8" s="22" t="n">
-        <v>16.96</v>
+        <v>16.95</v>
       </c>
       <c r="O8" s="23" t="n">
         <v>-35.09</v>
       </c>
       <c r="P8" s="22" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="Q8" s="22" t="n">
         <v>-1.62</v>
       </c>
       <c r="R8" s="24" t="n">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="S8" s="24" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="T8" s="21" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="U8" s="25" t="n">
-        <v>0.867</v>
+        <v>0.866</v>
       </c>
       <c r="V8" s="25" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="W8" s="21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="X8" s="24" t="n">
         <v>72.3</v>
@@ -34869,7 +34869,7 @@
         <v>13.6</v>
       </c>
       <c r="Z8" s="19" t="n">
-        <v>205.76</v>
+        <v>205.28</v>
       </c>
     </row>
     <row r="9">
@@ -35046,65 +35046,65 @@
         </is>
       </c>
       <c r="C11" s="28" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>8.210000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>8.59</v>
+        <v>9.09</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>5.07</v>
+        <v>5.36</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>9.5</v>
+        <v>10.64</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>9.5</v>
+        <v>10.64</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>15.09</v>
+        <v>15.1</v>
       </c>
       <c r="O11" s="13" t="n">
         <v>-26.24</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="Q11" s="10" t="n">
         <v>-1.57</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="S11" s="17" t="n">
         <v>85</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>8.48</v>
+        <v>9.01</v>
       </c>
       <c r="U11" s="18" t="n">
         <v>0.717</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="X11" s="17" t="n">
         <v>86.3</v>
@@ -35113,7 +35113,7 @@
         <v>2.4</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>12.8537</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="12">
@@ -35438,25 +35438,25 @@
         </is>
       </c>
       <c r="C16" s="27" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>-6.1</v>
+        <v>-5.94</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>-2.08</v>
+        <v>-1.87</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>-2.08</v>
+        <v>-1.87</v>
       </c>
       <c r="J16" s="23" t="n">
         <v>-2.97</v>
@@ -35466,10 +35466,10 @@
         <v>-0.08</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="N16" s="22" t="n">
-        <v>17.22</v>
+        <v>17.21</v>
       </c>
       <c r="O16" s="23" t="n">
         <v>-28.59</v>
@@ -35487,7 +35487,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="T16" s="21" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="U16" s="25" t="n">
         <v>0.86</v>
@@ -35505,7 +35505,7 @@
         <v>2.4</v>
       </c>
       <c r="Z16" s="19" t="n">
-        <v>10.859</v>
+        <v>10.887</v>
       </c>
     </row>
   </sheetData>
@@ -42188,25 +42188,25 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>62.3</v>
+        <v>61.9</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>6.81</v>
+        <v>6.44</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>12.93</v>
+        <v>12.87</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>11.91</v>
+        <v>11.71</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>12.06</v>
+        <v>12.04</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>9.539999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>11.9</v>
+        <v>11.82</v>
       </c>
       <c r="J10" s="21" t="n">
         <v>12.78</v>
@@ -42218,7 +42218,7 @@
         <v>0.68</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="N10" s="22" t="n">
         <v>11.4</v>
@@ -42227,28 +42227,28 @@
         <v>-31.06</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="Q10" s="22" t="n">
         <v>-1.11</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>67.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="S10" s="24" t="n">
         <v>84.5</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>7.36</v>
+        <v>7.21</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="V10" s="25" t="n">
         <v>0.829</v>
       </c>
       <c r="W10" s="21" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X10" s="24" t="n">
         <v>84.3</v>
@@ -42257,7 +42257,7 @@
         <v>12.2</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>44.955</v>
+        <v>44.8806</v>
       </c>
     </row>
     <row r="11">
@@ -42516,25 +42516,25 @@
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>4.6</v>
+        <v>4.41</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>11.87</v>
+        <v>11.86</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>10.83</v>
+        <v>10.73</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>8.619999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>10.8</v>
+        <v>10.78</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>11.06</v>
@@ -42549,7 +42549,7 @@
         <v>0.87</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O14" s="22" t="n">
         <v>-17.3</v>
@@ -42558,25 +42558,25 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.93</v>
       </c>
       <c r="R14" s="24" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="S14" s="24" t="n">
         <v>70.7</v>
       </c>
       <c r="T14" s="21" t="n">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
       <c r="U14" s="25" t="n">
         <v>0.614</v>
       </c>
       <c r="V14" s="25" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="W14" s="21" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="X14" s="24" t="n">
         <v>95</v>
@@ -42585,7 +42585,7 @@
         <v>11.8</v>
       </c>
       <c r="Z14" s="19" t="n">
-        <v>47.1626</v>
+        <v>47.1447</v>
       </c>
     </row>
     <row r="15">
@@ -43980,25 +43980,25 @@
         </is>
       </c>
       <c r="C32" s="20" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>8.48</v>
+        <v>8.31</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>6.78</v>
+        <v>6.94</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>8.98</v>
+        <v>9.1</v>
       </c>
       <c r="J32" s="21" t="n">
         <v>11.43</v>
@@ -44007,31 +44007,31 @@
         <v>11.09</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="O32" s="23" t="n">
         <v>-31.22</v>
       </c>
       <c r="P32" s="22" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="Q32" s="22" t="n">
         <v>-0.96</v>
       </c>
       <c r="R32" s="24" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="S32" s="24" t="n">
         <v>81.7</v>
       </c>
       <c r="T32" s="21" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="U32" s="25" t="n">
         <v>0.6870000000000001</v>
@@ -44049,7 +44049,7 @@
         <v>10.4</v>
       </c>
       <c r="Z32" s="19" t="n">
-        <v>157.03</v>
+        <v>157.43</v>
       </c>
     </row>
   </sheetData>
@@ -44431,25 +44431,25 @@
         </is>
       </c>
       <c r="C5" s="26" t="n">
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>6.23</v>
+        <v>5.93</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>14.02</v>
+        <v>13.99</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>12.79</v>
+        <v>12.63</v>
       </c>
       <c r="G5" s="11" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I5" s="11" t="n">
         <v>12.73</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>12.77</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>13.34</v>
@@ -44464,7 +44464,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
       <c r="O5" s="10" t="n">
         <v>-22.15</v>
@@ -44476,22 +44476,22 @@
         <v>-1.11</v>
       </c>
       <c r="R5" s="17" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="S5" s="17" t="n">
         <v>78.2</v>
       </c>
       <c r="T5" s="11" t="n">
-        <v>8.77</v>
+        <v>8.65</v>
       </c>
       <c r="U5" s="18" t="n">
         <v>0.722</v>
       </c>
       <c r="V5" s="18" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="W5" s="11" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="X5" s="17" t="n">
         <v>89.5</v>
@@ -44500,7 +44500,7 @@
         <v>11.8</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>62.257</v>
+        <v>62.1967</v>
       </c>
     </row>
     <row r="6">
@@ -45491,25 +45491,25 @@
         </is>
       </c>
       <c r="C18" s="20" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>12.06</v>
+        <v>11.83</v>
       </c>
       <c r="G18" s="21" t="n">
         <v>10.65</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>10.15</v>
+        <v>10.05</v>
       </c>
       <c r="J18" s="21" t="n">
         <v>12.63</v>
@@ -45518,10 +45518,10 @@
         <v>11.87</v>
       </c>
       <c r="L18" s="22" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="N18" s="22" t="n">
         <v>6.96</v>
@@ -45536,13 +45536,13 @@
         <v>-0.67</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="S18" s="24" t="n">
         <v>60</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>7.33</v>
+        <v>7.26</v>
       </c>
       <c r="U18" s="25" t="n">
         <v>0.482</v>
@@ -45551,7 +45551,7 @@
         <v>0.796</v>
       </c>
       <c r="W18" s="21" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="X18" s="24" t="n">
         <v>91.3</v>
@@ -45560,7 +45560,7 @@
         <v>13.6</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>190.8629</v>
+        <v>190.8108</v>
       </c>
     </row>
     <row r="19">
@@ -47987,7 +47987,7 @@
         </is>
       </c>
       <c r="C49" s="28" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>3.57</v>
@@ -48006,13 +48006,13 @@
       <c r="J49" s="13" t="n"/>
       <c r="K49" s="13" t="n"/>
       <c r="L49" s="10" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="M49" s="10" t="n">
         <v>-0.34</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>7.48</v>
+        <v>7.47</v>
       </c>
       <c r="O49" s="10" t="n">
         <v>-7.84</v>
@@ -48021,16 +48021,16 @@
         <v>0.15</v>
       </c>
       <c r="Q49" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="R49" s="17" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="S49" s="17" t="n">
         <v>65.59999999999999</v>
       </c>
       <c r="T49" s="11" t="n">
-        <v>4.21</v>
+        <v>4.01</v>
       </c>
       <c r="U49" s="18" t="n">
         <v>0.517</v>
@@ -48039,14 +48039,14 @@
         <v>0.837</v>
       </c>
       <c r="W49" s="11" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="X49" s="17" t="n"/>
       <c r="Y49" s="17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Z49" s="8" t="n">
-        <v>10.396</v>
+        <v>10.3962</v>
       </c>
     </row>
     <row r="50">
@@ -64446,160 +64446,160 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>360 ONE FLEXICAP FUND-DIRECT PLAN- GROWTH</t>
+          <t>Parag Parikh Flexi Cap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>7.37</v>
+        <v>68.8</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>-0.62</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>17.75</v>
+        <v>14.03</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10.66</v>
+        <v>13.54</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>5.2</v>
+        <v>17.42</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>12.18</v>
+        <v>7.64</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>12.22</v>
+        <v>12.59</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="K17" s="13" t="n"/>
+        <v>20.49</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>19.11</v>
+      </c>
       <c r="L17" s="10" t="n">
         <v>0.87</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>-18.12</v>
+        <v>9.890000000000001</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>-31.2</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>-1.56</v>
+        <v>-1.03</v>
       </c>
       <c r="R17" s="17" t="n">
-        <v>104.2</v>
+        <v>55.8</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>95</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>9.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.759</v>
+        <v>0.769</v>
       </c>
       <c r="W17" s="11" t="n">
-        <v>1.24</v>
+        <v>0.79</v>
       </c>
       <c r="X17" s="17" t="n">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>3.1</v>
+        <v>13.2</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>16.6744</v>
+        <v>91.34269999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Parag Parikh Flexi Cap Fund - Direct Plan - Growth</t>
+          <t>360 ONE FLEXICAP FUND-DIRECT PLAN- GROWTH</t>
         </is>
       </c>
       <c r="C18" s="20" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="D18" s="23" t="n">
-        <v>-0.96</v>
+      <c r="D18" s="21" t="n">
+        <v>7.37</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>13.89</v>
+        <v>17.75</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>13.44</v>
+        <v>10.66</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>17.38</v>
+        <v>5.2</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>7.42</v>
+        <v>12.18</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>12.48</v>
+        <v>12.22</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>19.11</v>
-      </c>
+        <v>15.89</v>
+      </c>
+      <c r="K18" s="23" t="n"/>
       <c r="L18" s="22" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="O18" s="23" t="n">
-        <v>-31.2</v>
+        <v>15.18</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>-18.12</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>-1.03</v>
+        <v>-1.56</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>55.7</v>
+        <v>104.2</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>77.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>8.56</v>
+        <v>9.65</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.656</v>
+        <v>1</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.769</v>
+        <v>0.759</v>
       </c>
       <c r="W18" s="21" t="n">
-        <v>0.79</v>
+        <v>1.24</v>
       </c>
       <c r="X18" s="24" t="n">
-        <v>90.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>13.2</v>
+        <v>3.1</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>91.0119</v>
+        <v>16.6744</v>
       </c>
     </row>
     <row r="19">
@@ -66491,22 +66491,22 @@
         <v>54.9</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>8.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>9.74</v>
+        <v>9.59</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>12.14</v>
+        <v>12.16</v>
       </c>
       <c r="H42" s="21" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>8.31</v>
+        <v>8.32</v>
       </c>
       <c r="J42" s="21" t="n">
         <v>17.86</v>
@@ -66515,13 +66515,13 @@
         <v>15.82</v>
       </c>
       <c r="L42" s="22" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="M42" s="22" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="N42" s="22" t="n">
-        <v>12.37</v>
+        <v>12.36</v>
       </c>
       <c r="O42" s="23" t="n">
         <v>-35.8</v>
@@ -66539,7 +66539,7 @@
         <v>92.8</v>
       </c>
       <c r="T42" s="21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U42" s="25" t="n">
         <v>0.885</v>
@@ -66548,7 +66548,7 @@
         <v>0.885</v>
       </c>
       <c r="W42" s="21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="X42" s="24" t="n">
         <v>83.5</v>
@@ -66557,7 +66557,7 @@
         <v>13.6</v>
       </c>
       <c r="Z42" s="19" t="n">
-        <v>121.0352</v>
+        <v>121.252</v>
       </c>
     </row>
     <row r="43">

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -616,7 +616,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 20 Aug 2026 17:52</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 21 Aug 2026 17:52</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 24 Aug 2026 17:56</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 25 Aug 2026 17:52</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 25 Aug 2026 17:52</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 26 Aug 2026 19:23</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 26 Aug 2026 19:23</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 28 Aug 2026 01:34</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 28 Aug 2026 01:34</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 29 Aug 2026 01:02</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>-0.42</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>8427847910015416</v>
+        <v>8427847910015000</v>
       </c>
     </row>
     <row r="33">
@@ -51489,7 +51489,7 @@
         <v>-13.7</v>
       </c>
       <c r="T3" s="11" t="n">
-        <v>8427847910015416</v>
+        <v>8427847910015000</v>
       </c>
       <c r="U3" s="18" t="n">
         <v>11.604</v>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 29 Aug 2026 01:02</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 31 Aug 2026 21:57</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>-0.42</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>8427847910015000</v>
+        <v>8427847910015416</v>
       </c>
     </row>
     <row r="33">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Kotak Global Innovation Overseas Equity Omni FOF- Direct Plan -Growth</t>
+          <t>Kotak Global Innovation Overseas Equity Active FOF- Direct Plan -Growth</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Kotak International REIT Overseas Equity Omni FOF - Direct Plan - Growth</t>
+          <t>Kotak International REIT Overseas Equity Active FOF - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C33" s="28" t="n">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>JM Midcap Fund (Direct) - Growth</t>
+          <t>JM Mid Cap Fund (Direct) - Growth</t>
         </is>
       </c>
       <c r="C36" s="20" t="n">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>BANDHAN MIDCAP FUND - GROWTH - DIRECT PLAN</t>
+          <t>BANDHAN MID CAP FUND - GROWTH - DIRECT PLAN</t>
         </is>
       </c>
       <c r="C68" s="20" t="n">
@@ -20915,7 +20915,7 @@
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Large and Mid Cap Fund- Direct Plan- Growth</t>
+          <t>Bajaj Finserv Large &amp; Mid Cap Fund- Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C88" s="29" t="n">
@@ -22047,7 +22047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -22736,78 +22736,78 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>HDFC Multi Cap Fund - Growth Option - Direct Plan</t>
+          <t>Kotak Multi Cap Fund-Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>77.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>-1.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>23.18</v>
+        <v>25.17</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>14.56</v>
+        <v>14.92</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>7.03</v>
+        <v>7.2</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>19.66</v>
+        <v>22.15</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>20.77</v>
+        <v>22.67</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>27.4</v>
+        <v>28.61</v>
       </c>
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>13.93</v>
+        <v>14.93</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>-20.2</v>
+        <v>-21</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>-1.42</v>
+        <v>-1.51</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>101.4</v>
+        <v>105.7</v>
       </c>
       <c r="S9" s="17" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="T9" s="11" t="n">
-        <v>9.9</v>
+        <v>11.74</v>
       </c>
       <c r="U9" s="18" t="n">
-        <v>0.969</v>
+        <v>0.978</v>
       </c>
       <c r="V9" s="18" t="n">
-        <v>0.765</v>
+        <v>0.679</v>
       </c>
       <c r="W9" s="11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X9" s="17" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="Y9" s="17" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>19.779</v>
+        <v>20.065</v>
       </c>
     </row>
     <row r="10">
@@ -22816,78 +22816,78 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Bank of India Multi Cap Fund Direct Plan - Growth</t>
+          <t>HDFC Multi Cap Fund - Growth Option - Direct Plan</t>
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>76.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>-2.15</v>
+        <v>-1.82</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>22.05</v>
+        <v>23.18</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>12.7</v>
+        <v>14.56</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>6.16</v>
+        <v>7.03</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>18.27</v>
+        <v>19.66</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>18.27</v>
+        <v>20.77</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>29.01</v>
+        <v>27.4</v>
       </c>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="22" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>16.01</v>
+        <v>13.93</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>-20.31</v>
+        <v>-20.2</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>-1.5</v>
+        <v>-1.42</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>110.8</v>
+        <v>101.4</v>
       </c>
       <c r="S10" s="24" t="n">
-        <v>95.3</v>
+        <v>93.7</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>10.48</v>
+        <v>9.9</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>1.031</v>
+        <v>0.969</v>
       </c>
       <c r="V10" s="25" t="n">
-        <v>0.65</v>
+        <v>0.765</v>
       </c>
       <c r="W10" s="21" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="X10" s="24" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="Y10" s="24" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>18.2</v>
+        <v>19.779</v>
       </c>
     </row>
     <row r="11">
@@ -22896,78 +22896,78 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>LIC MF Multi Cap Fund-Direct Plan-Growth</t>
+          <t>Bank of India Multi Cap Fund Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>74.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>-0.2</v>
+        <v>-2.15</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>20.9</v>
+        <v>22.05</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12.06</v>
+        <v>12.7</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>5.86</v>
+        <v>6.16</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>21.12</v>
+        <v>18.27</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>21.12</v>
+        <v>18.27</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>31.67</v>
+        <v>29.01</v>
       </c>
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="10" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>13.95</v>
+        <v>16.01</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>-19.32</v>
+        <v>-20.31</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>-1.42</v>
+        <v>-1.5</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>90.3</v>
+        <v>110.8</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>89.5</v>
+        <v>95.3</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>0.899</v>
+        <v>1.031</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.634</v>
+        <v>0.65</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X11" s="17" t="n">
-        <v>98.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="Y11" s="17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>17.7123</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="12">
@@ -22976,80 +22976,78 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Principal Multi Cap Growth Fund-Direct Plan - Growth Option</t>
+          <t>LIC MF Multi Cap Fund-Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>47.35</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>-0.2</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>21.35</v>
+        <v>20.9</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>19.76</v>
+        <v>12.06</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>16.01</v>
+        <v>5.86</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>34.35</v>
+        <v>21.12</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>21.95</v>
+        <v>21.12</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>14.28</v>
-      </c>
+        <v>31.67</v>
+      </c>
+      <c r="K12" s="23" t="n"/>
       <c r="L12" s="22" t="n">
-        <v>0.87</v>
+        <v>1.29</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>0.91</v>
+        <v>1.49</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>20.63</v>
-      </c>
-      <c r="O12" s="23" t="n">
-        <v>-38.67</v>
+        <v>13.95</v>
+      </c>
+      <c r="O12" s="22" t="n">
+        <v>-19.32</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>0.55</v>
+        <v>1.08</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>-1.72</v>
+        <v>-1.42</v>
       </c>
       <c r="R12" s="24" t="n">
-        <v>78.2</v>
+        <v>90.3</v>
       </c>
       <c r="S12" s="24" t="n">
-        <v>95.2</v>
+        <v>89.5</v>
       </c>
       <c r="T12" s="21" t="n">
-        <v>4.86</v>
+        <v>10.5</v>
       </c>
       <c r="U12" s="25" t="n">
-        <v>0.919</v>
+        <v>0.899</v>
       </c>
       <c r="V12" s="25" t="n">
-        <v>0.925</v>
+        <v>0.634</v>
       </c>
       <c r="W12" s="21" t="n">
-        <v>0.55</v>
+        <v>1.01</v>
       </c>
       <c r="X12" s="24" t="n">
-        <v>81.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Y12" s="24" t="n">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="Z12" s="19" t="n">
-        <v>259.0319</v>
+        <v>17.7123</v>
       </c>
     </row>
     <row r="13">
@@ -23058,78 +23056,80 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>BANDHAN MULTI CAP FUND - GROWTH - DIRECT PLAN</t>
+          <t>Principal Multi Cap Growth Fund-Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>-0.87</v>
+        <v>74.2</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>47.35</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>20.44</v>
+        <v>21.35</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>12.65</v>
+        <v>19.76</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>6.13</v>
+        <v>16.01</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>18.21</v>
+        <v>34.35</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>18.63</v>
+        <v>21.95</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K13" s="13" t="n"/>
+        <v>21.12</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>14.28</v>
+      </c>
       <c r="L13" s="10" t="n">
-        <v>1.22</v>
+        <v>0.87</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1.46</v>
+        <v>0.91</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>-18.3</v>
+        <v>20.63</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>-38.67</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>1.12</v>
+        <v>0.55</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-1.3</v>
+        <v>-1.72</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>87.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="S13" s="17" t="n">
-        <v>90.8</v>
+        <v>95.2</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>8.34</v>
+        <v>4.86</v>
       </c>
       <c r="U13" s="18" t="n">
-        <v>0.891</v>
+        <v>0.919</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>0.771</v>
+        <v>0.925</v>
       </c>
       <c r="W13" s="11" t="n">
-        <v>1.05</v>
+        <v>0.55</v>
       </c>
       <c r="X13" s="17" t="n">
-        <v>97.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Y13" s="17" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>18.156</v>
+        <v>259.0319</v>
       </c>
     </row>
     <row r="14">
@@ -23138,80 +23138,78 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>quant Multi Cap Fund-GROWTH OPTION-Direct Plan</t>
+          <t>BANDHAN MULTI CAP FUND - GROWTH - DIRECT PLAN</t>
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>73.8</v>
+        <v>74</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>-14.42</v>
+        <v>-0.87</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>14.44</v>
+        <v>20.44</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>23.99</v>
+        <v>12.65</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>18.61</v>
+        <v>6.13</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>9.640000000000001</v>
+        <v>18.21</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>15.92</v>
+        <v>18.63</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>21.77</v>
-      </c>
+        <v>22.99</v>
+      </c>
+      <c r="K14" s="23" t="n"/>
       <c r="L14" s="22" t="n">
-        <v>0.59</v>
+        <v>1.22</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="O14" s="23" t="n">
-        <v>-36.26</v>
+        <v>12.73</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>-18.3</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>-1.89</v>
+        <v>-1.3</v>
       </c>
       <c r="R14" s="24" t="n">
-        <v>113.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="S14" s="24" t="n">
-        <v>102.3</v>
+        <v>90.8</v>
       </c>
       <c r="T14" s="21" t="n">
-        <v>0.96</v>
+        <v>8.34</v>
       </c>
       <c r="U14" s="25" t="n">
-        <v>1.073</v>
+        <v>0.891</v>
       </c>
       <c r="V14" s="25" t="n">
-        <v>0.624</v>
+        <v>0.771</v>
       </c>
       <c r="W14" s="21" t="n">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="X14" s="24" t="n">
-        <v>84.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y14" s="24" t="n">
-        <v>12.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z14" s="19" t="n">
-        <v>668.4321</v>
+        <v>18.156</v>
       </c>
     </row>
     <row r="15">
@@ -23220,78 +23218,80 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>WhiteOak Capital Multi Cap Fund Direct Plan Growth</t>
+          <t>quant Multi Cap Fund-GROWTH OPTION-Direct Plan</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>8.710000000000001</v>
+        <v>73.8</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>-14.42</v>
       </c>
       <c r="E15" s="11" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="I15" s="11" t="n">
         <v>15.92</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>19.82</v>
-      </c>
       <c r="J15" s="11" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K15" s="13" t="n"/>
+        <v>25.32</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>21.77</v>
+      </c>
       <c r="L15" s="10" t="n">
-        <v>1.45</v>
+        <v>0.59</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>-16.93</v>
+        <v>17.09</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>-36.26</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>-1.57</v>
+        <v>-1.89</v>
       </c>
       <c r="R15" s="17" t="n">
-        <v>100.7</v>
+        <v>113.5</v>
       </c>
       <c r="S15" s="17" t="n">
-        <v>92.40000000000001</v>
+        <v>102.3</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>11.86</v>
+        <v>0.96</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>0.968</v>
+        <v>1.073</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>0.728</v>
+        <v>0.624</v>
       </c>
       <c r="W15" s="11" t="n">
-        <v>1.35</v>
+        <v>0.18</v>
       </c>
       <c r="X15" s="17" t="n">
-        <v>100</v>
+        <v>84.5</v>
       </c>
       <c r="Y15" s="17" t="n">
-        <v>1.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>15.608</v>
+        <v>668.4321</v>
       </c>
     </row>
     <row r="16">
@@ -23300,80 +23300,78 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>BNP Paribas MULTI CAP Fund - Direct Plan - Growth Option</t>
+          <t>WhiteOak Capital Multi Cap Fund Direct Plan Growth</t>
         </is>
       </c>
       <c r="C16" s="20" t="n">
-        <v>70.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>21.91</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>18.99</v>
+        <v>15.92</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>14.99</v>
+        <v>9.27</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>14.95</v>
+        <v>4.53</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>24.47</v>
+        <v>19.82</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>17.33</v>
+        <v>19.82</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>14.21</v>
-      </c>
+        <v>21.99</v>
+      </c>
+      <c r="K16" s="23" t="n"/>
       <c r="L16" s="22" t="n">
-        <v>0.77</v>
+        <v>1.45</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="N16" s="22" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="O16" s="23" t="n">
-        <v>-36.18</v>
+        <v>15.25</v>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>-16.93</v>
       </c>
       <c r="P16" s="22" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>-1.73</v>
+        <v>-1.57</v>
       </c>
       <c r="R16" s="24" t="n">
-        <v>73.09999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="S16" s="24" t="n">
-        <v>94.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="T16" s="21" t="n">
-        <v>6.12</v>
+        <v>11.86</v>
       </c>
       <c r="U16" s="25" t="n">
-        <v>0.862</v>
+        <v>0.968</v>
       </c>
       <c r="V16" s="25" t="n">
-        <v>0.926</v>
+        <v>0.728</v>
       </c>
       <c r="W16" s="21" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="X16" s="24" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="Y16" s="24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" s="19" t="n">
-        <v>83.9294</v>
+        <v>15.608</v>
       </c>
     </row>
     <row r="17">
@@ -23382,78 +23380,80 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Edelweiss Multi Cap Fund - Direct Plan - Growth</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>-0.21</v>
+          <t>BNP Paribas MULTI CAP Fund - Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>21.91</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>14.88</v>
+        <v>18.99</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8.68</v>
+        <v>14.99</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>4.25</v>
+        <v>14.95</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>13.75</v>
+        <v>24.47</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>13.75</v>
+        <v>17.33</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="K17" s="13" t="n"/>
+        <v>20.43</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>14.21</v>
+      </c>
       <c r="L17" s="10" t="n">
-        <v>1.37</v>
+        <v>0.77</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>1.62</v>
+        <v>0.83</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>-20.19</v>
+        <v>19.89</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>-36.18</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>-1.55</v>
+        <v>-1.73</v>
       </c>
       <c r="R17" s="17" t="n">
-        <v>112.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>97.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>8.09</v>
+        <v>6.12</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>1.03</v>
+        <v>0.862</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.769</v>
+        <v>0.926</v>
       </c>
       <c r="W17" s="11" t="n">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="X17" s="17" t="n">
-        <v>97.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>15.3825</v>
+        <v>83.9294</v>
       </c>
     </row>
     <row r="18">
@@ -23462,78 +23462,78 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Canara Robeco Multi Cap Fund - Direct Plan - Growth Option</t>
+          <t>Edelweiss Multi Cap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>2.95</v>
+        <v>69.2</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>-0.21</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>14.55</v>
+        <v>14.88</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>8.49</v>
+        <v>8.68</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>16.2</v>
+        <v>13.75</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>16.2</v>
+        <v>13.75</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>21.4</v>
+        <v>15.91</v>
       </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="22" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>14.09</v>
+        <v>15.91</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>-18.32</v>
+        <v>-20.19</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>-1.58</v>
+        <v>-1.55</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>92.09999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>91.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>9.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.919</v>
+        <v>1.03</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.731</v>
+        <v>0.769</v>
       </c>
       <c r="W18" s="21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X18" s="24" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>15.03</v>
+        <v>15.3825</v>
       </c>
     </row>
     <row r="19">
@@ -23542,78 +23542,78 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Multi Cap Fund (Formerly Known as Principal Multi Cap Growth Fund)-Direct Plan - Growth Option</t>
+          <t>Canara Robeco Multi Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>18.28</v>
+        <v>14.55</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10.17</v>
+        <v>8.49</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>4.96</v>
+        <v>4.16</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>18.09</v>
+        <v>16.2</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>17.84</v>
+        <v>16.2</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>21.03</v>
+        <v>21.4</v>
       </c>
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="10" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>12.68</v>
+        <v>14.09</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>-19.45</v>
+        <v>-18.32</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>-1.25</v>
+        <v>-1.58</v>
       </c>
       <c r="R19" s="17" t="n">
-        <v>82.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>90.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>6.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>0.883</v>
+        <v>0.919</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>0.768</v>
+        <v>0.731</v>
       </c>
       <c r="W19" s="11" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="X19" s="17" t="n">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="Y19" s="17" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>425.4797</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="20">
@@ -23622,80 +23622,78 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Sundaram Multi Cap Fund Series II Direct Plan - Growth</t>
+          <t>Sundaram Multi Cap Fund (Formerly Known as Principal Multi Cap Growth Fund)-Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>66</v>
+        <v>67.5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>8.01</v>
+        <v>1.84</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>20.17</v>
+        <v>18.28</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>12.8</v>
+        <v>10.17</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>6.21</v>
+        <v>4.96</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>11.43</v>
+        <v>18.09</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>14.61</v>
+        <v>17.84</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="K20" s="21" t="n">
-        <v>20.49</v>
-      </c>
+        <v>21.03</v>
+      </c>
+      <c r="K20" s="23" t="n"/>
       <c r="L20" s="22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="O20" s="23" t="n">
-        <v>-36.8</v>
+        <v>12.68</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>-19.45</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="R20" s="24" t="n">
-        <v>75.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S20" s="24" t="n">
-        <v>94.5</v>
+        <v>90.2</v>
       </c>
       <c r="T20" s="21" t="n">
-        <v>0.57</v>
+        <v>6.43</v>
       </c>
       <c r="U20" s="25" t="n">
-        <v>0.909</v>
+        <v>0.883</v>
       </c>
       <c r="V20" s="25" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="W20" s="23" t="n">
-        <v>-0.27</v>
+        <v>0.768</v>
+      </c>
+      <c r="W20" s="21" t="n">
+        <v>0.74</v>
       </c>
       <c r="X20" s="24" t="n">
-        <v>88</v>
+        <v>91.2</v>
       </c>
       <c r="Y20" s="24" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" s="19" t="n">
-        <v>18.309</v>
+        <v>425.4797</v>
       </c>
     </row>
     <row r="21">
@@ -23704,80 +23702,80 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Multi Cap Fund Series I Direct Plan - Growth</t>
+          <t>Sundaram Multi Cap Fund Series II Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>64.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.32</v>
+        <v>8.01</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>20.53</v>
+        <v>20.17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>12.28</v>
+        <v>12.8</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>5.96</v>
+        <v>6.21</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>11.02</v>
+        <v>11.43</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>13.98</v>
+        <v>14.61</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>17.8</v>
+        <v>18.22</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>20.18</v>
+        <v>20.49</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>14.85</v>
+        <v>14.79</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>-36.8</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="Q21" s="10" t="n">
         <v>-1.45</v>
       </c>
       <c r="R21" s="17" t="n">
-        <v>75.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="S21" s="17" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="T21" s="13" t="n">
-        <v>-0.35</v>
+        <v>94.5</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>0.57</v>
       </c>
       <c r="U21" s="18" t="n">
-        <v>0.908</v>
+        <v>0.909</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>0.893</v>
+        <v>0.89</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>-0.48</v>
+        <v>-0.27</v>
       </c>
       <c r="X21" s="17" t="n">
-        <v>86.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="Y21" s="17" t="n">
         <v>5</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>17.872</v>
+        <v>18.309</v>
       </c>
     </row>
     <row r="22">
@@ -23786,74 +23784,80 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Motilal Oswal Multi Cap Fund-Direct Plan Growth</t>
+          <t>Sundaram Multi Cap Fund Series I Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C22" s="27" t="n">
-        <v>59.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>18.76</v>
+        <v>12.32</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>10.66</v>
+        <v>20.53</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>6.27</v>
+        <v>12.28</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>3.09</v>
+        <v>5.96</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>20.25</v>
+        <v>11.02</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="23" t="n"/>
+        <v>13.98</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <v>20.18</v>
+      </c>
       <c r="L22" s="22" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="O22" s="22" t="n">
-        <v>-18.87</v>
+        <v>14.85</v>
+      </c>
+      <c r="O22" s="23" t="n">
+        <v>-36.8</v>
       </c>
       <c r="P22" s="22" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>-1.92</v>
+        <v>-1.45</v>
       </c>
       <c r="R22" s="24" t="n">
-        <v>139.6</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S22" s="24" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="T22" s="21" t="n">
-        <v>24.4</v>
+        <v>94.8</v>
+      </c>
+      <c r="T22" s="23" t="n">
+        <v>-0.35</v>
       </c>
       <c r="U22" s="25" t="n">
-        <v>1.019</v>
+        <v>0.908</v>
       </c>
       <c r="V22" s="25" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="W22" s="21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X22" s="24" t="n"/>
+        <v>0.893</v>
+      </c>
+      <c r="W22" s="23" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="X22" s="24" t="n">
+        <v>86.59999999999999</v>
+      </c>
       <c r="Y22" s="24" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="Z22" s="19" t="n">
-        <v>13.8885</v>
+        <v>17.872</v>
       </c>
     </row>
     <row r="23">
@@ -23862,80 +23866,74 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Principal Multi Cap Growth Fund - Direct Plan -Half Yearly Income Distribution CUM Capital Withdrawal Option</t>
+          <t>Motilal Oswal Multi Cap Fund-Direct Plan Growth</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>57</v>
+        <v>59.9</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>36.95</v>
+        <v>18.76</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>16.63</v>
+        <v>10.66</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>11.67</v>
+        <v>6.27</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>9.99</v>
+        <v>3.09</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>26.62</v>
+        <v>20.25</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>6.72</v>
-      </c>
+        <v>20.25</v>
+      </c>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="13" t="n"/>
       <c r="L23" s="10" t="n">
-        <v>0.62</v>
+        <v>1.37</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>0.64</v>
+        <v>1.87</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="O23" s="13" t="n">
-        <v>-40.63</v>
+        <v>19.53</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>-18.87</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>-1.75</v>
+        <v>-1.92</v>
       </c>
       <c r="R23" s="17" t="n">
-        <v>75.7</v>
+        <v>139.6</v>
       </c>
       <c r="S23" s="17" t="n">
-        <v>96.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>0.7</v>
+        <v>24.4</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>0.925</v>
+        <v>1.019</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="W23" s="13" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="X23" s="17" t="n">
-        <v>68.2</v>
-      </c>
+        <v>0.461</v>
+      </c>
+      <c r="W23" s="11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X23" s="17" t="n"/>
       <c r="Y23" s="17" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>68.8862</v>
+        <v>13.8885</v>
       </c>
     </row>
     <row r="24">
@@ -23944,78 +23942,80 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>UTI Multi Cap Fund - Growth Option - Direct</t>
+          <t>Principal Multi Cap Growth Fund - Direct Plan -Half Yearly Income Distribution CUM Capital Withdrawal Option</t>
         </is>
       </c>
       <c r="C24" s="27" t="n">
-        <v>50.4</v>
+        <v>57</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>14.54</v>
+        <v>36.95</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>9.949999999999999</v>
+        <v>16.63</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>7.39</v>
+        <v>11.67</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>3.63</v>
+        <v>9.99</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>13.31</v>
+        <v>26.62</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>11.67</v>
+        <v>16.22</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="K24" s="23" t="n"/>
+        <v>13.93</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>6.72</v>
+      </c>
       <c r="L24" s="22" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="M24" s="22" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="N24" s="22" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="O24" s="22" t="n">
-        <v>-18.58</v>
+        <v>21.2</v>
+      </c>
+      <c r="O24" s="23" t="n">
+        <v>-40.63</v>
       </c>
       <c r="P24" s="22" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>-1.53</v>
+        <v>-1.75</v>
       </c>
       <c r="R24" s="24" t="n">
-        <v>94.2</v>
+        <v>75.7</v>
       </c>
       <c r="S24" s="24" t="n">
-        <v>98</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="T24" s="21" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="U24" s="25" t="n">
-        <v>0.979</v>
+        <v>0.925</v>
       </c>
       <c r="V24" s="25" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="W24" s="21" t="n">
-        <v>0.2</v>
+        <v>0.888</v>
+      </c>
+      <c r="W24" s="23" t="n">
+        <v>-0.1</v>
       </c>
       <c r="X24" s="24" t="n">
-        <v>78.7</v>
+        <v>68.2</v>
       </c>
       <c r="Y24" s="24" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="Z24" s="19" t="n">
-        <v>14.2467</v>
+        <v>68.8862</v>
       </c>
     </row>
     <row r="25">
@@ -24024,70 +24024,78 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>UTI Multi Cap Fund - Direct Plan - Growth Option</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="n">
-        <v>38.6</v>
+          <t>UTI Multi Cap Fund - Growth Option - Direct</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>50.4</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>3.51</v>
+        <v>14.54</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1.16</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
+        <v>3.63</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>10.14</v>
+      </c>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="10" t="n">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>1.21</v>
+        <v>0.42</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>9.41</v>
+        <v>13.64</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>-3.63</v>
+        <v>-18.58</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>0.32</v>
+        <v>0.54</v>
       </c>
       <c r="Q25" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.53</v>
       </c>
       <c r="R25" s="17" t="n">
-        <v>81.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="S25" s="17" t="n">
-        <v>83.7</v>
+        <v>98</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>9.75</v>
+        <v>1.02</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>0.839</v>
+        <v>0.979</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.909</v>
       </c>
       <c r="W25" s="11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X25" s="17" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>78.7</v>
+      </c>
       <c r="Y25" s="17" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>10.3177</v>
+        <v>14.2467</v>
       </c>
     </row>
     <row r="26">
@@ -24096,70 +24104,76 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>BAJAJ FINSERV MULTI CAP FUND - DIRECT - GROWTH</t>
+          <t>DSP Multi Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>11.68</v>
+        <v>48.2</v>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>-0.93</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>3.75</v>
+        <v>7.71</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>2.23</v>
+        <v>4.56</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H26" s="23" t="n"/>
-      <c r="I26" s="23" t="n"/>
+        <v>2.25</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>11.26</v>
+      </c>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="22" t="n">
-        <v>1.74</v>
+        <v>0.7</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>2.24</v>
+        <v>0.87</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>12.93</v>
+        <v>15.33</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>-5.98</v>
+        <v>-21.27</v>
       </c>
       <c r="P26" s="22" t="n">
-        <v>0.63</v>
+        <v>0.36</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>-1.06</v>
+        <v>-1.7</v>
       </c>
       <c r="R26" s="24" t="n">
-        <v>68.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="S26" s="24" t="n">
-        <v>89.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="T26" s="21" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="U26" s="25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.876</v>
       </c>
       <c r="V26" s="25" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="W26" s="23" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="X26" s="24" t="n"/>
+        <v>0.62</v>
+      </c>
+      <c r="W26" s="21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X26" s="24" t="n">
+        <v>89.7</v>
+      </c>
       <c r="Y26" s="24" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z26" s="19" t="n">
-        <v>11.19</v>
+        <v>12.521</v>
       </c>
     </row>
     <row r="27">
@@ -24168,74 +24182,70 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Franklin India Multi Cap Fund - Direct - Growth</t>
+          <t>UTI Multi Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C27" s="28" t="n">
-        <v>34.4</v>
+        <v>38.6</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>2.29</v>
+        <v>3.51</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H27" s="11" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>8.960000000000001</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
       <c r="J27" s="13" t="n"/>
       <c r="K27" s="13" t="n"/>
       <c r="L27" s="10" t="n">
-        <v>-0.06</v>
+        <v>0.96</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>-0.09</v>
+        <v>1.21</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>15.21</v>
+        <v>9.41</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>-18.68</v>
+        <v>-3.63</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>-1.67</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="R27" s="17" t="n">
-        <v>100.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>98.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="T27" s="11" t="n">
-        <v>3.62</v>
+        <v>9.75</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>0.959</v>
+        <v>0.839</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>0.708</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W27" s="11" t="n">
-        <v>0.42</v>
+        <v>1.53</v>
       </c>
       <c r="X27" s="17" t="n"/>
       <c r="Y27" s="17" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>10.4452</v>
+        <v>10.3177</v>
       </c>
     </row>
     <row r="28">
@@ -24244,74 +24254,70 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>PGIM India Multi Cap Fund - Direct Plan - Growth Option</t>
+          <t>BAJAJ FINSERV MULTI CAP FUND - DIRECT - GROWTH</t>
         </is>
       </c>
       <c r="C28" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="D28" s="23" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E28" s="23" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F28" s="23" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G28" s="23" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="I28" s="21" t="n">
-        <v>12.54</v>
-      </c>
+        <v>38.5</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="23" t="n"/>
       <c r="J28" s="23" t="n"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="22" t="n">
-        <v>-0.37</v>
+        <v>1.74</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>-0.51</v>
+        <v>2.24</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>15.16</v>
+        <v>12.93</v>
       </c>
       <c r="O28" s="22" t="n">
-        <v>-18.1</v>
+        <v>-5.98</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>-0</v>
+        <v>0.63</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>-1.77</v>
+        <v>-1.06</v>
       </c>
       <c r="R28" s="24" t="n">
-        <v>92.8</v>
+        <v>68.5</v>
       </c>
       <c r="S28" s="24" t="n">
-        <v>97.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T28" s="21" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="U28" s="25" t="n">
-        <v>0.967</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V28" s="25" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="W28" s="21" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
+      </c>
+      <c r="W28" s="23" t="n">
+        <v>-0.44</v>
       </c>
       <c r="X28" s="24" t="n"/>
       <c r="Y28" s="24" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="Z28" s="19" t="n">
-        <v>10.07</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="29">
@@ -24320,69 +24326,221 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Samco Multi Cap Fund - Direct Plan - Growth</t>
+          <t>Franklin India Multi Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C29" s="28" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>-4.97</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
+        <v>34.4</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="J29" s="13" t="n"/>
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="10" t="n">
-        <v>-1.17</v>
+        <v>-0.06</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>-1.45</v>
+        <v>-0.09</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>10.6</v>
+        <v>15.21</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>-13.14</v>
+        <v>-18.68</v>
       </c>
       <c r="P29" s="10" t="n">
-        <v>-0.13</v>
+        <v>0.08</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>-1.09</v>
+        <v>-1.67</v>
       </c>
       <c r="R29" s="17" t="n">
-        <v>33.6</v>
+        <v>100.3</v>
       </c>
       <c r="S29" s="17" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="T29" s="13" t="n">
-        <v>-7.95</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>3.62</v>
       </c>
       <c r="U29" s="18" t="n">
-        <v>0.542</v>
+        <v>0.959</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="W29" s="13" t="n">
-        <v>-1.03</v>
+        <v>0.708</v>
+      </c>
+      <c r="W29" s="11" t="n">
+        <v>0.42</v>
       </c>
       <c r="X29" s="17" t="n"/>
       <c r="Y29" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z29" s="8" t="n">
+        <v>10.4452</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>PGIM India Multi Cap Fund - Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="22" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="O30" s="22" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="P30" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="R30" s="24" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="S30" s="24" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="T30" s="21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U30" s="25" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="V30" s="25" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="W30" s="21" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X30" s="24" t="n"/>
+      <c r="Y30" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Z30" s="19" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Samco Multi Cap Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="10" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="P31" s="10" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="Q31" s="10" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="R31" s="17" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="T31" s="13" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="U31" s="18" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="V31" s="18" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="W31" s="13" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="X31" s="17" t="n"/>
+      <c r="Y31" s="17" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z29" s="8" t="n">
+      <c r="Z31" s="8" t="n">
         <v>9.56</v>
       </c>
     </row>
@@ -27775,7 +27933,7 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Banking and PSU Fund-Direct Plan- Growth</t>
+          <t>Bajaj Finserv Banking and PSU Debt Fund-Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C42" s="27" t="n">
@@ -28181,7 +28339,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Banking and PSU Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Banking and PSU Debt Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C47" s="26" t="n">
@@ -29035,23 +29193,23 @@
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>Axis CRISIL-IBX AAA Bond Financial Services - Sep 2027 Index Fund - Direct Plan - Growth Option</t>
+          <t>Edelweiss CRISIL IBX AAA Financial Services - Jan 2028 Index Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C58" s="29" t="n">
         <v>48</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>6.85</v>
+        <v>6.87</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H58" s="23" t="n"/>
       <c r="I58" s="23" t="n"/>
@@ -29061,44 +29219,44 @@
         <v>3.55</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>7.61</v>
+        <v>6.14</v>
       </c>
       <c r="N58" s="22" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="O58" s="22" t="n">
         <v>-0.29</v>
       </c>
       <c r="P58" s="22" t="n">
-        <v>7.69</v>
+        <v>7.72</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="R58" s="24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="S58" s="24" t="n">
-        <v>-10.6</v>
+        <v>-12.4</v>
       </c>
       <c r="T58" s="21" t="n">
-        <v>9.81</v>
+        <v>10.1</v>
       </c>
       <c r="U58" s="25" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="V58" s="25" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="W58" s="21" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="X58" s="24" t="n"/>
       <c r="Y58" s="24" t="n">
         <v>0.7</v>
       </c>
       <c r="Z58" s="19" t="n">
-        <v>10.6941</v>
+        <v>10.691</v>
       </c>
     </row>
     <row r="59">
@@ -29107,23 +29265,23 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Edelweiss CRISIL IBX AAA Financial Services - Jan 2028 Index Fund - Direct - Growth</t>
+          <t>Axis CRISIL-IBX AAA Bond Financial Services - Sep 2027 Index Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C59" s="28" t="n">
         <v>48</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H59" s="13" t="n"/>
       <c r="I59" s="13" t="n"/>
@@ -29133,44 +29291,44 @@
         <v>3.55</v>
       </c>
       <c r="M59" s="10" t="n">
-        <v>6.14</v>
+        <v>7.61</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="O59" s="10" t="n">
         <v>-0.29</v>
       </c>
       <c r="P59" s="10" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="Q59" s="10" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="R59" s="17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S59" s="17" t="n">
-        <v>-12.4</v>
+        <v>-10.6</v>
       </c>
       <c r="T59" s="11" t="n">
-        <v>10.1</v>
+        <v>9.81</v>
       </c>
       <c r="U59" s="18" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="W59" s="11" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="X59" s="17" t="n"/>
       <c r="Y59" s="17" t="n">
         <v>0.7</v>
       </c>
       <c r="Z59" s="8" t="n">
-        <v>10.691</v>
+        <v>10.6941</v>
       </c>
     </row>
     <row r="60">
@@ -42145,7 +42303,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Balanced Advantage Fund ( Formerly Known as Principal Balanced Advantage Fund) - Direct Plan - Growth Option</t>
+          <t>Sundaram Dynamic Asset Allocation Fund Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -51237,7 +51395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z39"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -51489,7 +51647,7 @@
         <v>-13.7</v>
       </c>
       <c r="T3" s="11" t="n">
-        <v>8427847910015000</v>
+        <v>8427847910015416</v>
       </c>
       <c r="U3" s="18" t="n">
         <v>11.604</v>
@@ -52008,80 +52166,80 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Nippon India Ultra Short Duration Fund- Direct Plan- Growth Option</t>
+          <t>SBI ULTRA SHORT DURATION FUND - DIRECT PLAN - GROWTH</t>
         </is>
       </c>
       <c r="C10" s="27" t="n">
-        <v>62.9</v>
+        <v>62.6</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>8.02</v>
+        <v>7.62</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>7.67</v>
+        <v>7.31</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>4.71</v>
+        <v>6.74</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>7.88</v>
+        <v>7.52</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>7.57</v>
+        <v>6.75</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>6.26</v>
+        <v>7.13</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>6.51</v>
+        <v>6.87</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>4.32</v>
+        <v>3.33</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>9.24</v>
+        <v>6.69</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>-5.24</v>
+        <v>-0.95</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>1.46</v>
+        <v>7.69</v>
       </c>
       <c r="Q10" s="22" t="n">
         <v>0.01</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S10" s="24" t="n">
-        <v>-10</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>8.01</v>
+        <v>7.6</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="V10" s="25" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="W10" s="23" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="X10" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y10" s="24" t="n">
-        <v>7.3</v>
+        <v>12.6</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>4488.7441</v>
+        <v>6140.166</v>
       </c>
     </row>
     <row r="11">
@@ -52090,80 +52248,80 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SBI ULTRA SHORT DURATION FUND - DIRECT PLAN - GROWTH</t>
+          <t>Axis Ultra Short Duration Fund - Direct Plan Growth</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>7.62</v>
+        <v>7.93</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>7.31</v>
+        <v>7.58</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>5.9</v>
+        <v>6.29</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>6.74</v>
+        <v>4.66</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>7.52</v>
+        <v>7.78</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>6.75</v>
+        <v>7.06</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>7.13</v>
+        <v>6.5</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>6.87</v>
+        <v>5.97</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>3.33</v>
+        <v>4.03</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>6.69</v>
+        <v>10.3</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>-0.95</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>7.69</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q11" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>7.6</v>
+        <v>7.89</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="W11" s="13" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="X11" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y11" s="17" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>6140.166</v>
+        <v>15.7895</v>
       </c>
     </row>
     <row r="12">
@@ -52172,80 +52330,80 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Axis Ultra Short Duration Fund - Direct Plan Growth</t>
+          <t>BANK OF INDIA Ultra Short Duration Fund- Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C12" s="27" t="n">
-        <v>62.2</v>
+        <v>61.7</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>7.93</v>
+        <v>7.42</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>7.58</v>
+        <v>6.94</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>6.29</v>
+        <v>5.59</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>4.66</v>
+        <v>6.77</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>7.78</v>
+        <v>7.15</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>7.06</v>
+        <v>6.42</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>6.5</v>
+        <v>7.26</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>5.97</v>
+        <v>7.03</v>
       </c>
       <c r="L12" s="22" t="n">
-        <v>4.03</v>
+        <v>2.35</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>10.3</v>
+        <v>6.14</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="O12" s="22" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>9.359999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q12" s="22" t="n">
         <v>0.01</v>
       </c>
       <c r="R12" s="24" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S12" s="24" t="n">
-        <v>-9.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T12" s="21" t="n">
-        <v>7.89</v>
+        <v>7.25</v>
       </c>
       <c r="U12" s="25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V12" s="25" t="n">
         <v>0.002</v>
       </c>
-      <c r="V12" s="25" t="n">
-        <v>0.005</v>
-      </c>
       <c r="W12" s="23" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="X12" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y12" s="24" t="n">
-        <v>6.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z12" s="19" t="n">
-        <v>15.7895</v>
+        <v>3302.6183</v>
       </c>
     </row>
     <row r="13">
@@ -52254,50 +52412,50 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Baroda BNP Paribas Ultra Short Duration Fund- Direct Plan- Growth</t>
+          <t>Mahindra Manulife Ultra Short Duration Fund - Direct Plan -Growth</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>61.8</v>
+        <v>61.4</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>7.7</v>
+        <v>7.76</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7.45</v>
+        <v>7.44</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6.09</v>
+        <v>6.03</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>4.66</v>
+        <v>3.59</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>7.59</v>
+        <v>7.63</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>11.74</v>
+        <v>12.44</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>0.34</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>7.45</v>
+        <v>14.88</v>
       </c>
       <c r="Q13" s="10" t="n">
         <v>0.01</v>
@@ -52306,7 +52464,7 @@
         <v>2.5</v>
       </c>
       <c r="S13" s="17" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="T13" s="11" t="n">
         <v>7.77</v>
@@ -52315,7 +52473,7 @@
         <v>0.002</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="W13" s="13" t="n">
         <v>-0.38</v>
@@ -52324,10 +52482,10 @@
         <v>100</v>
       </c>
       <c r="Y13" s="17" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>1577.9903</v>
+        <v>1423.423</v>
       </c>
     </row>
     <row r="14">
@@ -52336,80 +52494,80 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>BANK OF INDIA Ultra Short Duration Fund- Direct Plan- Growth</t>
+          <t>HSBC Ultra Short Duration Fund - Direct Growth</t>
         </is>
       </c>
       <c r="C14" s="27" t="n">
-        <v>61.7</v>
+        <v>61.2</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>7.42</v>
+        <v>7.69</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>6.94</v>
+        <v>7.38</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>6.77</v>
+        <v>3.32</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>7.15</v>
+        <v>7.57</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>6.42</v>
+        <v>6.83</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>7.26</v>
+        <v>5.85</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>7.03</v>
+        <v>5.83</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>2.35</v>
+        <v>3.62</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>6.14</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>-0.76</v>
+        <v>-0.96</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>9.130000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="Q14" s="22" t="n">
         <v>0.01</v>
       </c>
       <c r="R14" s="24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S14" s="24" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T14" s="21" t="n">
-        <v>7.25</v>
+        <v>7.7</v>
       </c>
       <c r="U14" s="25" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V14" s="25" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="W14" s="23" t="n">
-        <v>-0.42</v>
+        <v>-0.39</v>
       </c>
       <c r="X14" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y14" s="24" t="n">
-        <v>12.6</v>
+        <v>5.6</v>
       </c>
       <c r="Z14" s="19" t="n">
-        <v>3302.6183</v>
+        <v>1386.5435</v>
       </c>
     </row>
     <row r="15">
@@ -52418,80 +52576,80 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Ultra Short Duration Fund - Direct Plan - Growth</t>
+          <t>UTI Short Duration Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>61.5</v>
+        <v>59.7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>7.9</v>
+        <v>8.66</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>7.51</v>
+        <v>7.99</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>5.96</v>
+        <v>7.67</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>2.94</v>
+        <v>6.9</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>7.76</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>7.04</v>
+        <v>7.85</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>6.19</v>
+        <v>7.43</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>6.29</v>
+        <v>7.02</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>4.06</v>
+        <v>2.47</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>12.87</v>
+        <v>3.56</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>-0.16</v>
+        <v>-13.16</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>46.94</v>
+        <v>0.61</v>
       </c>
       <c r="Q15" s="10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" s="17" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="T15" s="11" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="U15" s="18" t="n">
         <v>0.01</v>
       </c>
-      <c r="R15" s="17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S15" s="17" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="T15" s="11" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="U15" s="18" t="n">
-        <v>0.002</v>
-      </c>
       <c r="V15" s="18" t="n">
-        <v>0.005</v>
+        <v>0.027</v>
       </c>
       <c r="W15" s="13" t="n">
-        <v>-0.38</v>
+        <v>-0.34</v>
       </c>
       <c r="X15" s="17" t="n">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Y15" s="17" t="n">
-        <v>4.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>1335.9388</v>
+        <v>34.0857</v>
       </c>
     </row>
     <row r="16">
@@ -52500,162 +52658,160 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Ultra Short Duration Fund - Direct Plan -Growth</t>
+          <t>Bandhan Short Duration Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C16" s="27" t="n">
-        <v>61.4</v>
+        <v>59.6</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>7.76</v>
+        <v>8.66</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>7.44</v>
+        <v>7.75</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>6.03</v>
+        <v>6.28</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>3.59</v>
+        <v>7.49</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>7.63</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>6.88</v>
+        <v>7.18</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>5.95</v>
+        <v>7.89</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>5.78</v>
+        <v>7.61</v>
       </c>
       <c r="L16" s="22" t="n">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>12.44</v>
+        <v>2.2</v>
       </c>
       <c r="N16" s="22" t="n">
-        <v>0.34</v>
+        <v>1.04</v>
       </c>
       <c r="O16" s="22" t="n">
-        <v>-0.5</v>
+        <v>-2.55</v>
       </c>
       <c r="P16" s="22" t="n">
-        <v>14.88</v>
+        <v>3.04</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R16" s="24" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="S16" s="24" t="n">
-        <v>-9.800000000000001</v>
+        <v>-6.6</v>
       </c>
       <c r="T16" s="21" t="n">
-        <v>7.77</v>
+        <v>7.85</v>
       </c>
       <c r="U16" s="25" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="V16" s="25" t="n">
-        <v>0.004</v>
+        <v>0.05</v>
       </c>
       <c r="W16" s="23" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="X16" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y16" s="24" t="n">
-        <v>5.8</v>
+        <v>12.6</v>
       </c>
       <c r="Z16" s="19" t="n">
-        <v>1423.423</v>
+        <v>61.7129</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Short Duration Fund - Direct Plan - Growth</t>
+          <t>Mahindra Manulife Short Duration Fund - Direct Plan -Growth</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>61.4</v>
+        <v>59.5</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>8.91</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7.86</v>
+        <v>8.02</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6.48</v>
+        <v>6.07</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>5.33</v>
+        <v>2.99</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>8.390000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>7.32</v>
+        <v>7.69</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>6.51</v>
-      </c>
+        <v>6.63</v>
+      </c>
+      <c r="K17" s="13" t="n"/>
       <c r="L17" s="10" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>-2.2</v>
+        <v>-1.1</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>3.57</v>
+        <v>7.29</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R17" s="17" t="n">
         <v>3.2</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>-7.8</v>
+        <v>-8</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>8.07</v>
+        <v>8.23</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="X17" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>16.8568</v>
+        <v>13.4328</v>
       </c>
     </row>
     <row r="18">
@@ -52664,80 +52820,78 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>BANDHAN ULTRA SHORT DURATION FUND - DIRECT PLAN GROWTH</t>
+          <t>Sundaram Short Duration Fund (Formerly Known as Principal Short Term Debt Fund)- Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>61.3</v>
+        <v>59</v>
       </c>
       <c r="D18" s="21" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" s="21" t="n">
         <v>7.6</v>
       </c>
-      <c r="E18" s="21" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>5.56</v>
-      </c>
+      <c r="K18" s="23" t="n"/>
       <c r="L18" s="22" t="n">
-        <v>3.23</v>
+        <v>2.18</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>6.33</v>
+        <v>3.12</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>0.34</v>
+        <v>0.82</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>-0.89</v>
+        <v>-0.67</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>8.18</v>
+        <v>11.79</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>-9.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>7.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.004</v>
+        <v>0.036</v>
       </c>
       <c r="W18" s="23" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="X18" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>15.5569</v>
+        <v>48.3358</v>
       </c>
     </row>
     <row r="19">
@@ -52746,80 +52900,80 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSBC Ultra Short Duration Fund - Direct Growth</t>
+          <t>CANARA ROBECO SHORT DURATION FUND - DIRECT PLAN - GROWTH OPTION</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>61.2</v>
+        <v>58.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>7.69</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>7.38</v>
+        <v>7.29</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5.98</v>
+        <v>5.95</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>3.32</v>
+        <v>7.25</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>7.57</v>
+        <v>7.74</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>5.85</v>
+        <v>7.34</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>5.83</v>
+        <v>7.18</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>3.62</v>
+        <v>1.51</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>9.720000000000001</v>
+        <v>2.15</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>-0.96</v>
+        <v>-2.15</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>7.69</v>
+        <v>3.39</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R19" s="17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.2</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>7.7</v>
+        <v>7.46</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>0.004</v>
+        <v>0.046</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="X19" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y19" s="17" t="n">
-        <v>5.6</v>
+        <v>12.6</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>1386.5435</v>
+        <v>27.9368</v>
       </c>
     </row>
     <row r="20">
@@ -52828,80 +52982,78 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>WhiteOak Capital Ultra Short Duration Fund- Direct plan-Growth Option</t>
+          <t>Edelweiss CRISIL IBX 50:50 Gilt Plus SDL Short Duration Index fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>60.9</v>
+        <v>58.4</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>7.48</v>
+        <v>8.09</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>7.16</v>
+        <v>6.75</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>6.04</v>
+        <v>4</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>3.58</v>
+        <v>1.98</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>7.34</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>6.67</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="K20" s="21" t="n">
-        <v>5.46</v>
-      </c>
+        <v>8.31</v>
+      </c>
+      <c r="K20" s="23" t="n"/>
       <c r="L20" s="22" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>9.960000000000001</v>
+        <v>3.37</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>-0.16</v>
+        <v>-0.43</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>44.75</v>
+        <v>15.7</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R20" s="24" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="S20" s="24" t="n">
-        <v>-9.5</v>
+        <v>-9.1</v>
       </c>
       <c r="T20" s="21" t="n">
-        <v>7.48</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="U20" s="25" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="V20" s="25" t="n">
-        <v>0.003</v>
+        <v>0.021</v>
       </c>
       <c r="W20" s="23" t="n">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="X20" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y20" s="24" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z20" s="19" t="n">
-        <v>1423.2937</v>
+        <v>12.1865</v>
       </c>
     </row>
     <row r="21">
@@ -52910,80 +53062,78 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>LIC MF Short Duration Fund-Direct Plan-Growth</t>
+          <t>HSBC Short Duration Fund - Direct Growth</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>60.3</v>
+        <v>58.1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>7.76</v>
+        <v>7.19</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6.15</v>
+        <v>4.26</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>4.63</v>
+        <v>2.11</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>8.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>7.11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>5.71</v>
-      </c>
+        <v>8.039999999999999</v>
+      </c>
+      <c r="K21" s="13" t="n"/>
       <c r="L21" s="10" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="O21" s="10" t="n">
-        <v>-2.28</v>
+        <v>-0.48</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>3.4</v>
+        <v>14.98</v>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="R21" s="17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S21" s="17" t="n">
-        <v>-7.5</v>
+        <v>-8</v>
       </c>
       <c r="T21" s="11" t="n">
-        <v>7.94</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="U21" s="18" t="n">
         <v>0.014</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>-0.36</v>
+        <v>-0.27</v>
       </c>
       <c r="X21" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y21" s="17" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>15.7098</v>
+        <v>28.3353</v>
       </c>
     </row>
     <row r="22">
@@ -52992,80 +53142,74 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>LIC MF Ultra Short Duration Fund-Direct Plan-Growth</t>
+          <t>Nippon India Ultra Short Duration Fund - Segregated Portfolio 1 - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C22" s="27" t="n">
-        <v>60.2</v>
+        <v>57.9</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>7.67</v>
+        <v>195.09</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>7</v>
+        <v>30.74</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>5.62</v>
+        <v>17.45</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>3.14</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>7.35</v>
+        <v>236.88</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>5.27</v>
-      </c>
+        <v>236.88</v>
+      </c>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
       <c r="L22" s="22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="M22" s="22" t="n">
-        <v>6.74</v>
-      </c>
+        <v>1.65</v>
+      </c>
+      <c r="M22" s="22" t="n"/>
       <c r="N22" s="22" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O22" s="22" t="n">
-        <v>-1.31</v>
+        <v>224.83</v>
+      </c>
+      <c r="O22" s="23" t="n">
+        <v>-38.82</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>5.34</v>
+        <v>0.79</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R22" s="24" t="n">
-        <v>2.3</v>
+        <v>-3.9</v>
       </c>
       <c r="S22" s="24" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9194.799999999999</v>
       </c>
       <c r="T22" s="21" t="n">
-        <v>7.31</v>
+        <v>409.94</v>
       </c>
       <c r="U22" s="25" t="n">
-        <v>0.002</v>
+        <v>-0.289</v>
       </c>
       <c r="V22" s="25" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="W22" s="23" t="n">
-        <v>-0.42</v>
+        <v>0.001</v>
+      </c>
+      <c r="W22" s="21" t="n">
+        <v>0.59</v>
       </c>
       <c r="X22" s="24" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="24" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" s="19" t="n">
-        <v>1363.6699</v>
+        <v>101.752</v>
       </c>
     </row>
     <row r="23">
@@ -53074,148 +53218,148 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>UTI Short Duration Fund - Direct Plan - Growth Option</t>
+          <t>PGIM India Ultra Short Duration Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>8.66</v>
+        <v>7.6</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>7.99</v>
+        <v>7.29</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7.67</v>
+        <v>5.98</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>6.9</v>
+        <v>7.03</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>8.289999999999999</v>
+        <v>7.47</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>7.85</v>
+        <v>6.77</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>7.43</v>
+        <v>7.4</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>7.02</v>
+        <v>7.29</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>2.47</v>
+        <v>3.39</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>3.56</v>
+        <v>12.42</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="O23" s="10" t="n">
-        <v>-13.16</v>
+        <v>0.34</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>-30.29</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R23" s="17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S23" s="17" t="n">
-        <v>-8.9</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>8.24</v>
+        <v>7.62</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="W23" s="13" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>91.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="Y23" s="17" t="n">
-        <v>12.6</v>
+        <v>9.5</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>34.0857</v>
+        <v>35.9771</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Sundaram Ultra Short Duration Fund (Formerly Known as Principal Ultra Short Term Fund)- Direct Plan -Growth Option</t>
+          <t>TRUSTMF Short Duration Fund-Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C24" s="27" t="n">
-        <v>59.7</v>
+        <v>56.1</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>7.79</v>
+        <v>8.73</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>7.46</v>
+        <v>7.54</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>7.65</v>
+        <v>8.1</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>7.49</v>
+        <v>7.53</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>7.22</v>
+        <v>6.61</v>
       </c>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="22" t="n">
-        <v>3.9</v>
+        <v>1.66</v>
       </c>
       <c r="M24" s="22" t="n">
-        <v>16.62</v>
+        <v>2.43</v>
       </c>
       <c r="N24" s="22" t="n">
-        <v>0.34</v>
+        <v>0.84</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>-0.16</v>
+        <v>-1.07</v>
       </c>
       <c r="P24" s="22" t="n">
-        <v>46.62</v>
+        <v>7.05</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R24" s="24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="S24" s="24" t="n">
-        <v>-9.800000000000001</v>
+        <v>-7.1</v>
       </c>
       <c r="T24" s="21" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="U24" s="25" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="V24" s="25" t="n">
-        <v>0.004</v>
+        <v>0.048</v>
       </c>
       <c r="W24" s="23" t="n">
         <v>-0.38</v>
@@ -53224,10 +53368,10 @@
         <v>100</v>
       </c>
       <c r="Y24" s="24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Z24" s="19" t="n">
-        <v>2958.95</v>
+        <v>1289.2273</v>
       </c>
     </row>
     <row r="25">
@@ -53236,80 +53380,74 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Bandhan Short Duration Fund - Direct Plan - Growth</t>
+          <t>Franklin India Ultra Short Duration Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
-        <v>59.6</v>
+        <v>50.7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>8.66</v>
+        <v>7.84</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>7.75</v>
+        <v>2.55</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6.28</v>
+        <v>1.52</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>7.49</v>
+        <v>0.76</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>7.61</v>
-      </c>
+        <v>7.87</v>
+      </c>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="n"/>
       <c r="L25" s="10" t="n">
-        <v>1.52</v>
+        <v>4.47</v>
       </c>
       <c r="M25" s="10" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="17" t="n">
         <v>2.2</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="P25" s="10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="R25" s="17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="S25" s="17" t="n">
-        <v>-6.6</v>
+        <v>-11</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>7.85</v>
+        <v>8.43</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W25" s="13" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="X25" s="17" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W25" s="11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="X25" s="17" t="n"/>
       <c r="Y25" s="17" t="n">
-        <v>12.6</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>61.7129</v>
+        <v>10.7836</v>
       </c>
     </row>
     <row r="26">
@@ -53318,78 +53456,80 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Short Duration Fund - Direct Plan -Growth</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>59.5</v>
+          <t>JM Ultra Short Duration Fund - (Direct) - Growth Option</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>45</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>8.91</v>
+        <v>5.85</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>8.02</v>
+        <v>4.76</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>6.07</v>
+        <v>6.26</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>2.99</v>
+        <v>5.63</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>8.550000000000001</v>
+        <v>4.77</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>7.69</v>
+        <v>5.35</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="K26" s="23" t="n"/>
+        <v>7.01</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>7.49</v>
+      </c>
       <c r="L26" s="22" t="n">
-        <v>2.29</v>
+        <v>-0.36</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>3.07</v>
+        <v>-0.13</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>0.83</v>
+        <v>4.1</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>-1.1</v>
+        <v>-5.5</v>
       </c>
       <c r="P26" s="22" t="n">
-        <v>7.29</v>
+        <v>0.87</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="R26" s="24" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="S26" s="24" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T26" s="21" t="n">
-        <v>8.23</v>
+        <v>4.99</v>
       </c>
       <c r="U26" s="25" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="V26" s="25" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="W26" s="23" t="n">
-        <v>-0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="X26" s="24" t="n">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="Y26" s="24" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="Z26" s="19" t="n">
-        <v>13.4328</v>
+        <v>27.5938</v>
       </c>
     </row>
     <row r="27">
@@ -53398,78 +53538,80 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Short Duration Fund (Formerly Known as Principal Short Term Debt Fund)- Direct Plan - Growth Option</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="n">
-        <v>59</v>
+          <t>HSBC Short Duration Fund - Direct Growth</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>40.9</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>8.75</v>
+        <v>3.01</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>7.9</v>
+        <v>4.51</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5.08</v>
+        <v>4.05</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>2.51</v>
+        <v>6.35</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>8.27</v>
+        <v>4.28</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>8</v>
+        <v>4.06</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K27" s="13" t="n"/>
+        <v>6.54</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>6.36</v>
+      </c>
       <c r="L27" s="10" t="n">
-        <v>2.18</v>
+        <v>-0.2</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>3.12</v>
+        <v>-0.15</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>0.82</v>
+        <v>7.46</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>-0.67</v>
+        <v>-10.15</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>11.79</v>
+        <v>0.44</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="R27" s="17" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2.8</v>
       </c>
       <c r="T27" s="11" t="n">
-        <v>8.119999999999999</v>
+        <v>4.71</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="W27" s="13" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="X27" s="17" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Y27" s="17" t="n">
-        <v>3.6</v>
+        <v>9.9</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>48.3358</v>
+        <v>35.6582</v>
       </c>
     </row>
     <row r="28">
@@ -53478,951 +53620,79 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>CANARA ROBECO SHORT DURATION FUND - DIRECT PLAN - GROWTH OPTION</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="n">
-        <v>58.5</v>
+          <t>PGIM India Short Duration Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>33.9</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>8.109999999999999</v>
+        <v>6.73</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>7.29</v>
+        <v>4.94</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>5.95</v>
+        <v>4.77</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>7.25</v>
+        <v>4.48</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>7.74</v>
+        <v>5.21</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>6.74</v>
+        <v>5.21</v>
       </c>
       <c r="J28" s="21" t="n">
-        <v>7.34</v>
+        <v>5.59</v>
       </c>
       <c r="K28" s="21" t="n">
-        <v>7.18</v>
+        <v>5.05</v>
       </c>
       <c r="L28" s="22" t="n">
-        <v>1.51</v>
+        <v>-1.69</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>2.15</v>
+        <v>-1.93</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O28" s="22" t="n">
-        <v>-2.15</v>
+        <v>0.8</v>
+      </c>
+      <c r="O28" s="23" t="n">
+        <v>-36.31</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>3.39</v>
+        <v>0.14</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R28" s="24" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="S28" s="24" t="n">
-        <v>-7.2</v>
+        <v>-4.2</v>
       </c>
       <c r="T28" s="21" t="n">
-        <v>7.46</v>
+        <v>5.04</v>
       </c>
       <c r="U28" s="25" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="V28" s="25" t="n">
-        <v>0.046</v>
+        <v>0.007</v>
       </c>
       <c r="W28" s="23" t="n">
-        <v>-0.4</v>
+        <v>-1.05</v>
       </c>
       <c r="X28" s="24" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="Y28" s="24" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z28" s="19" t="n">
-        <v>27.9368</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Edelweiss CRISIL IBX 50:50 Gilt Plus SDL Short Duration Index fund - Direct Plan - Growth</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="P29" s="10" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="Q29" s="10" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="R29" s="17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S29" s="17" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="T29" s="11" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="U29" s="18" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="V29" s="18" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="W29" s="13" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="X29" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y29" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z29" s="8" t="n">
-        <v>12.1865</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>HSBC Short Duration Fund - Direct Growth</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="F30" s="21" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I30" s="21" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J30" s="21" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="K30" s="23" t="n"/>
-      <c r="L30" s="22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M30" s="22" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N30" s="22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="O30" s="22" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="P30" s="22" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="Q30" s="22" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="R30" s="24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S30" s="24" t="n">
-        <v>-8</v>
-      </c>
-      <c r="T30" s="21" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="U30" s="25" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="V30" s="25" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="W30" s="23" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="X30" s="24" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y30" s="24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z30" s="19" t="n">
-        <v>28.3353</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Nippon India Ultra Short Duration Fund - Segregated Portfolio 1 - Direct Plan - Growth Option</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>195.09</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="H31" s="11" t="n">
-        <v>236.88</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>236.88</v>
-      </c>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M31" s="10" t="n"/>
-      <c r="N31" s="10" t="n">
-        <v>224.83</v>
-      </c>
-      <c r="O31" s="13" t="n">
-        <v>-38.82</v>
-      </c>
-      <c r="P31" s="10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Q31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="17" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="S31" s="17" t="n">
-        <v>-9194.799999999999</v>
-      </c>
-      <c r="T31" s="11" t="n">
-        <v>409.94</v>
-      </c>
-      <c r="U31" s="18" t="n">
-        <v>-0.289</v>
-      </c>
-      <c r="V31" s="18" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="W31" s="11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="X31" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y31" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" s="8" t="n">
-        <v>101.752</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>PGIM India Ultra Short Duration Fund - Direct Plan - Growth</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="D32" s="21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="H32" s="21" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="I32" s="21" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="J32" s="21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K32" s="21" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="L32" s="22" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="M32" s="22" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="N32" s="22" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="O32" s="23" t="n">
-        <v>-30.29</v>
-      </c>
-      <c r="P32" s="22" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Q32" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R32" s="24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S32" s="24" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="T32" s="21" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="U32" s="25" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V32" s="25" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="W32" s="23" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="X32" s="24" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="Y32" s="24" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z32" s="19" t="n">
-        <v>35.9771</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>JM Short Duration Fund (Direct) - Growth</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H33" s="11" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M33" s="10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N33" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="O33" s="10" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="P33" s="10" t="n">
-        <v>14.06</v>
-      </c>
-      <c r="Q33" s="10" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="R33" s="17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S33" s="17" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="T33" s="11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="U33" s="18" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="V33" s="18" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="W33" s="13" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="X33" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y33" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="8" t="n">
-        <v>12.4262</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>TRUSTMF Short Duration Fund-Direct Plan-Growth</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="D34" s="21" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="E34" s="21" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G34" s="21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="H34" s="21" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I34" s="21" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="J34" s="21" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="K34" s="23" t="n"/>
-      <c r="L34" s="22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M34" s="22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="N34" s="22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="O34" s="22" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="P34" s="22" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="Q34" s="22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="R34" s="24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S34" s="24" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="T34" s="21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="U34" s="25" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="V34" s="25" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="W34" s="23" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="X34" s="24" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y34" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z34" s="19" t="n">
-        <v>1289.2273</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Franklin India Ultra Short Duration Fund - Direct - Growth</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H35" s="11" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="10" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="M35" s="10" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="N35" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O35" s="10" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="P35" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S35" s="17" t="n">
-        <v>-11</v>
-      </c>
-      <c r="T35" s="11" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="U35" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="11" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="X35" s="17" t="n"/>
-      <c r="Y35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="8" t="n">
-        <v>10.7836</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>Union Short Duration Fund - Direct Plan - Growth Option</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="D36" s="21" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E36" s="21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="F36" s="21" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="23" t="n"/>
-      <c r="J36" s="23" t="n"/>
-      <c r="K36" s="23" t="n"/>
-      <c r="L36" s="22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M36" s="22" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="N36" s="22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="O36" s="22" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="P36" s="22" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="Q36" s="22" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="R36" s="24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S36" s="24" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="T36" s="21" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="U36" s="25" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="V36" s="25" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="W36" s="23" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="X36" s="24" t="n"/>
-      <c r="Y36" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z36" s="19" t="n">
-        <v>10.5023</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>JM Ultra Short Duration Fund - (Direct) - Growth Option</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="n">
-        <v>45</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="G37" s="11" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="H37" s="11" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L37" s="10" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="N37" s="10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O37" s="10" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="P37" s="10" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="R37" s="17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S37" s="17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="T37" s="11" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="U37" s="18" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V37" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="13" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="X37" s="17" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="Y37" s="17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Z37" s="8" t="n">
-        <v>27.5938</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>HSBC Short Duration Fund - Direct Growth</t>
-        </is>
-      </c>
-      <c r="C38" s="29" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="D38" s="21" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="E38" s="21" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="H38" s="21" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="I38" s="21" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="J38" s="21" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="K38" s="21" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="L38" s="22" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M38" s="22" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="N38" s="22" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="O38" s="22" t="n">
-        <v>-10.15</v>
-      </c>
-      <c r="P38" s="22" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Q38" s="22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="R38" s="24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S38" s="24" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="T38" s="21" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="U38" s="25" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="V38" s="25" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="W38" s="23" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X38" s="24" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Y38" s="24" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="Z38" s="19" t="n">
-        <v>35.6582</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>PGIM India Short Duration Fund - Direct Plan - Growth</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="G39" s="11" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="H39" s="11" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="K39" s="11" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="L39" s="10" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="M39" s="10" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="N39" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O39" s="13" t="n">
-        <v>-36.31</v>
-      </c>
-      <c r="P39" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Q39" s="10" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="R39" s="17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S39" s="17" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="T39" s="11" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="U39" s="18" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V39" s="18" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="W39" s="13" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="X39" s="17" t="n">
-        <v>93</v>
-      </c>
-      <c r="Y39" s="17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z39" s="8" t="n">
         <v>42.8534</v>
       </c>
     </row>
@@ -57661,7 +56931,7 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>NJ ELSS Tax Saver Scheme Direct Growth</t>
+          <t>NJ ELSS Tax Saver Fund Direct Growth</t>
         </is>
       </c>
       <c r="C40" s="27" t="n">
@@ -58225,7 +57495,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>BAJAJ FINSERV ELSS TAX SAVER FUND - DIRECT - GROWTH</t>
+          <t>BAJAJ FINSERV ELSS - TAX SAVER FUND - DIRECT - GROWTH</t>
         </is>
       </c>
       <c r="C47" s="28" t="n">
@@ -59810,7 +59080,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ICICI Prudential Flexicap Fund - Direct Plan - Growth</t>
+          <t>ICICI Prudential Flexi Cap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 31 Aug 2026 21:57</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 01 Sep 2026 20:00</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 01 Sep 2026 20:00</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 02 Sep 2026 19:55</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 02 Sep 2026 19:55</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 03 Sep 2026 19:58</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 03 Sep 2026 19:58</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 04 Sep 2026 19:43</t>
         </is>
       </c>
     </row>
@@ -1573,26 +1573,26 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>HDFC Flexi Cap Fund - Growth Option - Direct Plan</t>
+          <t>Edelweiss Flexi Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
         <v>82.7</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>23.56</v>
+        <v>20.36</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>28.09</v>
+        <v>23.35</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-41.84</v>
+        <v>-36.1</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>11.74</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="49">
@@ -1601,26 +1601,26 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Edelweiss Flexi Cap Fund - Direct Plan - Growth Option</t>
+          <t>HDFC Flexi Cap Fund - Growth Option - Direct Plan</t>
         </is>
       </c>
       <c r="C49" s="9" t="n">
         <v>82.7</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>20.36</v>
+        <v>23.56</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>23.35</v>
+        <v>28.09</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>-36.1</v>
+        <v>-41.84</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>6.6</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="50">
@@ -7725,80 +7725,80 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>ICICI Prudential Global Stable Equity Fund (FOF) - Direct - Growth</t>
+          <t>HSBC Global Consumer Opportunities Fund - Growth Direct</t>
         </is>
       </c>
       <c r="C18" s="27" t="n">
         <v>58.9</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>12.6</v>
+        <v>35.26</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>12.26</v>
+        <v>11.88</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>12.14</v>
+        <v>15.49</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>10.05</v>
+        <v>6.68</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>13.77</v>
+        <v>19.03</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>11.95</v>
+        <v>16.17</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>9.92</v>
+        <v>11.69</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>9.34</v>
+        <v>11.25</v>
       </c>
       <c r="L18" s="22" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>0.91</v>
+        <v>0.59</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>12.62</v>
+        <v>18.12</v>
       </c>
       <c r="O18" s="23" t="n">
-        <v>-26.16</v>
+        <v>-28.74</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>-1.17</v>
+        <v>-1.76</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>43.5</v>
+        <v>59.9</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>10.32</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.318</v>
+        <v>0.402</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.099</v>
+        <v>0.242</v>
       </c>
       <c r="W18" s="21" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="X18" s="24" t="n">
-        <v>95.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>11.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>31.28</v>
+        <v>19.0214</v>
       </c>
     </row>
     <row r="19">
@@ -7807,80 +7807,80 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSBC Global Consumer Opportunities Fund - Growth Direct</t>
+          <t>ICICI Prudential Global Stable Equity Fund (FOF) - Direct - Growth</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
         <v>58.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>35.26</v>
+        <v>12.6</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>11.88</v>
+        <v>12.26</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>15.49</v>
+        <v>12.14</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>6.68</v>
+        <v>10.05</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>19.03</v>
+        <v>13.77</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>16.17</v>
+        <v>11.95</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>11.69</v>
+        <v>9.92</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>11.25</v>
+        <v>9.34</v>
       </c>
       <c r="L19" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>-26.16</v>
+      </c>
+      <c r="P19" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="M19" s="10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="O19" s="13" t="n">
-        <v>-28.74</v>
-      </c>
-      <c r="P19" s="10" t="n">
-        <v>0.41</v>
-      </c>
       <c r="Q19" s="10" t="n">
-        <v>-1.76</v>
+        <v>-1.17</v>
       </c>
       <c r="R19" s="17" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>59.9</v>
+        <v>43.5</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>8.869999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>0.402</v>
+        <v>0.318</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>0.242</v>
+        <v>0.099</v>
       </c>
       <c r="W19" s="11" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="X19" s="17" t="n">
-        <v>78.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Y19" s="17" t="n">
-        <v>6.2</v>
+        <v>11.9</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>19.0214</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="20">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Kotak Global Innovation Overseas Equity Active FOF- Direct Plan -Growth</t>
+          <t>Kotak Global Innovation Overseas Equity Omni FOF- Direct Plan -Growth</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -8783,78 +8783,78 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>PGIM India Global Select Real Estate Securities Fund of Fund - Direct Plan - Growth Option</t>
+          <t>HSBC Global Equity Climate Change Fund of Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C31" s="28" t="n">
         <v>40.1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>7.43</v>
+        <v>10.32</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>7.52</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>12.12</v>
+        <v>12.04</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>9.51</v>
+        <v>7.8</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>6.44</v>
+        <v>1.89</v>
       </c>
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="10" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>15.98</v>
+        <v>18.14</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>-27.4</v>
+        <v>-31.35</v>
       </c>
       <c r="P31" s="10" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="Q31" s="10" t="n">
-        <v>-1.62</v>
+        <v>-1.77</v>
       </c>
       <c r="R31" s="17" t="n">
-        <v>12.4</v>
+        <v>32.2</v>
       </c>
       <c r="S31" s="17" t="n">
-        <v>25</v>
+        <v>59.5</v>
       </c>
       <c r="T31" s="11" t="n">
-        <v>7.45</v>
+        <v>6.88</v>
       </c>
       <c r="U31" s="18" t="n">
-        <v>0.132</v>
+        <v>0.38</v>
       </c>
       <c r="V31" s="18" t="n">
-        <v>0.011</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W31" s="13" t="n">
-        <v>-0.24</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="X31" s="17" t="n">
-        <v>73.8</v>
+        <v>67.8</v>
       </c>
       <c r="Y31" s="17" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>11.56</v>
+        <v>11.5746</v>
       </c>
     </row>
     <row r="32">
@@ -8863,78 +8863,78 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>HSBC Global Equity Climate Change Fund of Fund - Direct - Growth</t>
+          <t>PGIM India Global Select Real Estate Securities Fund of Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C32" s="29" t="n">
         <v>40.1</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>10.32</v>
+        <v>7.43</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>9.369999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>12.04</v>
+        <v>12.12</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>7.8</v>
+        <v>9.51</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>1.89</v>
+        <v>6.44</v>
       </c>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="22" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>18.14</v>
+        <v>15.98</v>
       </c>
       <c r="O32" s="23" t="n">
-        <v>-31.35</v>
+        <v>-27.4</v>
       </c>
       <c r="P32" s="22" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>-1.77</v>
+        <v>-1.62</v>
       </c>
       <c r="R32" s="24" t="n">
-        <v>32.2</v>
+        <v>12.4</v>
       </c>
       <c r="S32" s="24" t="n">
-        <v>59.5</v>
+        <v>25</v>
       </c>
       <c r="T32" s="21" t="n">
-        <v>6.88</v>
+        <v>7.45</v>
       </c>
       <c r="U32" s="25" t="n">
-        <v>0.38</v>
+        <v>0.132</v>
       </c>
       <c r="V32" s="25" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="W32" s="23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="X32" s="24" t="n">
-        <v>67.8</v>
+        <v>73.8</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="Z32" s="19" t="n">
-        <v>11.5746</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="33">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Kotak International REIT Overseas Equity Active FOF - Direct Plan - Growth</t>
+          <t>Kotak International REIT Overseas Equity Omni FOF - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C33" s="28" t="n">
@@ -12378,78 +12378,80 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Growth Option - Direct Plan</t>
+          <t>Union Largecap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C34" s="27" t="n">
         <v>62.8</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>-5.01</v>
+        <v>0</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>15.99</v>
+        <v>13.64</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>9.210000000000001</v>
+        <v>17.59</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>4.51</v>
+        <v>9.57</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>14.81</v>
+        <v>12.66</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>14.8</v>
+        <v>13.66</v>
       </c>
       <c r="J34" s="21" t="n">
-        <v>24.87</v>
-      </c>
-      <c r="K34" s="23" t="n"/>
+        <v>13.6</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>14.06</v>
+      </c>
       <c r="L34" s="22" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="O34" s="22" t="n">
-        <v>-21.11</v>
+        <v>12.81</v>
+      </c>
+      <c r="O34" s="23" t="n">
+        <v>-36.39</v>
       </c>
       <c r="P34" s="22" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q34" s="22" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="R34" s="24" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="S34" s="24" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="T34" s="21" t="n">
         <v>0.76</v>
       </c>
-      <c r="Q34" s="22" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="R34" s="24" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="S34" s="24" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="T34" s="21" t="n">
-        <v>2.85</v>
-      </c>
       <c r="U34" s="25" t="n">
-        <v>1.013</v>
+        <v>0.985</v>
       </c>
       <c r="V34" s="25" t="n">
-        <v>0.713</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="W34" s="21" t="n">
-        <v>0.37</v>
+        <v>0.17</v>
       </c>
       <c r="X34" s="24" t="n">
-        <v>76.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Y34" s="24" t="n">
-        <v>3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z34" s="19" t="n">
-        <v>15.5551</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="35">
@@ -12458,80 +12460,78 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Union Largecap Fund - Direct Plan - Growth Option</t>
+          <t>quant Large Cap Fund - Growth Option - Direct Plan</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
         <v>62.8</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0</v>
+        <v>-5.01</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>13.64</v>
+        <v>15.99</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>17.59</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>9.57</v>
+        <v>4.51</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>12.66</v>
+        <v>14.81</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>13.66</v>
+        <v>14.8</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K35" s="11" t="n">
-        <v>14.06</v>
-      </c>
+        <v>24.87</v>
+      </c>
+      <c r="K35" s="13" t="n"/>
       <c r="L35" s="10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="O35" s="13" t="n">
-        <v>-36.39</v>
+        <v>15.09</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>-21.11</v>
       </c>
       <c r="P35" s="10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U35" s="18" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="V35" s="18" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="W35" s="11" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q35" s="10" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="R35" s="17" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="S35" s="17" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T35" s="11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="U35" s="18" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="V35" s="18" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="W35" s="11" t="n">
-        <v>0.17</v>
-      </c>
       <c r="X35" s="17" t="n">
-        <v>79.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Y35" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="8" t="n">
-        <v>24.98</v>
+        <v>15.5551</v>
       </c>
     </row>
     <row r="36">
@@ -12540,80 +12540,80 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Reliance Focused Large Cap Fund - Direct Plan Growth Plan - Bonus Option</t>
+          <t>Axis Large Cap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C36" s="27" t="n">
         <v>62.1</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>9.369999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>9.84</v>
+        <v>12.48</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>16.24</v>
+        <v>15.5</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>7.55</v>
+        <v>13.91</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>11.95</v>
+        <v>13.33</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>13.82</v>
+        <v>12.46</v>
       </c>
       <c r="J36" s="21" t="n">
-        <v>19.61</v>
+        <v>16.43</v>
       </c>
       <c r="K36" s="21" t="n">
-        <v>14.36</v>
+        <v>14.3</v>
       </c>
       <c r="L36" s="22" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="M36" s="22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="O36" s="23" t="n">
+        <v>-30.1</v>
+      </c>
+      <c r="P36" s="22" t="n">
         <v>0.41</v>
       </c>
-      <c r="N36" s="22" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="O36" s="22" t="n">
-        <v>-23.44</v>
-      </c>
-      <c r="P36" s="22" t="n">
-        <v>0.42</v>
-      </c>
       <c r="Q36" s="22" t="n">
-        <v>-1.48</v>
+        <v>-1.14</v>
       </c>
       <c r="R36" s="24" t="n">
-        <v>102.3</v>
+        <v>82.7</v>
       </c>
       <c r="S36" s="24" t="n">
-        <v>100.1</v>
+        <v>94.8</v>
       </c>
       <c r="T36" s="21" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="U36" s="25" t="n">
-        <v>1.032</v>
+        <v>0.896</v>
       </c>
       <c r="V36" s="25" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="W36" s="21" t="n">
-        <v>0.15</v>
+        <v>0.926</v>
+      </c>
+      <c r="W36" s="23" t="n">
+        <v>-0.18</v>
       </c>
       <c r="X36" s="24" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>5.2</v>
+        <v>12.6</v>
       </c>
       <c r="Z36" s="19" t="n">
-        <v>31.0443</v>
+        <v>70.08</v>
       </c>
     </row>
     <row r="37">
@@ -12622,80 +12622,80 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Axis Large Cap Fund - Direct Plan - Growth</t>
+          <t>Reliance Focused Large Cap Fund - Direct Plan Growth Plan - Bonus Option</t>
         </is>
       </c>
       <c r="C37" s="26" t="n">
         <v>62.1</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>2.34</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>12.48</v>
+        <v>9.84</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>15.5</v>
+        <v>16.24</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>13.91</v>
+        <v>7.55</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>13.33</v>
+        <v>11.95</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>12.46</v>
+        <v>13.82</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>16.43</v>
+        <v>19.61</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>14.3</v>
+        <v>14.36</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>0.86</v>
+        <v>0.41</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="O37" s="13" t="n">
-        <v>-30.1</v>
+        <v>14.63</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>-23.44</v>
       </c>
       <c r="P37" s="10" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="Q37" s="10" t="n">
-        <v>-1.14</v>
+        <v>-1.48</v>
       </c>
       <c r="R37" s="17" t="n">
-        <v>82.7</v>
+        <v>102.3</v>
       </c>
       <c r="S37" s="17" t="n">
-        <v>94.8</v>
+        <v>100.1</v>
       </c>
       <c r="T37" s="11" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="U37" s="18" t="n">
-        <v>0.896</v>
+        <v>1.032</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="W37" s="13" t="n">
-        <v>-0.18</v>
+        <v>0.883</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>0.15</v>
       </c>
       <c r="X37" s="17" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Y37" s="17" t="n">
-        <v>12.6</v>
+        <v>5.2</v>
       </c>
       <c r="Z37" s="8" t="n">
-        <v>70.08</v>
+        <v>31.0443</v>
       </c>
     </row>
     <row r="38">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Midcap Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Midcap Fund- Direct Growth Option</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -16717,78 +16717,78 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>JM Mid Cap Fund (Direct) - Growth</t>
+          <t>Aditya Birla Sun Life Nifty Midcap 150 Index Fund-Direct Growth</t>
         </is>
       </c>
       <c r="C36" s="20" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>-2.15</v>
+        <v>-1.39</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>26.41</v>
+        <v>23.08</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>15.1</v>
+        <v>19.23</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>7.28</v>
+        <v>9.19</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>24.7</v>
+        <v>21.04</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>24.7</v>
+        <v>21.01</v>
       </c>
       <c r="J36" s="21" t="n">
-        <v>39.53</v>
+        <v>23.41</v>
       </c>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="22" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="M36" s="22" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>16.61</v>
+        <v>16.08</v>
       </c>
       <c r="O36" s="22" t="n">
-        <v>-22.54</v>
+        <v>-21.19</v>
       </c>
       <c r="P36" s="22" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>-1.69</v>
+        <v>-1.75</v>
       </c>
       <c r="R36" s="24" t="n">
-        <v>111.4</v>
+        <v>105.6</v>
       </c>
       <c r="S36" s="24" t="n">
-        <v>91.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T36" s="21" t="n">
-        <v>16.82</v>
+        <v>9.9</v>
       </c>
       <c r="U36" s="25" t="n">
-        <v>0.97</v>
+        <v>0.986</v>
       </c>
       <c r="V36" s="25" t="n">
-        <v>0.524</v>
+        <v>0.595</v>
       </c>
       <c r="W36" s="21" t="n">
-        <v>1.32</v>
+        <v>0.91</v>
       </c>
       <c r="X36" s="24" t="n">
-        <v>93.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="Z36" s="19" t="n">
-        <v>20.2824</v>
+        <v>24.2057</v>
       </c>
     </row>
     <row r="37">
@@ -16797,78 +16797,78 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life Nifty Midcap 150 Index Fund-Direct Growth</t>
+          <t>JM Midcap Fund (Direct) - Growth</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>-1.39</v>
+        <v>-2.15</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>23.08</v>
+        <v>26.41</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>19.23</v>
+        <v>15.1</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>9.19</v>
+        <v>7.28</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>21.04</v>
+        <v>24.7</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>21.01</v>
+        <v>24.7</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>23.41</v>
+        <v>39.53</v>
       </c>
       <c r="K37" s="13" t="n"/>
       <c r="L37" s="10" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>16.08</v>
+        <v>16.61</v>
       </c>
       <c r="O37" s="10" t="n">
-        <v>-21.19</v>
+        <v>-22.54</v>
       </c>
       <c r="P37" s="10" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Q37" s="10" t="n">
-        <v>-1.75</v>
+        <v>-1.69</v>
       </c>
       <c r="R37" s="17" t="n">
-        <v>105.6</v>
+        <v>111.4</v>
       </c>
       <c r="S37" s="17" t="n">
-        <v>94.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="T37" s="11" t="n">
-        <v>9.9</v>
+        <v>16.82</v>
       </c>
       <c r="U37" s="18" t="n">
-        <v>0.986</v>
+        <v>0.97</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>0.595</v>
+        <v>0.524</v>
       </c>
       <c r="W37" s="11" t="n">
-        <v>0.91</v>
+        <v>1.32</v>
       </c>
       <c r="X37" s="17" t="n">
-        <v>94.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="Y37" s="17" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="Z37" s="8" t="n">
-        <v>24.2057</v>
+        <v>20.2824</v>
       </c>
     </row>
     <row r="38">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>BANDHAN MID CAP FUND - GROWTH - DIRECT PLAN</t>
+          <t>BANDHAN MIDCAP FUND - GROWTH - DIRECT PLAN</t>
         </is>
       </c>
       <c r="C68" s="20" t="n">
@@ -20677,76 +20677,78 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>PGIM India Large and Midcap Fund - Direct Plan - Growth Option</t>
+          <t>DSP Nifty Midcap 150 Quality 50 Index Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C85" s="26" t="n">
         <v>55.8</v>
       </c>
-      <c r="D85" s="11" t="n">
-        <v>6.99</v>
+      <c r="D85" s="13" t="n">
+        <v>-3.26</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>8.66</v>
+        <v>13.47</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>5.11</v>
+        <v>8.18</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>2.52</v>
+        <v>4.01</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>14.8</v>
+        <v>14.46</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="J85" s="13" t="n"/>
+        <v>14.49</v>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>21.25</v>
+      </c>
       <c r="K85" s="13" t="n"/>
       <c r="L85" s="10" t="n">
-        <v>0.93</v>
+        <v>0.61</v>
       </c>
       <c r="M85" s="10" t="n">
-        <v>1.14</v>
+        <v>0.76</v>
       </c>
       <c r="N85" s="10" t="n">
-        <v>14.34</v>
+        <v>13.99</v>
       </c>
       <c r="O85" s="10" t="n">
-        <v>-15.46</v>
+        <v>-21.41</v>
       </c>
       <c r="P85" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="Q85" s="10" t="n">
-        <v>-1.4</v>
+        <v>-1.45</v>
       </c>
       <c r="R85" s="17" t="n">
-        <v>95.7</v>
+        <v>67.8</v>
       </c>
       <c r="S85" s="17" t="n">
-        <v>93.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="T85" s="11" t="n">
-        <v>9.1</v>
+        <v>3.07</v>
       </c>
       <c r="U85" s="18" t="n">
-        <v>0.919</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>0.794</v>
+        <v>0.538</v>
       </c>
       <c r="W85" s="11" t="n">
-        <v>1.19</v>
+        <v>0.06</v>
       </c>
       <c r="X85" s="17" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Y85" s="17" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Z85" s="8" t="n">
-        <v>13.01</v>
+        <v>14.8564</v>
       </c>
     </row>
     <row r="86">
@@ -20755,78 +20757,76 @@
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>DSP Nifty Midcap 150 Quality 50 Index Fund - Direct - Growth</t>
+          <t>PGIM India Large and Midcap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C86" s="27" t="n">
         <v>55.8</v>
       </c>
-      <c r="D86" s="23" t="n">
-        <v>-3.26</v>
+      <c r="D86" s="21" t="n">
+        <v>6.99</v>
       </c>
       <c r="E86" s="21" t="n">
-        <v>13.47</v>
+        <v>8.66</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>8.18</v>
+        <v>5.11</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>4.01</v>
+        <v>2.52</v>
       </c>
       <c r="H86" s="21" t="n">
-        <v>14.46</v>
+        <v>14.8</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="J86" s="21" t="n">
-        <v>21.25</v>
-      </c>
+        <v>14.8</v>
+      </c>
+      <c r="J86" s="23" t="n"/>
       <c r="K86" s="23" t="n"/>
       <c r="L86" s="22" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>0.76</v>
+        <v>1.14</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>13.99</v>
+        <v>14.34</v>
       </c>
       <c r="O86" s="22" t="n">
-        <v>-21.41</v>
+        <v>-15.46</v>
       </c>
       <c r="P86" s="22" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>-1.45</v>
+        <v>-1.4</v>
       </c>
       <c r="R86" s="24" t="n">
-        <v>67.8</v>
+        <v>95.7</v>
       </c>
       <c r="S86" s="24" t="n">
-        <v>87</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="T86" s="21" t="n">
-        <v>3.07</v>
+        <v>9.1</v>
       </c>
       <c r="U86" s="25" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.919</v>
       </c>
       <c r="V86" s="25" t="n">
-        <v>0.538</v>
+        <v>0.794</v>
       </c>
       <c r="W86" s="21" t="n">
-        <v>0.06</v>
+        <v>1.19</v>
       </c>
       <c r="X86" s="24" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Y86" s="24" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Z86" s="19" t="n">
-        <v>14.8564</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="87">
@@ -20915,7 +20915,7 @@
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Large &amp; Mid Cap Fund- Direct Plan- Growth</t>
+          <t>Bajaj Finserv Large and Mid Cap Fund- Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C88" s="29" t="n">
@@ -22047,7 +22047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -22736,78 +22736,78 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Kotak Multi Cap Fund-Direct Plan-Growth</t>
+          <t>HDFC Multi Cap Fund - Growth Option - Direct Plan</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>78.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>25.17</v>
+        <v>23.18</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>14.92</v>
+        <v>14.56</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>7.2</v>
+        <v>7.03</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>22.15</v>
+        <v>19.66</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>22.67</v>
+        <v>20.77</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>28.61</v>
+        <v>27.4</v>
       </c>
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>14.93</v>
+        <v>13.93</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>-21</v>
+        <v>-20.2</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>105.7</v>
+        <v>101.4</v>
       </c>
       <c r="S9" s="17" t="n">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="T9" s="11" t="n">
-        <v>11.74</v>
+        <v>9.9</v>
       </c>
       <c r="U9" s="18" t="n">
-        <v>0.978</v>
+        <v>0.969</v>
       </c>
       <c r="V9" s="18" t="n">
-        <v>0.679</v>
+        <v>0.765</v>
       </c>
       <c r="W9" s="11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X9" s="17" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="Y9" s="17" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>20.065</v>
+        <v>19.779</v>
       </c>
     </row>
     <row r="10">
@@ -22816,78 +22816,78 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>HDFC Multi Cap Fund - Growth Option - Direct Plan</t>
+          <t>Bank of India Multi Cap Fund Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>77.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>-1.82</v>
+        <v>-2.15</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>23.18</v>
+        <v>22.05</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>14.56</v>
+        <v>12.7</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>7.03</v>
+        <v>6.16</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>19.66</v>
+        <v>18.27</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>20.77</v>
+        <v>18.27</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>27.4</v>
+        <v>29.01</v>
       </c>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="22" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>13.93</v>
+        <v>16.01</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>-20.2</v>
+        <v>-20.31</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>-1.42</v>
+        <v>-1.5</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>101.4</v>
+        <v>110.8</v>
       </c>
       <c r="S10" s="24" t="n">
-        <v>93.7</v>
+        <v>95.3</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>9.9</v>
+        <v>10.48</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>0.969</v>
+        <v>1.031</v>
       </c>
       <c r="V10" s="25" t="n">
-        <v>0.765</v>
+        <v>0.65</v>
       </c>
       <c r="W10" s="21" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="X10" s="24" t="n">
-        <v>97.2</v>
+        <v>94.7</v>
       </c>
       <c r="Y10" s="24" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>19.779</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="11">
@@ -22896,78 +22896,78 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Bank of India Multi Cap Fund Direct Plan - Growth</t>
+          <t>LIC MF Multi Cap Fund-Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>76.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>-2.15</v>
+        <v>-0.2</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>22.05</v>
+        <v>20.9</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12.7</v>
+        <v>12.06</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>6.16</v>
+        <v>5.86</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>18.27</v>
+        <v>21.12</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>18.27</v>
+        <v>21.12</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>29.01</v>
+        <v>31.67</v>
       </c>
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="10" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>16.01</v>
+        <v>13.95</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>-20.31</v>
+        <v>-19.32</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>-1.5</v>
+        <v>-1.42</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>110.8</v>
+        <v>90.3</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>95.3</v>
+        <v>89.5</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>1.031</v>
+        <v>0.899</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.65</v>
+        <v>0.634</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X11" s="17" t="n">
-        <v>94.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Y11" s="17" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>18.2</v>
+        <v>17.7123</v>
       </c>
     </row>
     <row r="12">
@@ -22976,78 +22976,80 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>LIC MF Multi Cap Fund-Direct Plan-Growth</t>
+          <t>Principal Multi Cap Growth Fund-Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>-0.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>47.35</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>20.9</v>
+        <v>21.35</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>12.06</v>
+        <v>19.76</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>5.86</v>
+        <v>16.01</v>
       </c>
       <c r="H12" s="21" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J12" s="21" t="n">
         <v>21.12</v>
       </c>
-      <c r="I12" s="21" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="K12" s="23" t="n"/>
+      <c r="K12" s="21" t="n">
+        <v>14.28</v>
+      </c>
       <c r="L12" s="22" t="n">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>1.49</v>
+        <v>0.91</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <v>-19.32</v>
+        <v>20.63</v>
+      </c>
+      <c r="O12" s="23" t="n">
+        <v>-38.67</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>-1.42</v>
+        <v>-1.72</v>
       </c>
       <c r="R12" s="24" t="n">
-        <v>90.3</v>
+        <v>78.2</v>
       </c>
       <c r="S12" s="24" t="n">
-        <v>89.5</v>
+        <v>95.2</v>
       </c>
       <c r="T12" s="21" t="n">
-        <v>10.5</v>
+        <v>4.86</v>
       </c>
       <c r="U12" s="25" t="n">
-        <v>0.899</v>
+        <v>0.919</v>
       </c>
       <c r="V12" s="25" t="n">
-        <v>0.634</v>
+        <v>0.925</v>
       </c>
       <c r="W12" s="21" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="X12" s="24" t="n">
-        <v>98.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Y12" s="24" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="Z12" s="19" t="n">
-        <v>17.7123</v>
+        <v>259.0319</v>
       </c>
     </row>
     <row r="13">
@@ -23056,80 +23058,78 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Principal Multi Cap Growth Fund-Direct Plan - Growth Option</t>
+          <t>BANDHAN MULTI CAP FUND - GROWTH - DIRECT PLAN</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>47.35</v>
+        <v>74</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>-0.87</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>21.35</v>
+        <v>20.44</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>19.76</v>
+        <v>12.65</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>16.01</v>
+        <v>6.13</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>34.35</v>
+        <v>18.21</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>21.95</v>
+        <v>18.63</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>14.28</v>
-      </c>
+        <v>22.99</v>
+      </c>
+      <c r="K13" s="13" t="n"/>
       <c r="L13" s="10" t="n">
-        <v>0.87</v>
+        <v>1.22</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>0.91</v>
+        <v>1.46</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>20.63</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>-38.67</v>
+        <v>12.73</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>-18.3</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>0.55</v>
+        <v>1.12</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-1.72</v>
+        <v>-1.3</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>78.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="S13" s="17" t="n">
-        <v>95.2</v>
+        <v>90.8</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>4.86</v>
+        <v>8.34</v>
       </c>
       <c r="U13" s="18" t="n">
-        <v>0.919</v>
+        <v>0.891</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>0.925</v>
+        <v>0.771</v>
       </c>
       <c r="W13" s="11" t="n">
-        <v>0.55</v>
+        <v>1.05</v>
       </c>
       <c r="X13" s="17" t="n">
-        <v>81.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y13" s="17" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>259.0319</v>
+        <v>18.156</v>
       </c>
     </row>
     <row r="14">
@@ -23138,78 +23138,80 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>BANDHAN MULTI CAP FUND - GROWTH - DIRECT PLAN</t>
+          <t>quant Multi Cap Fund-GROWTH OPTION-Direct Plan</t>
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>74</v>
+        <v>73.8</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>-0.87</v>
+        <v>-14.42</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>20.44</v>
+        <v>14.44</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>12.65</v>
+        <v>23.99</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>6.13</v>
+        <v>18.61</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>18.21</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>18.63</v>
+        <v>15.92</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K14" s="23" t="n"/>
+        <v>25.32</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>21.77</v>
+      </c>
       <c r="L14" s="22" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="O14" s="22" t="n">
-        <v>-18.3</v>
+        <v>17.09</v>
+      </c>
+      <c r="O14" s="23" t="n">
+        <v>-36.26</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>1.12</v>
+        <v>0.4</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>-1.3</v>
+        <v>-1.89</v>
       </c>
       <c r="R14" s="24" t="n">
-        <v>87.90000000000001</v>
+        <v>113.5</v>
       </c>
       <c r="S14" s="24" t="n">
-        <v>90.8</v>
+        <v>102.3</v>
       </c>
       <c r="T14" s="21" t="n">
-        <v>8.34</v>
+        <v>0.96</v>
       </c>
       <c r="U14" s="25" t="n">
-        <v>0.891</v>
+        <v>1.073</v>
       </c>
       <c r="V14" s="25" t="n">
-        <v>0.771</v>
+        <v>0.624</v>
       </c>
       <c r="W14" s="21" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="X14" s="24" t="n">
-        <v>97.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="Y14" s="24" t="n">
-        <v>3.7</v>
+        <v>12.6</v>
       </c>
       <c r="Z14" s="19" t="n">
-        <v>18.156</v>
+        <v>668.4321</v>
       </c>
     </row>
     <row r="15">
@@ -23218,80 +23220,78 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>quant Multi Cap Fund-GROWTH OPTION-Direct Plan</t>
+          <t>WhiteOak Capital Multi Cap Fund Direct Plan Growth</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>-14.42</v>
+        <v>72.2</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>8.710000000000001</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>14.44</v>
+        <v>15.92</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>23.99</v>
+        <v>9.27</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>18.61</v>
+        <v>4.53</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>9.640000000000001</v>
+        <v>19.82</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>15.92</v>
+        <v>19.82</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>21.77</v>
-      </c>
+        <v>21.99</v>
+      </c>
+      <c r="K15" s="13" t="n"/>
       <c r="L15" s="10" t="n">
-        <v>0.59</v>
+        <v>1.45</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>-36.26</v>
+        <v>15.25</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>-16.93</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>0.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>-1.89</v>
+        <v>-1.57</v>
       </c>
       <c r="R15" s="17" t="n">
-        <v>113.5</v>
+        <v>100.7</v>
       </c>
       <c r="S15" s="17" t="n">
-        <v>102.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>0.96</v>
+        <v>11.86</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>1.073</v>
+        <v>0.968</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>0.624</v>
+        <v>0.728</v>
       </c>
       <c r="W15" s="11" t="n">
-        <v>0.18</v>
+        <v>1.35</v>
       </c>
       <c r="X15" s="17" t="n">
-        <v>84.5</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="17" t="n">
-        <v>12.6</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>668.4321</v>
+        <v>15.608</v>
       </c>
     </row>
     <row r="16">
@@ -23300,78 +23300,80 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>WhiteOak Capital Multi Cap Fund Direct Plan Growth</t>
+          <t>BNP Paribas MULTI CAP Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C16" s="20" t="n">
-        <v>72.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>8.710000000000001</v>
+        <v>21.91</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>15.92</v>
+        <v>18.99</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>9.27</v>
+        <v>14.99</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>4.53</v>
+        <v>14.95</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>19.82</v>
+        <v>24.47</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>19.82</v>
+        <v>17.33</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K16" s="23" t="n"/>
+        <v>20.43</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>14.21</v>
+      </c>
       <c r="L16" s="22" t="n">
-        <v>1.45</v>
+        <v>0.77</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="N16" s="22" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="O16" s="22" t="n">
-        <v>-16.93</v>
+        <v>19.89</v>
+      </c>
+      <c r="O16" s="23" t="n">
+        <v>-36.18</v>
       </c>
       <c r="P16" s="22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>-1.57</v>
+        <v>-1.73</v>
       </c>
       <c r="R16" s="24" t="n">
-        <v>100.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="S16" s="24" t="n">
-        <v>92.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="T16" s="21" t="n">
-        <v>11.86</v>
+        <v>6.12</v>
       </c>
       <c r="U16" s="25" t="n">
-        <v>0.968</v>
+        <v>0.862</v>
       </c>
       <c r="V16" s="25" t="n">
-        <v>0.728</v>
+        <v>0.926</v>
       </c>
       <c r="W16" s="21" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="X16" s="24" t="n">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="Y16" s="24" t="n">
-        <v>1.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" s="19" t="n">
-        <v>15.608</v>
+        <v>83.9294</v>
       </c>
     </row>
     <row r="17">
@@ -23380,80 +23382,78 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>BNP Paribas MULTI CAP Fund - Direct Plan - Growth Option</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>21.91</v>
+          <t>Edelweiss Multi Cap Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>-0.21</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>18.99</v>
+        <v>14.88</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>14.99</v>
+        <v>8.68</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>14.95</v>
+        <v>4.25</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>24.47</v>
+        <v>13.75</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>17.33</v>
+        <v>13.75</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>14.21</v>
-      </c>
+        <v>15.91</v>
+      </c>
+      <c r="K17" s="13" t="n"/>
       <c r="L17" s="10" t="n">
-        <v>0.77</v>
+        <v>1.37</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>0.83</v>
+        <v>1.62</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="O17" s="13" t="n">
-        <v>-36.18</v>
+        <v>15.91</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>-20.19</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>-1.73</v>
+        <v>-1.55</v>
       </c>
       <c r="R17" s="17" t="n">
-        <v>73.09999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>94.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>6.12</v>
+        <v>8.09</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>0.862</v>
+        <v>1.03</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.926</v>
+        <v>0.769</v>
       </c>
       <c r="W17" s="11" t="n">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="X17" s="17" t="n">
-        <v>81.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>83.9294</v>
+        <v>15.3825</v>
       </c>
     </row>
     <row r="18">
@@ -23462,78 +23462,78 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Edelweiss Multi Cap Fund - Direct Plan - Growth</t>
+          <t>Canara Robeco Multi Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>-0.21</v>
+        <v>67.7</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>2.95</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>14.88</v>
+        <v>14.55</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>8.68</v>
+        <v>8.49</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>13.75</v>
+        <v>16.2</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>13.75</v>
+        <v>16.2</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>15.91</v>
+        <v>21.4</v>
       </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="22" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>15.91</v>
+        <v>14.09</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>-20.19</v>
+        <v>-18.32</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>-1.55</v>
+        <v>-1.58</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>112.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>97.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>8.09</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="U18" s="25" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="V18" s="25" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="W18" s="21" t="n">
         <v>1.03</v>
       </c>
-      <c r="V18" s="25" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="W18" s="21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="X18" s="24" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>15.3825</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="19">
@@ -23542,78 +23542,78 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Canara Robeco Multi Cap Fund - Direct Plan - Growth Option</t>
+          <t>Sundaram Multi Cap Fund (Formerly Known as Principal Multi Cap Growth Fund)-Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>67.7</v>
+        <v>67.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>14.55</v>
+        <v>18.28</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8.49</v>
+        <v>10.17</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>4.16</v>
+        <v>4.96</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>16.2</v>
+        <v>18.09</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>16.2</v>
+        <v>17.84</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>21.4</v>
+        <v>21.03</v>
       </c>
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="10" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>14.09</v>
+        <v>12.68</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>-18.32</v>
+        <v>-19.45</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>-1.58</v>
+        <v>-1.25</v>
       </c>
       <c r="R19" s="17" t="n">
-        <v>92.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>91.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>9.140000000000001</v>
+        <v>6.43</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>0.919</v>
+        <v>0.883</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>0.731</v>
+        <v>0.768</v>
       </c>
       <c r="W19" s="11" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="X19" s="17" t="n">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="Y19" s="17" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>15.03</v>
+        <v>425.4797</v>
       </c>
     </row>
     <row r="20">
@@ -23622,78 +23622,80 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Sundaram Multi Cap Fund (Formerly Known as Principal Multi Cap Growth Fund)-Direct Plan - Growth Option</t>
+          <t>Sundaram Multi Cap Fund Series II Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>67.5</v>
+        <v>66</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>1.84</v>
+        <v>8.01</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>18.28</v>
+        <v>20.17</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>10.17</v>
+        <v>12.8</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>4.96</v>
+        <v>6.21</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>18.09</v>
+        <v>11.43</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>17.84</v>
+        <v>14.61</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="K20" s="23" t="n"/>
+        <v>18.22</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>20.49</v>
+      </c>
       <c r="L20" s="22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>12.68</v>
-      </c>
-      <c r="O20" s="22" t="n">
-        <v>-19.45</v>
+        <v>14.79</v>
+      </c>
+      <c r="O20" s="23" t="n">
+        <v>-36.8</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>-1.25</v>
+        <v>-1.45</v>
       </c>
       <c r="R20" s="24" t="n">
-        <v>82.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="S20" s="24" t="n">
-        <v>90.2</v>
+        <v>94.5</v>
       </c>
       <c r="T20" s="21" t="n">
-        <v>6.43</v>
+        <v>0.57</v>
       </c>
       <c r="U20" s="25" t="n">
-        <v>0.883</v>
+        <v>0.909</v>
       </c>
       <c r="V20" s="25" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="W20" s="21" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
+      </c>
+      <c r="W20" s="23" t="n">
+        <v>-0.27</v>
       </c>
       <c r="X20" s="24" t="n">
-        <v>91.2</v>
+        <v>88</v>
       </c>
       <c r="Y20" s="24" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="Z20" s="19" t="n">
-        <v>425.4797</v>
+        <v>18.309</v>
       </c>
     </row>
     <row r="21">
@@ -23702,80 +23704,80 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Multi Cap Fund Series II Direct Plan - Growth</t>
+          <t>Sundaram Multi Cap Fund Series I Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>66</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>8.01</v>
+        <v>12.32</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>20.17</v>
+        <v>20.53</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>12.8</v>
+        <v>12.28</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>6.21</v>
+        <v>5.96</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>11.43</v>
+        <v>11.02</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>14.61</v>
+        <v>13.98</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>18.22</v>
+        <v>17.8</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>20.49</v>
+        <v>20.18</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>14.79</v>
+        <v>14.85</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>-36.8</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q21" s="10" t="n">
         <v>-1.45</v>
       </c>
       <c r="R21" s="17" t="n">
-        <v>75.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="S21" s="17" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="T21" s="11" t="n">
-        <v>0.57</v>
+        <v>94.8</v>
+      </c>
+      <c r="T21" s="13" t="n">
+        <v>-0.35</v>
       </c>
       <c r="U21" s="18" t="n">
-        <v>0.909</v>
+        <v>0.908</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>0.89</v>
+        <v>0.893</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>-0.27</v>
+        <v>-0.48</v>
       </c>
       <c r="X21" s="17" t="n">
-        <v>88</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Y21" s="17" t="n">
         <v>5</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>18.309</v>
+        <v>17.872</v>
       </c>
     </row>
     <row r="22">
@@ -23784,80 +23786,74 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Sundaram Multi Cap Fund Series I Direct Plan - Growth</t>
+          <t>Motilal Oswal Multi Cap Fund-Direct Plan Growth</t>
         </is>
       </c>
       <c r="C22" s="27" t="n">
-        <v>64.59999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>12.32</v>
+        <v>18.76</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>20.53</v>
+        <v>10.66</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>12.28</v>
+        <v>6.27</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>5.96</v>
+        <v>3.09</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>11.02</v>
+        <v>20.25</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>20.18</v>
-      </c>
+        <v>20.25</v>
+      </c>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
       <c r="L22" s="22" t="n">
-        <v>1.06</v>
+        <v>1.37</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="O22" s="23" t="n">
-        <v>-36.8</v>
+        <v>19.53</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>-18.87</v>
       </c>
       <c r="P22" s="22" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>-1.45</v>
+        <v>-1.92</v>
       </c>
       <c r="R22" s="24" t="n">
-        <v>75.09999999999999</v>
+        <v>139.6</v>
       </c>
       <c r="S22" s="24" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="T22" s="23" t="n">
-        <v>-0.35</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="T22" s="21" t="n">
+        <v>24.4</v>
       </c>
       <c r="U22" s="25" t="n">
-        <v>0.908</v>
+        <v>1.019</v>
       </c>
       <c r="V22" s="25" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="W22" s="23" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="X22" s="24" t="n">
-        <v>86.59999999999999</v>
-      </c>
+        <v>0.461</v>
+      </c>
+      <c r="W22" s="21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X22" s="24" t="n"/>
       <c r="Y22" s="24" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" s="19" t="n">
-        <v>17.872</v>
+        <v>13.8885</v>
       </c>
     </row>
     <row r="23">
@@ -23866,74 +23862,80 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Motilal Oswal Multi Cap Fund-Direct Plan Growth</t>
+          <t>Principal Multi Cap Growth Fund - Direct Plan -Half Yearly Income Distribution CUM Capital Withdrawal Option</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>59.9</v>
+        <v>57</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>18.76</v>
+        <v>36.95</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>10.66</v>
+        <v>16.63</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6.27</v>
+        <v>11.67</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>3.09</v>
+        <v>9.99</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>20.25</v>
+        <v>26.62</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+        <v>16.22</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>6.72</v>
+      </c>
       <c r="L23" s="10" t="n">
-        <v>1.37</v>
+        <v>0.62</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>1.87</v>
+        <v>0.64</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="O23" s="10" t="n">
-        <v>-18.87</v>
+        <v>21.2</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>-40.63</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>-1.92</v>
+        <v>-1.75</v>
       </c>
       <c r="R23" s="17" t="n">
-        <v>139.6</v>
+        <v>75.7</v>
       </c>
       <c r="S23" s="17" t="n">
-        <v>94.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>24.4</v>
+        <v>0.7</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>1.019</v>
+        <v>0.925</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="W23" s="11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X23" s="17" t="n"/>
+        <v>0.888</v>
+      </c>
+      <c r="W23" s="13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X23" s="17" t="n">
+        <v>68.2</v>
+      </c>
       <c r="Y23" s="17" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>13.8885</v>
+        <v>68.8862</v>
       </c>
     </row>
     <row r="24">
@@ -23942,80 +23944,78 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Principal Multi Cap Growth Fund - Direct Plan -Half Yearly Income Distribution CUM Capital Withdrawal Option</t>
+          <t>UTI Multi Cap Fund - Growth Option - Direct</t>
         </is>
       </c>
       <c r="C24" s="27" t="n">
-        <v>57</v>
+        <v>50.4</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>36.95</v>
+        <v>14.54</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>16.63</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F24" s="21" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="I24" s="21" t="n">
         <v>11.67</v>
       </c>
-      <c r="G24" s="21" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="I24" s="21" t="n">
-        <v>16.22</v>
-      </c>
       <c r="J24" s="21" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="K24" s="21" t="n">
-        <v>6.72</v>
-      </c>
+        <v>10.14</v>
+      </c>
+      <c r="K24" s="23" t="n"/>
       <c r="L24" s="22" t="n">
-        <v>0.62</v>
+        <v>0.35</v>
       </c>
       <c r="M24" s="22" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="N24" s="22" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="O24" s="23" t="n">
-        <v>-40.63</v>
+        <v>13.64</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>-18.58</v>
       </c>
       <c r="P24" s="22" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>-1.75</v>
+        <v>-1.53</v>
       </c>
       <c r="R24" s="24" t="n">
-        <v>75.7</v>
+        <v>94.2</v>
       </c>
       <c r="S24" s="24" t="n">
-        <v>96.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="T24" s="21" t="n">
-        <v>0.7</v>
+        <v>1.02</v>
       </c>
       <c r="U24" s="25" t="n">
-        <v>0.925</v>
+        <v>0.979</v>
       </c>
       <c r="V24" s="25" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="W24" s="23" t="n">
-        <v>-0.1</v>
+        <v>0.909</v>
+      </c>
+      <c r="W24" s="21" t="n">
+        <v>0.2</v>
       </c>
       <c r="X24" s="24" t="n">
-        <v>68.2</v>
+        <v>78.7</v>
       </c>
       <c r="Y24" s="24" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="Z24" s="19" t="n">
-        <v>68.8862</v>
+        <v>14.2467</v>
       </c>
     </row>
     <row r="25">
@@ -24024,78 +24024,70 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>UTI Multi Cap Fund - Growth Option - Direct</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="n">
-        <v>50.4</v>
+          <t>UTI Multi Cap Fund - Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>38.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>14.54</v>
+        <v>3.51</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>9.949999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>10.14</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="10" t="n">
-        <v>0.35</v>
+        <v>0.96</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>0.42</v>
+        <v>1.21</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>13.64</v>
+        <v>9.41</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>-18.58</v>
+        <v>-3.63</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="Q25" s="10" t="n">
-        <v>-1.53</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="R25" s="17" t="n">
-        <v>94.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="S25" s="17" t="n">
-        <v>98</v>
+        <v>83.7</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>1.02</v>
+        <v>9.75</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>0.979</v>
+        <v>0.839</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>0.909</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W25" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X25" s="17" t="n">
-        <v>78.7</v>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="X25" s="17" t="n"/>
       <c r="Y25" s="17" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>14.2467</v>
+        <v>10.3177</v>
       </c>
     </row>
     <row r="26">
@@ -24104,76 +24096,70 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>DSP Multi Cap Fund - Direct - Growth</t>
+          <t>BAJAJ FINSERV MULTI CAP FUND - DIRECT - GROWTH</t>
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="D26" s="23" t="n">
-        <v>-0.93</v>
+        <v>38.5</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>11.68</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>7.71</v>
+        <v>3.75</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>4.56</v>
+        <v>2.23</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>11.26</v>
-      </c>
+        <v>1.11</v>
+      </c>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
       <c r="J26" s="23" t="n"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="22" t="n">
-        <v>0.7</v>
+        <v>1.74</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>0.87</v>
+        <v>2.24</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>15.33</v>
+        <v>12.93</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>-21.27</v>
+        <v>-5.98</v>
       </c>
       <c r="P26" s="22" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>-1.7</v>
+        <v>-1.06</v>
       </c>
       <c r="R26" s="24" t="n">
-        <v>81.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="S26" s="24" t="n">
-        <v>90.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T26" s="21" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="U26" s="25" t="n">
-        <v>0.876</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V26" s="25" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="W26" s="21" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="X26" s="24" t="n">
-        <v>89.7</v>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="W26" s="23" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="X26" s="24" t="n"/>
       <c r="Y26" s="24" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z26" s="19" t="n">
-        <v>12.521</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="27">
@@ -24182,70 +24168,74 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>UTI Multi Cap Fund - Direct Plan - Growth Option</t>
+          <t>Franklin India Multi Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C27" s="28" t="n">
-        <v>38.6</v>
+        <v>34.4</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>3.51</v>
+        <v>2.29</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
+        <v>0.44</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>8.960000000000001</v>
+      </c>
       <c r="J27" s="13" t="n"/>
       <c r="K27" s="13" t="n"/>
       <c r="L27" s="10" t="n">
-        <v>0.96</v>
+        <v>-0.06</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>1.21</v>
+        <v>-0.09</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>9.41</v>
+        <v>15.21</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>-3.63</v>
+        <v>-18.68</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0.32</v>
+        <v>0.08</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.67</v>
       </c>
       <c r="R27" s="17" t="n">
-        <v>81.40000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>83.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T27" s="11" t="n">
-        <v>9.75</v>
+        <v>3.62</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>0.839</v>
+        <v>0.959</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="W27" s="11" t="n">
-        <v>1.53</v>
+        <v>0.42</v>
       </c>
       <c r="X27" s="17" t="n"/>
       <c r="Y27" s="17" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>10.3177</v>
+        <v>10.4452</v>
       </c>
     </row>
     <row r="28">
@@ -24254,70 +24244,74 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>BAJAJ FINSERV MULTI CAP FUND - DIRECT - GROWTH</t>
+          <t>PGIM India Multi Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C28" s="29" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="D28" s="21" t="n">
-        <v>11.68</v>
-      </c>
-      <c r="E28" s="21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H28" s="23" t="n"/>
-      <c r="I28" s="23" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E28" s="23" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>12.54</v>
+      </c>
       <c r="J28" s="23" t="n"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="22" t="n">
-        <v>1.74</v>
+        <v>-0.37</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>2.24</v>
+        <v>-0.51</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>12.93</v>
+        <v>15.16</v>
       </c>
       <c r="O28" s="22" t="n">
-        <v>-5.98</v>
+        <v>-18.1</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>0.63</v>
+        <v>-0</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>-1.06</v>
+        <v>-1.77</v>
       </c>
       <c r="R28" s="24" t="n">
-        <v>68.5</v>
+        <v>92.8</v>
       </c>
       <c r="S28" s="24" t="n">
-        <v>89.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="T28" s="21" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="U28" s="25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.967</v>
       </c>
       <c r="V28" s="25" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="W28" s="23" t="n">
-        <v>-0.44</v>
+        <v>0.727</v>
+      </c>
+      <c r="W28" s="21" t="n">
+        <v>0.16</v>
       </c>
       <c r="X28" s="24" t="n"/>
       <c r="Y28" s="24" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Z28" s="19" t="n">
-        <v>11.19</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="29">
@@ -24326,221 +24320,69 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Franklin India Multi Cap Fund - Direct - Growth</t>
+          <t>Samco Multi Cap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C29" s="28" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="I29" s="11" t="n">
-        <v>8.960000000000001</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
       <c r="J29" s="13" t="n"/>
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="10" t="n">
-        <v>-0.06</v>
+        <v>-1.17</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>-0.09</v>
+        <v>-1.45</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>15.21</v>
+        <v>10.6</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>-18.68</v>
+        <v>-13.14</v>
       </c>
       <c r="P29" s="10" t="n">
-        <v>0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>-1.67</v>
+        <v>-1.09</v>
       </c>
       <c r="R29" s="17" t="n">
-        <v>100.3</v>
+        <v>33.6</v>
       </c>
       <c r="S29" s="17" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="T29" s="11" t="n">
-        <v>3.62</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="T29" s="13" t="n">
+        <v>-7.95</v>
       </c>
       <c r="U29" s="18" t="n">
-        <v>0.959</v>
+        <v>0.542</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="W29" s="11" t="n">
-        <v>0.42</v>
+        <v>0.484</v>
+      </c>
+      <c r="W29" s="13" t="n">
+        <v>-1.03</v>
       </c>
       <c r="X29" s="17" t="n"/>
       <c r="Y29" s="17" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>10.4452</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>PGIM India Multi Cap Fund - Direct Plan - Growth Option</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="D30" s="23" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F30" s="23" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="G30" s="23" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="I30" s="21" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="J30" s="23" t="n"/>
-      <c r="K30" s="23" t="n"/>
-      <c r="L30" s="22" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="M30" s="22" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="N30" s="22" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="O30" s="22" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="P30" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q30" s="22" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="R30" s="24" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="S30" s="24" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="T30" s="21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="U30" s="25" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="V30" s="25" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="W30" s="21" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="X30" s="24" t="n"/>
-      <c r="Y30" s="24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Z30" s="19" t="n">
-        <v>10.07</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Samco Multi Cap Fund - Direct Plan - Growth</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>-4.97</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="10" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="M31" s="10" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="N31" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="O31" s="10" t="n">
-        <v>-13.14</v>
-      </c>
-      <c r="P31" s="10" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="Q31" s="10" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="R31" s="17" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="S31" s="17" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="T31" s="13" t="n">
-        <v>-7.95</v>
-      </c>
-      <c r="U31" s="18" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="V31" s="18" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="W31" s="13" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="X31" s="17" t="n"/>
-      <c r="Y31" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z31" s="8" t="n">
         <v>9.56</v>
       </c>
     </row>
@@ -25249,7 +25091,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Banking and Financial Services Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Banking and Financial Services Fund Direct Growth</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
@@ -25331,80 +25173,80 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Baroda BNP Paribas Banking and Financial Services Fund - Direct - Growth Option</t>
+          <t>Aditya Birla Sun Life Banking and Financial Services Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C10" s="20" t="n">
         <v>74.3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>14.46</v>
+        <v>8.52</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>18.31</v>
+        <v>16.96</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>20.75</v>
+        <v>22</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>13.36</v>
+        <v>15.32</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>18.62</v>
+        <v>15.67</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>17.56</v>
+        <v>16.59</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>16.16</v>
+        <v>18.86</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>12.95</v>
+        <v>15.63</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>15.38</v>
+        <v>15.1</v>
       </c>
       <c r="O10" s="23" t="n">
-        <v>-42.79</v>
+        <v>-47.45</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>-1.44</v>
+        <v>-1.57</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>107.1</v>
+        <v>107.5</v>
       </c>
       <c r="S10" s="24" t="n">
-        <v>98.5</v>
+        <v>99.5</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>1.061</v>
+        <v>1.048</v>
       </c>
       <c r="V10" s="25" t="n">
-        <v>0.753</v>
+        <v>0.763</v>
       </c>
       <c r="W10" s="21" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="X10" s="24" t="n">
-        <v>79.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="Y10" s="24" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>53.4499</v>
+        <v>67.53</v>
       </c>
     </row>
     <row r="11">
@@ -25413,80 +25255,80 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life Banking and Financial Services Fund - Direct Plan - Growth</t>
+          <t>Baroda BNP Paribas Banking and Financial Services Fund - Direct - Growth Option</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
         <v>74.3</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>8.52</v>
+        <v>14.46</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>16.96</v>
+        <v>18.31</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>22</v>
+        <v>20.75</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>15.32</v>
+        <v>13.36</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>15.67</v>
+        <v>18.62</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>16.59</v>
+        <v>17.56</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>18.86</v>
+        <v>16.16</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>15.63</v>
+        <v>12.95</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>15.1</v>
+        <v>15.38</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>-47.45</v>
+        <v>-42.79</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>-1.57</v>
+        <v>-1.44</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>107.5</v>
+        <v>107.1</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>99.5</v>
+        <v>98.5</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>1.048</v>
+        <v>1.061</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.763</v>
+        <v>0.753</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="X11" s="17" t="n">
-        <v>80.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Y11" s="17" t="n">
-        <v>11.7</v>
+        <v>12.6</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>67.53</v>
+        <v>53.4499</v>
       </c>
     </row>
     <row r="12">
@@ -27611,78 +27453,80 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>DWS Banking and PSU Debt fund- Direct Plan-Growth</t>
+          <t>DSP Banking &amp; PSU Debt Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C38" s="27" t="n">
         <v>57.8</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>8.140000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>9.23</v>
+        <v>7.55</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>5.44</v>
+        <v>6.2</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>2.68</v>
+        <v>7.54</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>9.300000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>9.300000000000001</v>
+        <v>6.94</v>
       </c>
       <c r="J38" s="21" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="K38" s="23" t="n"/>
+        <v>7.91</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <v>7.58</v>
+      </c>
       <c r="L38" s="22" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="M38" s="22" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="N38" s="22" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="O38" s="22" t="n">
-        <v>-3.2</v>
+        <v>-3.05</v>
       </c>
       <c r="P38" s="22" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="R38" s="24" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="S38" s="24" t="n">
-        <v>-5.1</v>
+        <v>-6.3</v>
       </c>
       <c r="T38" s="21" t="n">
-        <v>9.57</v>
+        <v>7.64</v>
       </c>
       <c r="U38" s="25" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="V38" s="25" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="W38" s="21" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
+      </c>
+      <c r="W38" s="23" t="n">
+        <v>-0.38</v>
       </c>
       <c r="X38" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y38" s="24" t="n">
-        <v>3</v>
+        <v>11.9</v>
       </c>
       <c r="Z38" s="19" t="n">
-        <v>13.0504</v>
+        <v>25.0721</v>
       </c>
     </row>
     <row r="39">
@@ -27691,80 +27535,78 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>DSP Banking &amp; PSU Debt Fund - Direct Plan - Growth</t>
+          <t>DWS Banking and PSU Debt fund- Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C39" s="26" t="n">
         <v>57.8</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>7.95</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>7.55</v>
+        <v>9.23</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6.2</v>
+        <v>5.44</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>7.54</v>
+        <v>2.68</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>7.92</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>6.94</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="K39" s="11" t="n">
-        <v>7.58</v>
-      </c>
+        <v>10.05</v>
+      </c>
+      <c r="K39" s="13" t="n"/>
       <c r="L39" s="10" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>-3.05</v>
+        <v>-3.2</v>
       </c>
       <c r="P39" s="10" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="Q39" s="10" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R39" s="17" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="S39" s="17" t="n">
-        <v>-6.3</v>
+        <v>-5.1</v>
       </c>
       <c r="T39" s="11" t="n">
-        <v>7.64</v>
+        <v>9.57</v>
       </c>
       <c r="U39" s="18" t="n">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W39" s="13" t="n">
-        <v>-0.38</v>
+        <v>0.074</v>
+      </c>
+      <c r="W39" s="11" t="n">
+        <v>0.12</v>
       </c>
       <c r="X39" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y39" s="17" t="n">
-        <v>11.9</v>
+        <v>3</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>25.0721</v>
+        <v>13.0504</v>
       </c>
     </row>
     <row r="40">
@@ -27933,7 +27775,7 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Banking and PSU Debt Fund-Direct Plan- Growth</t>
+          <t>Bajaj Finserv Banking and PSU Fund-Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C42" s="27" t="n">
@@ -28339,7 +28181,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Banking and PSU Debt Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Banking and PSU Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C47" s="26" t="n">
@@ -29193,23 +29035,23 @@
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>Edelweiss CRISIL IBX AAA Financial Services - Jan 2028 Index Fund - Direct - Growth</t>
+          <t>Axis CRISIL-IBX AAA Bond Financial Services - Sep 2027 Index Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C58" s="29" t="n">
         <v>48</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H58" s="23" t="n"/>
       <c r="I58" s="23" t="n"/>
@@ -29219,44 +29061,44 @@
         <v>3.55</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>6.14</v>
+        <v>7.61</v>
       </c>
       <c r="N58" s="22" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="O58" s="22" t="n">
         <v>-0.29</v>
       </c>
       <c r="P58" s="22" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="R58" s="24" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S58" s="24" t="n">
-        <v>-12.4</v>
+        <v>-10.6</v>
       </c>
       <c r="T58" s="21" t="n">
-        <v>10.1</v>
+        <v>9.81</v>
       </c>
       <c r="U58" s="25" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="V58" s="25" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="W58" s="21" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="X58" s="24" t="n"/>
       <c r="Y58" s="24" t="n">
         <v>0.7</v>
       </c>
       <c r="Z58" s="19" t="n">
-        <v>10.691</v>
+        <v>10.6941</v>
       </c>
     </row>
     <row r="59">
@@ -29265,23 +29107,23 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Axis CRISIL-IBX AAA Bond Financial Services - Sep 2027 Index Fund - Direct Plan - Growth Option</t>
+          <t>Edelweiss CRISIL IBX AAA Financial Services - Jan 2028 Index Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="C59" s="28" t="n">
         <v>48</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>6.85</v>
+        <v>6.87</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H59" s="13" t="n"/>
       <c r="I59" s="13" t="n"/>
@@ -29291,44 +29133,44 @@
         <v>3.55</v>
       </c>
       <c r="M59" s="10" t="n">
-        <v>7.61</v>
+        <v>6.14</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="O59" s="10" t="n">
         <v>-0.29</v>
       </c>
       <c r="P59" s="10" t="n">
-        <v>7.69</v>
+        <v>7.72</v>
       </c>
       <c r="Q59" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="R59" s="17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="S59" s="17" t="n">
-        <v>-10.6</v>
+        <v>-12.4</v>
       </c>
       <c r="T59" s="11" t="n">
-        <v>9.81</v>
+        <v>10.1</v>
       </c>
       <c r="U59" s="18" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="W59" s="11" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="X59" s="17" t="n"/>
       <c r="Y59" s="17" t="n">
         <v>0.7</v>
       </c>
       <c r="Z59" s="8" t="n">
-        <v>10.6941</v>
+        <v>10.691</v>
       </c>
     </row>
     <row r="60">
@@ -33655,78 +33497,80 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>JPMorgan India Mid and Small Cap Fund - Direct Plan - Growth Option</t>
+          <t>Sundaram Emerging Small Cap Series VI Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
         <v>80.7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>3.82</v>
+        <v>7.75</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>31.69</v>
+        <v>35.49</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>17.39</v>
+        <v>20.22</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>8.35</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>17.07</v>
+        <v>22.77</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>22.4</v>
+        <v>24.8</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="K17" s="13" t="n"/>
+        <v>27.7</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>30.62</v>
+      </c>
       <c r="L17" s="10" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>16.26</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>-21.32</v>
+        <v>15.12</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>-41.04</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>1.49</v>
+        <v>0.86</v>
       </c>
       <c r="Q17" s="10" t="n">
         <v>-1.57</v>
       </c>
       <c r="R17" s="17" t="n">
-        <v>95.5</v>
+        <v>52.8</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>87.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>22.21</v>
+        <v>19.04</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>0.897</v>
+        <v>0.712</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.652</v>
+        <v>0.508</v>
       </c>
       <c r="W17" s="11" t="n">
-        <v>1.95</v>
+        <v>1</v>
       </c>
       <c r="X17" s="17" t="n">
-        <v>88.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>20.603</v>
+        <v>25.1352</v>
       </c>
     </row>
     <row r="18">
@@ -33735,80 +33579,78 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Sundaram Emerging Small Cap Series VI Direct Plan - Growth</t>
+          <t>JPMorgan India Mid and Small Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C18" s="20" t="n">
         <v>80.7</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>7.75</v>
+        <v>3.82</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>35.49</v>
+        <v>31.69</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>20.22</v>
+        <v>17.39</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>9.640000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>22.77</v>
+        <v>17.07</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>24.8</v>
+        <v>22.4</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>30.62</v>
-      </c>
+        <v>38.25</v>
+      </c>
+      <c r="K18" s="23" t="n"/>
       <c r="L18" s="22" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="O18" s="23" t="n">
-        <v>-41.04</v>
+        <v>16.26</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>-21.32</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>0.86</v>
+        <v>1.49</v>
       </c>
       <c r="Q18" s="22" t="n">
         <v>-1.57</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>52.8</v>
+        <v>95.5</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>71.7</v>
+        <v>87.8</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>19.04</v>
+        <v>22.21</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.712</v>
+        <v>0.897</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.508</v>
+        <v>0.652</v>
       </c>
       <c r="W18" s="21" t="n">
-        <v>1</v>
+        <v>1.95</v>
       </c>
       <c r="X18" s="24" t="n">
-        <v>85.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>25.1352</v>
+        <v>20.603</v>
       </c>
     </row>
     <row r="19">
@@ -34305,80 +34147,80 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ICICI Prudential Smallcap Fund - Direct Plan - Growth</t>
+          <t>CANARA ROBECO SMALL CAP FUND - DIRECT PLAN - GROWTH OPTION</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
         <v>77.5</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>-0.65</v>
+        <v>-4.64</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>20.45</v>
+        <v>18.42</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>29.29</v>
+        <v>29.62</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>17.62</v>
+        <v>15.61</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>17.56</v>
+        <v>16.22</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>21.94</v>
+        <v>21.68</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>22.34</v>
+        <v>33.83</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>18.5</v>
+        <v>32.28</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>1.18</v>
+        <v>0.92</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>13.25</v>
+        <v>15.03</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>-45.12</v>
+        <v>-36.18</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="Q25" s="10" t="n">
-        <v>-1.4</v>
+        <v>-1.75</v>
       </c>
       <c r="R25" s="17" t="n">
-        <v>65.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="S25" s="17" t="n">
-        <v>79.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>10.45</v>
+        <v>7.3</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>0.753</v>
+        <v>0.857</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>0.51</v>
+        <v>0.514</v>
       </c>
       <c r="W25" s="11" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="X25" s="17" t="n">
-        <v>80.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Y25" s="17" t="n">
-        <v>12.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>99.13</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="26">
@@ -34387,80 +34229,80 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>CANARA ROBECO SMALL CAP FUND - DIRECT PLAN - GROWTH OPTION</t>
+          <t>ICICI Prudential Smallcap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C26" s="20" t="n">
         <v>77.5</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>-4.64</v>
+        <v>-0.65</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>18.42</v>
+        <v>20.45</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>29.62</v>
+        <v>29.29</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>15.61</v>
+        <v>17.62</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>16.22</v>
+        <v>17.56</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>21.68</v>
+        <v>21.94</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>33.83</v>
+        <v>22.34</v>
       </c>
       <c r="K26" s="21" t="n">
-        <v>32.28</v>
+        <v>18.5</v>
       </c>
       <c r="L26" s="22" t="n">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>15.03</v>
+        <v>13.25</v>
       </c>
       <c r="O26" s="23" t="n">
-        <v>-36.18</v>
+        <v>-45.12</v>
       </c>
       <c r="P26" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="R26" s="24" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="S26" s="24" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="T26" s="21" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="U26" s="25" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="V26" s="25" t="n">
         <v>0.51</v>
       </c>
-      <c r="Q26" s="22" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="R26" s="24" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="S26" s="24" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="T26" s="21" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="U26" s="25" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="V26" s="25" t="n">
-        <v>0.514</v>
-      </c>
       <c r="W26" s="21" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="X26" s="24" t="n">
-        <v>89.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="Y26" s="24" t="n">
-        <v>6.5</v>
+        <v>12.6</v>
       </c>
       <c r="Z26" s="19" t="n">
-        <v>42.7</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="27">
@@ -34877,78 +34719,80 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>Axis Nifty Smallcap 50 Index Fund - Direct Plan - Growth Option</t>
+          <t>Sundaram Emerging Small Cap Series II Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C32" s="20" t="n">
         <v>76.5</v>
       </c>
-      <c r="D32" s="23" t="n">
-        <v>-4.69</v>
+      <c r="D32" s="21" t="n">
+        <v>4.68</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>26.07</v>
+        <v>44.23</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>13.01</v>
+        <v>12.39</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>6.31</v>
+        <v>6.01</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>22.84</v>
+        <v>29.88</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>22.67</v>
+        <v>22.54</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="K32" s="23" t="n"/>
+        <v>23.37</v>
+      </c>
+      <c r="K32" s="21" t="n">
+        <v>23.55</v>
+      </c>
       <c r="L32" s="22" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>1.36</v>
+        <v>2.81</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>19.51</v>
+        <v>16.66</v>
       </c>
       <c r="O32" s="23" t="n">
-        <v>-27.74</v>
+        <v>-46.9</v>
       </c>
       <c r="P32" s="22" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>-2.05</v>
+        <v>-1.66</v>
       </c>
       <c r="R32" s="24" t="n">
-        <v>123.5</v>
+        <v>51.6</v>
       </c>
       <c r="S32" s="24" t="n">
-        <v>97.7</v>
+        <v>73.2</v>
       </c>
       <c r="T32" s="21" t="n">
-        <v>11.86</v>
+        <v>23.68</v>
       </c>
       <c r="U32" s="25" t="n">
-        <v>1.085</v>
+        <v>0.706</v>
       </c>
       <c r="V32" s="25" t="n">
-        <v>0.488</v>
+        <v>0.521</v>
       </c>
       <c r="W32" s="21" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="X32" s="24" t="n">
-        <v>88.2</v>
+        <v>69.5</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="Z32" s="19" t="n">
-        <v>18.3443</v>
+        <v>18.0288</v>
       </c>
     </row>
     <row r="33">
@@ -34957,80 +34801,78 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Emerging Small Cap Series II Direct Plan - Growth</t>
+          <t>Axis Nifty Smallcap 50 Index Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
         <v>76.5</v>
       </c>
-      <c r="D33" s="11" t="n">
-        <v>4.68</v>
+      <c r="D33" s="13" t="n">
+        <v>-4.69</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>44.23</v>
+        <v>26.07</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>12.39</v>
+        <v>13.01</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>6.01</v>
+        <v>6.31</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>29.88</v>
+        <v>22.84</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>22.54</v>
+        <v>22.67</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <v>23.55</v>
-      </c>
+        <v>34.68</v>
+      </c>
+      <c r="K33" s="13" t="n"/>
       <c r="L33" s="10" t="n">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>2.81</v>
+        <v>1.36</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>16.66</v>
+        <v>19.51</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>-46.9</v>
+        <v>-27.74</v>
       </c>
       <c r="P33" s="10" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="Q33" s="10" t="n">
-        <v>-1.66</v>
+        <v>-2.05</v>
       </c>
       <c r="R33" s="17" t="n">
-        <v>51.6</v>
+        <v>123.5</v>
       </c>
       <c r="S33" s="17" t="n">
-        <v>73.2</v>
+        <v>97.7</v>
       </c>
       <c r="T33" s="11" t="n">
-        <v>23.68</v>
+        <v>11.86</v>
       </c>
       <c r="U33" s="18" t="n">
-        <v>0.706</v>
+        <v>1.085</v>
       </c>
       <c r="V33" s="18" t="n">
-        <v>0.521</v>
+        <v>0.488</v>
       </c>
       <c r="W33" s="11" t="n">
-        <v>1.11</v>
+        <v>0.88</v>
       </c>
       <c r="X33" s="17" t="n">
-        <v>69.5</v>
+        <v>88.2</v>
       </c>
       <c r="Y33" s="17" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>18.0288</v>
+        <v>18.3443</v>
       </c>
     </row>
     <row r="34">
@@ -41815,7 +41657,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Balanced Advantage Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Balanced Advantage Fund Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -42303,7 +42145,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Sundaram Dynamic Asset Allocation Fund Direct Plan - Growth</t>
+          <t>Sundaram Balanced Advantage Fund ( Formerly Known as Principal Balanced Advantage Fund) - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -46132,7 +45974,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Mirae Asset Corporate Bond Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Corporate Bond Fund Direct Growth Plan</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -47943,48 +47785,48 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Axis Liquid Fund - Direct Plan - Growth Option</t>
+          <t>Franklin India Liquid Fund - Super Institutional - Direct - Growth</t>
         </is>
       </c>
       <c r="C17" s="28" t="n">
         <v>45.2</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>7.11</v>
+        <v>7.12</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>6.31</v>
+        <v>6.35</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>6.49</v>
+        <v>6.54</v>
       </c>
       <c r="L17" s="10" t="n">
-        <v>-15.49</v>
+        <v>-15.6</v>
       </c>
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>37.42</v>
+        <v>44.25</v>
       </c>
       <c r="Q17" s="10" t="n">
         <v>0.01</v>
@@ -47996,13 +47838,13 @@
         <v>-6.4</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
       <c r="U17" s="18" t="n">
         <v>0.001</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="W17" s="13" t="n">
         <v>-0.6899999999999999</v>
@@ -48014,7 +47856,7 @@
         <v>12.6</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>2956.9343</v>
+        <v>3996.7166</v>
       </c>
     </row>
     <row r="18">
@@ -48023,48 +47865,48 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>BANK OF INDIA Liquid Fund- Direct Plan- Growth</t>
+          <t>Axis Liquid Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
         <v>45.2</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>7.07</v>
+        <v>7.11</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>6.28</v>
+        <v>6.31</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>7.16</v>
+        <v>7.18</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>6.53</v>
+        <v>6.55</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="L18" s="22" t="n">
-        <v>-16.25</v>
+        <v>-15.49</v>
       </c>
       <c r="M18" s="22" t="n"/>
       <c r="N18" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>44.38</v>
+        <v>37.42</v>
       </c>
       <c r="Q18" s="22" t="n">
         <v>0.01</v>
@@ -48073,10 +47915,10 @@
         <v>1.5</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>-6.3</v>
+        <v>-6.4</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="U18" s="25" t="n">
         <v>0.001</v>
@@ -48094,7 +47936,7 @@
         <v>12.6</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>3062.4281</v>
+        <v>2956.9343</v>
       </c>
     </row>
     <row r="19">
@@ -48103,48 +47945,48 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Baroda BNP Paribas LIQUID FUND - DIRECT PLAN - GROWTH OPTION</t>
+          <t>BANK OF INDIA Liquid Fund- Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C19" s="28" t="n">
         <v>45.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>7.02</v>
+        <v>7.07</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>7.07</v>
+        <v>7.1</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5.7</v>
+        <v>5.69</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>6.33</v>
+        <v>6.28</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>7.12</v>
+        <v>7.16</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>6.82</v>
+        <v>6.77</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>6.52</v>
+        <v>6.46</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>-16</v>
+        <v>-16.25</v>
       </c>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>-0.21</v>
+        <v>-0.16</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>33.67</v>
+        <v>44.38</v>
       </c>
       <c r="Q19" s="10" t="n">
         <v>0.01</v>
@@ -48156,7 +47998,7 @@
         <v>-6.3</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="U19" s="18" t="n">
         <v>0.001</v>
@@ -48174,7 +48016,7 @@
         <v>12.6</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>3065.3804</v>
+        <v>3062.4281</v>
       </c>
     </row>
     <row r="20">
@@ -48183,48 +48025,48 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Franklin India Liquid Fund - Super Institutional - Direct - Growth</t>
+          <t>Baroda BNP Paribas LIQUID FUND - DIRECT PLAN - GROWTH OPTION</t>
         </is>
       </c>
       <c r="C20" s="29" t="n">
         <v>45.2</v>
       </c>
       <c r="D20" s="21" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H20" s="21" t="n">
         <v>7.12</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>7.17</v>
       </c>
       <c r="I20" s="21" t="n">
         <v>6.52</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="K20" s="21" t="n">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
       <c r="L20" s="22" t="n">
-        <v>-15.6</v>
+        <v>-16</v>
       </c>
       <c r="M20" s="22" t="n"/>
       <c r="N20" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>-0.16</v>
+        <v>-0.21</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>44.25</v>
+        <v>33.67</v>
       </c>
       <c r="Q20" s="22" t="n">
         <v>0.01</v>
@@ -48233,16 +48075,16 @@
         <v>1.5</v>
       </c>
       <c r="S20" s="24" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="T20" s="21" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="U20" s="25" t="n">
         <v>0.001</v>
       </c>
       <c r="V20" s="25" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="W20" s="23" t="n">
         <v>-0.6899999999999999</v>
@@ -48254,7 +48096,7 @@
         <v>12.6</v>
       </c>
       <c r="Z20" s="19" t="n">
-        <v>3996.7166</v>
+        <v>3065.3804</v>
       </c>
     </row>
     <row r="21">
@@ -49143,48 +48985,48 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>PGIM India Liquid Fund - Direct Plan - Growth</t>
+          <t>Mahindra Manulife Liquid Fund - Direct Plan -Growth</t>
         </is>
       </c>
       <c r="C32" s="29" t="n">
         <v>44.7</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>7.09</v>
+        <v>7.07</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>7.11</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>5.89</v>
+        <v>5.64</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>6.54</v>
+        <v>6.55</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="K32" s="21" t="n">
-        <v>5.76</v>
+        <v>5.71</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>-14.64</v>
+        <v>-17.57</v>
       </c>
       <c r="M32" s="22" t="n"/>
       <c r="N32" s="22" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="O32" s="22" t="n">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="P32" s="22" t="n">
-        <v>47.4</v>
+        <v>32.32</v>
       </c>
       <c r="Q32" s="22" t="n">
         <v>0.01</v>
@@ -49196,13 +49038,13 @@
         <v>-6.4</v>
       </c>
       <c r="T32" s="21" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="U32" s="25" t="n">
         <v>0.001</v>
       </c>
       <c r="V32" s="25" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="W32" s="23" t="n">
         <v>-0.6899999999999999</v>
@@ -49211,10 +49053,10 @@
         <v>100</v>
       </c>
       <c r="Y32" s="24" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z32" s="19" t="n">
-        <v>346.8917</v>
+        <v>1731.8087</v>
       </c>
     </row>
     <row r="33">
@@ -49223,48 +49065,48 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Liquid Fund - Direct Plan -Growth</t>
+          <t>PGIM India Liquid Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C33" s="28" t="n">
         <v>44.7</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>7.07</v>
+        <v>7.09</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>7.11</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5.73</v>
+        <v>5.7</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>5.64</v>
+        <v>5.89</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>7.17</v>
+        <v>7.18</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>6.55</v>
+        <v>6.54</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>6.08</v>
+        <v>6.09</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>5.71</v>
+        <v>5.76</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>-17.57</v>
+        <v>-14.64</v>
       </c>
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="O33" s="10" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="P33" s="10" t="n">
-        <v>32.32</v>
+        <v>47.4</v>
       </c>
       <c r="Q33" s="10" t="n">
         <v>0.01</v>
@@ -49276,13 +49118,13 @@
         <v>-6.4</v>
       </c>
       <c r="T33" s="11" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="U33" s="18" t="n">
         <v>0.001</v>
       </c>
       <c r="V33" s="18" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="W33" s="13" t="n">
         <v>-0.6899999999999999</v>
@@ -49291,10 +49133,10 @@
         <v>100</v>
       </c>
       <c r="Y33" s="17" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>1731.8087</v>
+        <v>346.8917</v>
       </c>
     </row>
     <row r="34">
@@ -51395,7 +51237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -52166,80 +52008,80 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>SBI ULTRA SHORT DURATION FUND - DIRECT PLAN - GROWTH</t>
+          <t>Nippon India Ultra Short Duration Fund- Direct Plan- Growth Option</t>
         </is>
       </c>
       <c r="C10" s="27" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>7.62</v>
+        <v>8.02</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>7.31</v>
+        <v>7.67</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>6.74</v>
+        <v>4.71</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>7.52</v>
+        <v>7.88</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>6.75</v>
+        <v>7.57</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>7.13</v>
+        <v>6.26</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>6.87</v>
+        <v>6.51</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>3.33</v>
+        <v>4.32</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>6.69</v>
+        <v>9.24</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>-0.95</v>
+        <v>-5.24</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>7.69</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" s="22" t="n">
         <v>0.01</v>
       </c>
       <c r="R10" s="24" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S10" s="24" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10</v>
       </c>
       <c r="T10" s="21" t="n">
-        <v>7.6</v>
+        <v>8.01</v>
       </c>
       <c r="U10" s="25" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V10" s="25" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="W10" s="23" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="X10" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y10" s="24" t="n">
-        <v>12.6</v>
+        <v>7.3</v>
       </c>
       <c r="Z10" s="19" t="n">
-        <v>6140.166</v>
+        <v>4488.7441</v>
       </c>
     </row>
     <row r="11">
@@ -52248,80 +52090,80 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Axis Ultra Short Duration Fund - Direct Plan Growth</t>
+          <t>SBI ULTRA SHORT DURATION FUND - DIRECT PLAN - GROWTH</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>62.2</v>
+        <v>62.6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>7.93</v>
+        <v>7.62</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6.29</v>
+        <v>5.9</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>4.66</v>
+        <v>6.74</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>7.78</v>
+        <v>7.52</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>7.06</v>
+        <v>6.75</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>6.5</v>
+        <v>7.13</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>5.97</v>
+        <v>6.87</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>4.03</v>
+        <v>3.33</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>10.3</v>
+        <v>6.69</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.95</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>9.359999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="Q11" s="10" t="n">
         <v>0.01</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S11" s="17" t="n">
-        <v>-9.9</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>7.89</v>
+        <v>7.6</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="W11" s="13" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="X11" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y11" s="17" t="n">
-        <v>6.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>15.7895</v>
+        <v>6140.166</v>
       </c>
     </row>
     <row r="12">
@@ -52330,80 +52172,80 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>BANK OF INDIA Ultra Short Duration Fund- Direct Plan- Growth</t>
+          <t>Axis Ultra Short Duration Fund - Direct Plan Growth</t>
         </is>
       </c>
       <c r="C12" s="27" t="n">
-        <v>61.7</v>
+        <v>62.2</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>7.42</v>
+        <v>7.93</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>6.94</v>
+        <v>7.58</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>5.59</v>
+        <v>6.29</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>6.77</v>
+        <v>4.66</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>7.15</v>
+        <v>7.78</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>6.42</v>
+        <v>7.06</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>7.26</v>
+        <v>6.5</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>7.03</v>
+        <v>5.97</v>
       </c>
       <c r="L12" s="22" t="n">
-        <v>2.35</v>
+        <v>4.03</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>6.14</v>
+        <v>10.3</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O12" s="22" t="n">
-        <v>-0.76</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>9.130000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q12" s="22" t="n">
         <v>0.01</v>
       </c>
       <c r="R12" s="24" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S12" s="24" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="T12" s="21" t="n">
-        <v>7.25</v>
+        <v>7.89</v>
       </c>
       <c r="U12" s="25" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V12" s="25" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="W12" s="23" t="n">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="X12" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y12" s="24" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
       <c r="Z12" s="19" t="n">
-        <v>3302.6183</v>
+        <v>15.7895</v>
       </c>
     </row>
     <row r="13">
@@ -52412,50 +52254,50 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Ultra Short Duration Fund - Direct Plan -Growth</t>
+          <t>Baroda BNP Paribas Ultra Short Duration Fund- Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>7.76</v>
+        <v>7.7</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7.44</v>
+        <v>7.45</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6.03</v>
+        <v>6.09</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>3.59</v>
+        <v>4.66</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>7.63</v>
+        <v>7.59</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>6.88</v>
+        <v>6.9</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>12.44</v>
+        <v>11.74</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>0.34</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>14.88</v>
+        <v>7.45</v>
       </c>
       <c r="Q13" s="10" t="n">
         <v>0.01</v>
@@ -52464,7 +52306,7 @@
         <v>2.5</v>
       </c>
       <c r="S13" s="17" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T13" s="11" t="n">
         <v>7.77</v>
@@ -52473,7 +52315,7 @@
         <v>0.002</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="W13" s="13" t="n">
         <v>-0.38</v>
@@ -52482,10 +52324,10 @@
         <v>100</v>
       </c>
       <c r="Y13" s="17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>1423.423</v>
+        <v>1577.9903</v>
       </c>
     </row>
     <row r="14">
@@ -52494,80 +52336,80 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>HSBC Ultra Short Duration Fund - Direct Growth</t>
+          <t>BANK OF INDIA Ultra Short Duration Fund- Direct Plan- Growth</t>
         </is>
       </c>
       <c r="C14" s="27" t="n">
-        <v>61.2</v>
+        <v>61.7</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>7.69</v>
+        <v>7.42</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>7.38</v>
+        <v>6.94</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>5.98</v>
+        <v>5.59</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>3.32</v>
+        <v>6.77</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>7.57</v>
+        <v>7.15</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>6.83</v>
+        <v>6.42</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>5.85</v>
+        <v>7.26</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>5.83</v>
+        <v>7.03</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>3.62</v>
+        <v>2.35</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>9.720000000000001</v>
+        <v>6.14</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>-0.96</v>
+        <v>-0.76</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>7.69</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q14" s="22" t="n">
         <v>0.01</v>
       </c>
       <c r="R14" s="24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S14" s="24" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T14" s="21" t="n">
-        <v>7.7</v>
+        <v>7.25</v>
       </c>
       <c r="U14" s="25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V14" s="25" t="n">
         <v>0.002</v>
       </c>
-      <c r="V14" s="25" t="n">
-        <v>0.004</v>
-      </c>
       <c r="W14" s="23" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="X14" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y14" s="24" t="n">
-        <v>5.6</v>
+        <v>12.6</v>
       </c>
       <c r="Z14" s="19" t="n">
-        <v>1386.5435</v>
+        <v>3302.6183</v>
       </c>
     </row>
     <row r="15">
@@ -52576,80 +52418,80 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>UTI Short Duration Fund - Direct Plan - Growth Option</t>
+          <t>Mirae Asset Ultra Short Duration Fund Direct Growth</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>59.7</v>
+        <v>61.5</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>8.66</v>
+        <v>7.9</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>7.99</v>
+        <v>7.51</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7.67</v>
+        <v>5.96</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>6.9</v>
+        <v>2.94</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>8.289999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>7.85</v>
+        <v>7.04</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>7.43</v>
+        <v>6.19</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>7.02</v>
+        <v>6.29</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>2.47</v>
+        <v>4.06</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>3.56</v>
+        <v>12.87</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>-13.16</v>
+        <v>-0.16</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>0.61</v>
+        <v>46.94</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R15" s="17" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="S15" s="17" t="n">
-        <v>-8.9</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>8.24</v>
+        <v>7.84</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>0.027</v>
+        <v>0.005</v>
       </c>
       <c r="W15" s="13" t="n">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="X15" s="17" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="17" t="n">
-        <v>12.6</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>34.0857</v>
+        <v>1335.9388</v>
       </c>
     </row>
     <row r="16">
@@ -52658,160 +52500,162 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Bandhan Short Duration Fund - Direct Plan - Growth</t>
+          <t>Mirae Asset Short Duration Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C16" s="27" t="n">
-        <v>59.6</v>
+        <v>61.4</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>8.66</v>
+        <v>8.91</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>7.75</v>
+        <v>7.86</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>6.28</v>
+        <v>6.48</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>7.49</v>
+        <v>5.33</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>7.18</v>
+        <v>7.32</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>7.89</v>
+        <v>7.3</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>7.61</v>
+        <v>6.51</v>
       </c>
       <c r="L16" s="22" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="N16" s="22" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="O16" s="22" t="n">
-        <v>-2.55</v>
+        <v>-2.2</v>
       </c>
       <c r="P16" s="22" t="n">
-        <v>3.04</v>
+        <v>3.57</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="R16" s="24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="S16" s="24" t="n">
-        <v>-6.6</v>
+        <v>-7.8</v>
       </c>
       <c r="T16" s="21" t="n">
-        <v>7.85</v>
+        <v>8.07</v>
       </c>
       <c r="U16" s="25" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="V16" s="25" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="W16" s="23" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="X16" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y16" s="24" t="n">
-        <v>12.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z16" s="19" t="n">
-        <v>61.7129</v>
+        <v>16.8568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Short Duration Fund - Direct Plan -Growth</t>
+          <t>Mahindra Manulife Ultra Short Duration Fund - Direct Plan -Growth</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>59.5</v>
+        <v>61.4</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>8.91</v>
+        <v>7.76</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>8.02</v>
+        <v>7.44</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6.07</v>
+        <v>6.03</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>2.99</v>
+        <v>3.59</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>8.550000000000001</v>
+        <v>7.63</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>7.69</v>
+        <v>6.88</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="K17" s="13" t="n"/>
+        <v>5.95</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>5.78</v>
+      </c>
       <c r="L17" s="10" t="n">
-        <v>2.29</v>
+        <v>3.85</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>3.07</v>
+        <v>12.44</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0.83</v>
+        <v>0.34</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>-1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="P17" s="10" t="n">
-        <v>7.29</v>
+        <v>14.88</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R17" s="17" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="S17" s="17" t="n">
-        <v>-8</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>8.23</v>
+        <v>7.77</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>0.041</v>
+        <v>0.004</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="X17" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>13.4328</v>
+        <v>1423.423</v>
       </c>
     </row>
     <row r="18">
@@ -52820,78 +52664,80 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Sundaram Short Duration Fund (Formerly Known as Principal Short Term Debt Fund)- Direct Plan - Growth Option</t>
+          <t>BANDHAN ULTRA SHORT DURATION FUND - DIRECT PLAN GROWTH</t>
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>59</v>
+        <v>61.3</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>8.75</v>
+        <v>7.6</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>7.9</v>
+        <v>7.28</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>5.08</v>
+        <v>5.83</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>2.51</v>
+        <v>4.51</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>8.27</v>
+        <v>7.49</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>8</v>
+        <v>6.72</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K18" s="23" t="n"/>
+        <v>6.16</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <v>5.56</v>
+      </c>
       <c r="L18" s="22" t="n">
-        <v>2.18</v>
+        <v>3.23</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>3.12</v>
+        <v>6.33</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>0.82</v>
+        <v>0.34</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>-0.67</v>
+        <v>-0.89</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>11.79</v>
+        <v>8.18</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>8.119999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.036</v>
+        <v>0.004</v>
       </c>
       <c r="W18" s="23" t="n">
-        <v>-0.35</v>
+        <v>-0.4</v>
       </c>
       <c r="X18" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>48.3358</v>
+        <v>15.5569</v>
       </c>
     </row>
     <row r="19">
@@ -52900,80 +52746,80 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>CANARA ROBECO SHORT DURATION FUND - DIRECT PLAN - GROWTH OPTION</t>
+          <t>HSBC Ultra Short Duration Fund - Direct Growth</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
-        <v>58.5</v>
+        <v>61.2</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>7.29</v>
+        <v>7.38</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>7.25</v>
+        <v>3.32</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>7.74</v>
+        <v>7.57</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>6.74</v>
+        <v>6.83</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>7.34</v>
+        <v>5.85</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>7.18</v>
+        <v>5.83</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>1.51</v>
+        <v>3.62</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>2.15</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>-2.15</v>
+        <v>-0.96</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>3.39</v>
+        <v>7.69</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="R19" s="17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>-7.2</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>7.46</v>
+        <v>7.7</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>0.046</v>
+        <v>0.004</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="X19" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y19" s="17" t="n">
-        <v>12.6</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>27.9368</v>
+        <v>1386.5435</v>
       </c>
     </row>
     <row r="20">
@@ -52982,78 +52828,80 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Edelweiss CRISIL IBX 50:50 Gilt Plus SDL Short Duration Index fund - Direct Plan - Growth</t>
+          <t>WhiteOak Capital Ultra Short Duration Fund- Direct plan-Growth Option</t>
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>58.4</v>
+        <v>60.9</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>8.09</v>
+        <v>7.48</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>6.75</v>
+        <v>7.16</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>4</v>
+        <v>6.04</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>1.98</v>
+        <v>3.58</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>8.109999999999999</v>
+        <v>7.34</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>8.109999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="K20" s="23" t="n"/>
+        <v>5.62</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>5.46</v>
+      </c>
       <c r="L20" s="22" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>3.37</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>0.91</v>
+        <v>0.33</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>-0.43</v>
+        <v>-0.16</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>15.7</v>
+        <v>44.75</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R20" s="24" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="S20" s="24" t="n">
-        <v>-9.1</v>
+        <v>-9.5</v>
       </c>
       <c r="T20" s="21" t="n">
-        <v>8.380000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="U20" s="25" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="V20" s="25" t="n">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="W20" s="23" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="X20" s="24" t="n">
         <v>100</v>
       </c>
       <c r="Y20" s="24" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z20" s="19" t="n">
-        <v>12.1865</v>
+        <v>1423.2937</v>
       </c>
     </row>
     <row r="21">
@@ -53062,78 +52910,80 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>HSBC Short Duration Fund - Direct Growth</t>
+          <t>LIC MF Short Duration Fund-Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
-        <v>58.1</v>
+        <v>60.3</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>8.76</v>
+        <v>8.75</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>7.19</v>
+        <v>7.76</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4.26</v>
+        <v>6.15</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>2.11</v>
+        <v>4.63</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="K21" s="13" t="n"/>
+        <v>6.65</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>5.71</v>
+      </c>
       <c r="L21" s="10" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="O21" s="10" t="n">
-        <v>-0.48</v>
+        <v>-2.28</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>14.98</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R21" s="17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="S21" s="17" t="n">
-        <v>-8</v>
+        <v>-7.5</v>
       </c>
       <c r="T21" s="11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="U21" s="18" t="n">
         <v>0.014</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>-0.27</v>
+        <v>-0.36</v>
       </c>
       <c r="X21" s="17" t="n">
         <v>100</v>
       </c>
       <c r="Y21" s="17" t="n">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>28.3353</v>
+        <v>15.7098</v>
       </c>
     </row>
     <row r="22">
@@ -53142,74 +52992,80 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Nippon India Ultra Short Duration Fund - Segregated Portfolio 1 - Direct Plan - Growth Option</t>
+          <t>LIC MF Ultra Short Duration Fund-Direct Plan-Growth</t>
         </is>
       </c>
       <c r="C22" s="27" t="n">
-        <v>57.9</v>
+        <v>60.2</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>195.09</v>
+        <v>7.67</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>30.74</v>
+        <v>7</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>17.45</v>
+        <v>5.62</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>8.369999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>236.88</v>
+        <v>7.35</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>236.88</v>
-      </c>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="23" t="n"/>
+        <v>6.52</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <v>5.27</v>
+      </c>
       <c r="L22" s="22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M22" s="22" t="n"/>
+        <v>2.54</v>
+      </c>
+      <c r="M22" s="22" t="n">
+        <v>6.74</v>
+      </c>
       <c r="N22" s="22" t="n">
-        <v>224.83</v>
-      </c>
-      <c r="O22" s="23" t="n">
-        <v>-38.82</v>
+        <v>0.33</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>-1.31</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.79</v>
+        <v>5.34</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R22" s="24" t="n">
-        <v>-3.9</v>
+        <v>2.3</v>
       </c>
       <c r="S22" s="24" t="n">
-        <v>-9194.799999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T22" s="21" t="n">
-        <v>409.94</v>
+        <v>7.31</v>
       </c>
       <c r="U22" s="25" t="n">
-        <v>-0.289</v>
+        <v>0.002</v>
       </c>
       <c r="V22" s="25" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="W22" s="21" t="n">
-        <v>0.59</v>
+        <v>0.004</v>
+      </c>
+      <c r="W22" s="23" t="n">
+        <v>-0.42</v>
       </c>
       <c r="X22" s="24" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="24" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z22" s="19" t="n">
-        <v>101.752</v>
+        <v>1363.6699</v>
       </c>
     </row>
     <row r="23">
@@ -53218,148 +53074,148 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>PGIM India Ultra Short Duration Fund - Direct Plan - Growth</t>
+          <t>UTI Short Duration Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>7.6</v>
+        <v>8.66</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>7.29</v>
+        <v>7.99</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5.98</v>
+        <v>7.67</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>7.03</v>
+        <v>6.9</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>7.47</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>6.77</v>
+        <v>7.85</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>7.4</v>
+        <v>7.43</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>7.29</v>
+        <v>7.02</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>3.39</v>
+        <v>2.47</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>12.42</v>
+        <v>3.56</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="O23" s="13" t="n">
-        <v>-30.29</v>
+        <v>0.76</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>-13.16</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>0.24</v>
+        <v>0.61</v>
       </c>
       <c r="Q23" s="10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="R23" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" s="17" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="U23" s="18" t="n">
         <v>0.01</v>
       </c>
-      <c r="R23" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S23" s="17" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="T23" s="11" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="U23" s="18" t="n">
-        <v>0.002</v>
-      </c>
       <c r="V23" s="18" t="n">
-        <v>0.003</v>
+        <v>0.027</v>
       </c>
       <c r="W23" s="13" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>99.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Y23" s="17" t="n">
-        <v>9.5</v>
+        <v>12.6</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>35.9771</v>
+        <v>34.0857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>TRUSTMF Short Duration Fund-Direct Plan-Growth</t>
+          <t>Sundaram Ultra Short Duration Fund (Formerly Known as Principal Ultra Short Term Fund)- Direct Plan -Growth Option</t>
         </is>
       </c>
       <c r="C24" s="27" t="n">
-        <v>56.1</v>
+        <v>59.7</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>8.73</v>
+        <v>7.79</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>7.54</v>
+        <v>7.46</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>5.2</v>
+        <v>4.97</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>7.53</v>
+        <v>7.49</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>6.61</v>
+        <v>7.22</v>
       </c>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="22" t="n">
-        <v>1.66</v>
+        <v>3.9</v>
       </c>
       <c r="M24" s="22" t="n">
-        <v>2.43</v>
+        <v>16.62</v>
       </c>
       <c r="N24" s="22" t="n">
-        <v>0.84</v>
+        <v>0.34</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>-1.07</v>
+        <v>-0.16</v>
       </c>
       <c r="P24" s="22" t="n">
-        <v>7.05</v>
+        <v>46.62</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R24" s="24" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="S24" s="24" t="n">
-        <v>-7.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="T24" s="21" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="U24" s="25" t="n">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="V24" s="25" t="n">
-        <v>0.048</v>
+        <v>0.004</v>
       </c>
       <c r="W24" s="23" t="n">
         <v>-0.38</v>
@@ -53368,10 +53224,10 @@
         <v>100</v>
       </c>
       <c r="Y24" s="24" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Z24" s="19" t="n">
-        <v>1289.2273</v>
+        <v>2958.95</v>
       </c>
     </row>
     <row r="25">
@@ -53380,74 +53236,80 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Franklin India Ultra Short Duration Fund - Direct - Growth</t>
+          <t>Bandhan Short Duration Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
-        <v>50.7</v>
+        <v>59.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>7.84</v>
+        <v>8.66</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>2.55</v>
+        <v>7.75</v>
       </c>
       <c r="F25" s="11" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>1.52</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="10" t="n">
-        <v>4.47</v>
-      </c>
       <c r="M25" s="10" t="n">
-        <v>17.15</v>
+        <v>2.2</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>-0.05</v>
+        <v>-2.55</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>51</v>
+        <v>3.04</v>
       </c>
       <c r="Q25" s="10" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R25" s="17" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="S25" s="17" t="n">
-        <v>-11</v>
+        <v>-6.6</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>8.43</v>
+        <v>7.85</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="11" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="X25" s="17" t="n"/>
+        <v>0.05</v>
+      </c>
+      <c r="W25" s="13" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="Y25" s="17" t="n">
-        <v>1</v>
+        <v>12.6</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>10.7836</v>
+        <v>61.7129</v>
       </c>
     </row>
     <row r="26">
@@ -53456,80 +53318,78 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>JM Ultra Short Duration Fund - (Direct) - Growth Option</t>
-        </is>
-      </c>
-      <c r="C26" s="29" t="n">
-        <v>45</v>
+          <t>Mahindra Manulife Short Duration Fund - Direct Plan -Growth</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>59.5</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>5.85</v>
+        <v>8.91</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>4.76</v>
+        <v>8.02</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>6.26</v>
+        <v>6.07</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>5.63</v>
+        <v>2.99</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>4.77</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>5.35</v>
+        <v>7.69</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>7.49</v>
-      </c>
+        <v>6.63</v>
+      </c>
+      <c r="K26" s="23" t="n"/>
       <c r="L26" s="22" t="n">
-        <v>-0.36</v>
+        <v>2.29</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>-0.13</v>
+        <v>3.07</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>4.1</v>
+        <v>0.83</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>-5.5</v>
+        <v>-1.1</v>
       </c>
       <c r="P26" s="22" t="n">
-        <v>0.87</v>
+        <v>7.29</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R26" s="24" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="S26" s="24" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="T26" s="21" t="n">
-        <v>4.99</v>
+        <v>8.23</v>
       </c>
       <c r="U26" s="25" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="V26" s="25" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="W26" s="23" t="n">
-        <v>-0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="X26" s="24" t="n">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="Y26" s="24" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z26" s="19" t="n">
-        <v>27.5938</v>
+        <v>13.4328</v>
       </c>
     </row>
     <row r="27">
@@ -53538,80 +53398,78 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>HSBC Short Duration Fund - Direct Growth</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="n">
-        <v>40.9</v>
+          <t>ITI Ultra Short Duration Fund - Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>59.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>3.01</v>
+        <v>7.42</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>4.51</v>
+        <v>7.19</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>6.35</v>
+        <v>2.59</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>4.28</v>
+        <v>7.35</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>4.06</v>
+        <v>6.93</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>6.36</v>
-      </c>
+        <v>6.34</v>
+      </c>
+      <c r="K27" s="13" t="n"/>
       <c r="L27" s="10" t="n">
-        <v>-0.2</v>
+        <v>3.2</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>-0.15</v>
+        <v>12.44</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>7.46</v>
+        <v>0.33</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>-10.15</v>
+        <v>-0.19</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0.44</v>
+        <v>37.84</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="R27" s="17" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="S27" s="17" t="n">
-        <v>-2.8</v>
+        <v>-9.4</v>
       </c>
       <c r="T27" s="11" t="n">
-        <v>4.71</v>
+        <v>7.52</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="W27" s="13" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="X27" s="17" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Y27" s="17" t="n">
-        <v>9.9</v>
+        <v>4.3</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>35.6582</v>
+        <v>1291.855</v>
       </c>
     </row>
     <row r="28">
@@ -53620,79 +53478,959 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
+          <t>Sundaram Short Duration Fund (Formerly Known as Principal Short Term Debt Fund)- Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>59</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M28" s="22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N28" s="22" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="P28" s="22" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="Q28" s="22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="R28" s="24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S28" s="24" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="T28" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="U28" s="25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="V28" s="25" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="W28" s="23" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X28" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y28" s="24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z28" s="19" t="n">
+        <v>48.3358</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>CANARA ROBECO SHORT DURATION FUND - DIRECT PLAN - GROWTH OPTION</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="P29" s="10" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="R29" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="U29" s="18" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V29" s="18" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="W29" s="13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Z29" s="8" t="n">
+        <v>27.9368</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Edelweiss CRISIL IBX 50:50 Gilt Plus SDL Short Duration Index fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="J30" s="21" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O30" s="22" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="P30" s="22" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="Q30" s="22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R30" s="24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S30" s="24" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="T30" s="21" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="U30" s="25" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="V30" s="25" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="W30" s="23" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="X30" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y30" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z30" s="19" t="n">
+        <v>12.1865</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>HSBC Short Duration Fund - Direct Growth</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="P31" s="10" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="Q31" s="10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="R31" s="17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T31" s="11" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="U31" s="18" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="V31" s="18" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="W31" s="13" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y31" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>28.3353</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Nippon India Ultra Short Duration Fund - Segregated Portfolio 1 - Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>195.09</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>236.88</v>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>236.88</v>
+      </c>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="23" t="n"/>
+      <c r="L32" s="22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n">
+        <v>224.83</v>
+      </c>
+      <c r="O32" s="23" t="n">
+        <v>-38.82</v>
+      </c>
+      <c r="P32" s="22" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="24" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="S32" s="24" t="n">
+        <v>-9194.799999999999</v>
+      </c>
+      <c r="T32" s="21" t="n">
+        <v>409.94</v>
+      </c>
+      <c r="U32" s="25" t="n">
+        <v>-0.289</v>
+      </c>
+      <c r="V32" s="25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="W32" s="21" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X32" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z32" s="19" t="n">
+        <v>101.752</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>PGIM India Ultra Short Duration Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>-30.29</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R33" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="T33" s="11" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="U33" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V33" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="W33" s="13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z33" s="8" t="n">
+        <v>35.9771</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>JM Short Duration Fund (Direct) - Growth</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="J34" s="21" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="K34" s="23" t="n"/>
+      <c r="L34" s="22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M34" s="22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O34" s="22" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="P34" s="22" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="Q34" s="22" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="R34" s="24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S34" s="24" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="T34" s="21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="U34" s="25" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V34" s="25" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="W34" s="23" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X34" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y34" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="19" t="n">
+        <v>12.4262</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>TRUSTMF Short Duration Fund-Direct Plan-Growth</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="U35" s="18" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="V35" s="18" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="W35" s="13" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y35" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z35" s="8" t="n">
+        <v>1289.2273</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Franklin India Ultra Short Duration Fund - Direct - Growth</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="23" t="n"/>
+      <c r="L36" s="22" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="N36" s="22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O36" s="22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P36" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S36" s="24" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T36" s="21" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="U36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="X36" s="24" t="n"/>
+      <c r="Y36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="19" t="n">
+        <v>10.7836</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>JM Ultra Short Duration Fund - (Direct) - Growth Option</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="P37" s="10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q37" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="R37" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T37" s="11" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="U37" s="18" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="V37" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="13" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Y37" s="17" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z37" s="8" t="n">
+        <v>27.5938</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>HSBC Short Duration Fund - Direct Growth</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J38" s="21" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="L38" s="22" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M38" s="22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N38" s="22" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="O38" s="22" t="n">
+        <v>-10.15</v>
+      </c>
+      <c r="P38" s="22" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q38" s="22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="R38" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S38" s="24" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="T38" s="21" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="U38" s="25" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="V38" s="25" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="W38" s="23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X38" s="24" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Y38" s="24" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Z38" s="19" t="n">
+        <v>35.6582</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>PGIM India Short Duration Fund - Direct Plan - Growth</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C39" s="28" t="n">
         <v>33.9</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D39" s="11" t="n">
         <v>6.73</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E39" s="11" t="n">
         <v>4.94</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="F39" s="11" t="n">
         <v>4.77</v>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G39" s="11" t="n">
         <v>4.48</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="H39" s="11" t="n">
         <v>5.21</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I39" s="11" t="n">
         <v>5.21</v>
       </c>
-      <c r="J28" s="21" t="n">
+      <c r="J39" s="11" t="n">
         <v>5.59</v>
       </c>
-      <c r="K28" s="21" t="n">
+      <c r="K39" s="11" t="n">
         <v>5.05</v>
       </c>
-      <c r="L28" s="22" t="n">
+      <c r="L39" s="10" t="n">
         <v>-1.69</v>
       </c>
-      <c r="M28" s="22" t="n">
+      <c r="M39" s="10" t="n">
         <v>-1.93</v>
       </c>
-      <c r="N28" s="22" t="n">
+      <c r="N39" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="O28" s="23" t="n">
+      <c r="O39" s="13" t="n">
         <v>-36.31</v>
       </c>
-      <c r="P28" s="22" t="n">
+      <c r="P39" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="Q28" s="22" t="n">
+      <c r="Q39" s="10" t="n">
         <v>-0.05</v>
       </c>
-      <c r="R28" s="24" t="n">
+      <c r="R39" s="17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S28" s="24" t="n">
+      <c r="S39" s="17" t="n">
         <v>-4.2</v>
       </c>
-      <c r="T28" s="21" t="n">
+      <c r="T39" s="11" t="n">
         <v>5.04</v>
       </c>
-      <c r="U28" s="25" t="n">
+      <c r="U39" s="18" t="n">
         <v>0.005</v>
       </c>
-      <c r="V28" s="25" t="n">
+      <c r="V39" s="18" t="n">
         <v>0.007</v>
       </c>
-      <c r="W28" s="23" t="n">
+      <c r="W39" s="13" t="n">
         <v>-1.05</v>
       </c>
-      <c r="X28" s="24" t="n">
+      <c r="X39" s="17" t="n">
         <v>93</v>
       </c>
-      <c r="Y28" s="24" t="n">
+      <c r="Y39" s="17" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z28" s="19" t="n">
+      <c r="Z39" s="8" t="n">
         <v>42.8534</v>
       </c>
     </row>
@@ -55137,80 +55875,80 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Edelweiss ELSS Tax Saver Fund - Direct Plan-Growth Option</t>
+          <t>Quantum ELSS Tax Saver Fund - Direct Plan Growth Option</t>
         </is>
       </c>
       <c r="C18" s="20" t="n">
         <v>76.3</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>0.09</v>
+        <v>1.18</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>17.93</v>
+        <v>18.27</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>20.69</v>
+        <v>21.34</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>13.89</v>
+        <v>13.91</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>16.76</v>
+        <v>17.21</v>
       </c>
       <c r="I18" s="21" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="J18" s="21" t="n">
         <v>17.36</v>
       </c>
-      <c r="J18" s="21" t="n">
-        <v>17.68</v>
-      </c>
       <c r="K18" s="21" t="n">
-        <v>14.54</v>
+        <v>13.9</v>
       </c>
       <c r="L18" s="22" t="n">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="N18" s="22" t="n">
-        <v>13.37</v>
+        <v>11.57</v>
       </c>
       <c r="O18" s="23" t="n">
-        <v>-36.8</v>
+        <v>-39.62</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>-1.29</v>
+        <v>-1.14</v>
       </c>
       <c r="R18" s="24" t="n">
-        <v>101.9</v>
+        <v>85.3</v>
       </c>
       <c r="S18" s="24" t="n">
-        <v>97.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>4.59</v>
+        <v>6.57</v>
       </c>
       <c r="U18" s="25" t="n">
-        <v>0.998</v>
+        <v>0.863</v>
       </c>
       <c r="V18" s="25" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="W18" s="21" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="X18" s="24" t="n">
-        <v>84.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Y18" s="24" t="n">
-        <v>12.6</v>
+        <v>16.6</v>
       </c>
       <c r="Z18" s="19" t="n">
-        <v>129.81</v>
+        <v>130.54</v>
       </c>
     </row>
     <row r="19">
@@ -55219,80 +55957,80 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Quantum ELSS Tax Saver Fund - Direct Plan Growth Option</t>
+          <t>Edelweiss ELSS Tax Saver Fund - Direct Plan-Growth Option</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
         <v>76.3</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1.18</v>
+        <v>0.09</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>18.27</v>
+        <v>17.93</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>21.34</v>
+        <v>20.69</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>13.91</v>
+        <v>13.89</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>17.21</v>
+        <v>16.76</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>17.65</v>
+        <v>17.36</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>17.36</v>
+        <v>17.68</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>13.9</v>
+        <v>14.54</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>11.57</v>
+        <v>13.37</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>-39.62</v>
+        <v>-36.8</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>-1.14</v>
+        <v>-1.29</v>
       </c>
       <c r="R19" s="17" t="n">
-        <v>85.3</v>
+        <v>101.9</v>
       </c>
       <c r="S19" s="17" t="n">
-        <v>91.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>6.57</v>
+        <v>4.59</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>0.863</v>
+        <v>0.998</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>0.881</v>
+        <v>0.88</v>
       </c>
       <c r="W19" s="11" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="X19" s="17" t="n">
-        <v>83.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y19" s="17" t="n">
-        <v>16.6</v>
+        <v>12.6</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>130.54</v>
+        <v>129.81</v>
       </c>
     </row>
     <row r="20">
@@ -56931,7 +57669,7 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>NJ ELSS Tax Saver Fund Direct Growth</t>
+          <t>NJ ELSS Tax Saver Scheme Direct Growth</t>
         </is>
       </c>
       <c r="C40" s="27" t="n">
@@ -57938,80 +58676,80 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>HDFC Flexi Cap Fund - Growth Option - Direct Plan</t>
+          <t>Edelweiss Flexi Cap Fund - Direct Plan - Growth Option</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
         <v>82.7</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>8.01</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>23.56</v>
+        <v>20.36</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>28.09</v>
+        <v>23.35</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>17.08</v>
+        <v>15.81</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>22.3</v>
+        <v>19.34</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>24.22</v>
+        <v>19.81</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>20.97</v>
+        <v>19.26</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>16.86</v>
+        <v>17.25</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>2.21</v>
+        <v>1.42</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>11.23</v>
+        <v>13.7</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>-41.84</v>
+        <v>-36.1</v>
       </c>
       <c r="P5" s="10" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>-1.05</v>
+        <v>-1.25</v>
       </c>
       <c r="R5" s="17" t="n">
-        <v>85.09999999999999</v>
+        <v>107.5</v>
       </c>
       <c r="S5" s="17" t="n">
-        <v>87.3</v>
+        <v>97.5</v>
       </c>
       <c r="T5" s="11" t="n">
-        <v>11.74</v>
+        <v>6.6</v>
       </c>
       <c r="U5" s="18" t="n">
-        <v>0.843</v>
+        <v>1.015</v>
       </c>
       <c r="V5" s="18" t="n">
-        <v>0.892</v>
+        <v>0.868</v>
       </c>
       <c r="W5" s="11" t="n">
-        <v>2.15</v>
+        <v>1.32</v>
       </c>
       <c r="X5" s="17" t="n">
-        <v>82.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y5" s="17" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>2186.098</v>
+        <v>44.098</v>
       </c>
     </row>
     <row r="6">
@@ -58020,80 +58758,80 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Edelweiss Flexi Cap Fund - Direct Plan - Growth Option</t>
+          <t>HDFC Flexi Cap Fund - Growth Option - Direct Plan</t>
         </is>
       </c>
       <c r="C6" s="20" t="n">
         <v>82.7</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>0.5</v>
+        <v>8.01</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>20.36</v>
+        <v>23.56</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>23.35</v>
+        <v>28.09</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>15.81</v>
+        <v>17.08</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>19.34</v>
+        <v>22.3</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>19.81</v>
+        <v>24.22</v>
       </c>
       <c r="J6" s="21" t="n">
-        <v>19.26</v>
+        <v>20.97</v>
       </c>
       <c r="K6" s="21" t="n">
-        <v>17.25</v>
+        <v>16.86</v>
       </c>
       <c r="L6" s="22" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>13.7</v>
+        <v>11.23</v>
       </c>
       <c r="O6" s="23" t="n">
-        <v>-36.1</v>
+        <v>-41.84</v>
       </c>
       <c r="P6" s="22" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>-1.25</v>
+        <v>-1.05</v>
       </c>
       <c r="R6" s="24" t="n">
-        <v>107.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="S6" s="24" t="n">
-        <v>97.5</v>
+        <v>87.3</v>
       </c>
       <c r="T6" s="21" t="n">
-        <v>6.6</v>
+        <v>11.74</v>
       </c>
       <c r="U6" s="25" t="n">
-        <v>1.015</v>
+        <v>0.843</v>
       </c>
       <c r="V6" s="25" t="n">
-        <v>0.868</v>
+        <v>0.892</v>
       </c>
       <c r="W6" s="21" t="n">
-        <v>1.32</v>
+        <v>2.15</v>
       </c>
       <c r="X6" s="24" t="n">
-        <v>86.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="Y6" s="24" t="n">
-        <v>8.699999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="Z6" s="19" t="n">
-        <v>44.098</v>
+        <v>2186.098</v>
       </c>
     </row>
     <row r="7">
@@ -59080,7 +59818,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ICICI Prudential Flexi Cap Fund - Direct Plan - Growth</t>
+          <t>ICICI Prudential Flexicap Fund - Direct Plan - Growth</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 04 Sep 2026 19:43</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 07 Sep 2026 20:41</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 07 Sep 2026 20:41</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 08 Sep 2026 19:59</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 08 Sep 2026 19:59</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 09 Sep 2026 19:53</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 09 Sep 2026 19:53</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 10 Sep 2026 19:52</t>
         </is>
       </c>
     </row>

--- a/output/MF_Expert_Rankings.xlsx
+++ b/output/MF_Expert_Rankings.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏆  MF EXPERT RANKINGS  |  Generated: 10 Sep 2026 19:52</t>
+          <t>🏆  MF EXPERT RANKINGS  |  Generated: 11 Sep 2026 19:53</t>
         </is>
       </c>
     </row>
